--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -4365,39 +4365,39 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
+          <t>admin@idcloudhost.com</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Jeffrey Springborn</t>
+          <t>Alfian Pamungkas Sakawiguna</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Founder &amp; CEO</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>IDCloudHost</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://idcloudhost.com</t>
         </is>
       </c>
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr"/>
       <c r="H51" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://arenalte.com/life/teknologi/ekosistem-ai-saas-idcloudhost-dedicated-server-enterprise/ — Launched enterprise-class GPU-tier Dedicated Server line across its multi-location data center architecture (incl. its own Bogor facility) explicitly to support AI/ML and SaaS workloads</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4407,16 +4407,28 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L51" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>1a09d4f1dbf4c524</t>
+        </is>
+      </c>
       <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q51" t="inlineStr">
         <is>
           <t>none</t>
@@ -4434,39 +4446,31 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Nidhi Chappell</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>President, AI Infrastructure</t>
-        </is>
-      </c>
+          <t>aicenter@itb.ac.id</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr"/>
+      <c r="C52" t="inlineStr"/>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Institut Teknologi Bandung (ITB) Center for Artificial Intelligence</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://aicenter.itb.ac.id</t>
         </is>
       </c>
       <c r="F52" t="inlineStr"/>
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://itb.ac.id/center-for-artificial-intelligence and https://www.itb.ac.id/news/read/3055/home/optimizing-performance-and-efficiency-through-high-performance-computing — ITB operates a dedicated Center for Artificial Intelligence plus faculty-level High Performance Computing clusters supporting machine learning, NLP, computer vision and robotics research -- ongoing HPC capacity for AI research workloads</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4476,16 +4480,28 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L52" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>1a09d4f4cdada08c</t>
+        </is>
+      </c>
       <c r="N52" t="inlineStr"/>
-      <c r="O52" t="inlineStr"/>
-      <c r="P52" t="inlineStr"/>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q52" t="inlineStr">
         <is>
           <t>none</t>
@@ -4503,39 +4519,35 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Michael Intrator</t>
-        </is>
-      </c>
+          <t>bizdev@nscc.sg</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr"/>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>National Supercomputing Centre (NSCC) Singapore</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://www.nscc.sg</t>
         </is>
       </c>
       <c r="F53" t="inlineStr"/>
       <c r="G53" t="inlineStr"/>
       <c r="H53" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.nscc.sg/portfolio/item/reimagining-the-future-with-high-performance-computing-hpc/ — Singapore's national high-performance computing facility, providing HPC resources for AI and research computing needs across NUS, NTU, A*STAR and industry</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4545,16 +4557,28 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L53" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1a09d4ff92955ea9</t>
+        </is>
+      </c>
       <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>none</t>
@@ -4572,27 +4596,39 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr"/>
-      <c r="C54" t="inlineStr"/>
+          <t>boyang.li@ntu.edu.sg</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Li Boyang (Albert)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Director, High Performance Computing Centre, NTU / Associate Professor, CCDS</t>
+        </is>
+      </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>NTU High Performance Computing Centre</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.ntu.edu.sg/hpcc</t>
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr"/>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.ntu.edu.sg/hpcc — Operates NTU's High Performance Computing Centre supporting compute- and data-intensive HPC/AI workloads for the university's research community; NTU also hosts the FutureGrid Accelerator HVDC-AI testbed with STT GDC supporting &gt;1,000kW density racks</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4602,16 +4638,28 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L54" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>1a09d4ff2133b4bf</t>
+        </is>
+      </c>
       <c r="N54" t="inlineStr"/>
-      <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q54" t="inlineStr">
         <is>
           <t>none</t>
@@ -4629,39 +4677,39 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>cassie@starhub.com</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Cassie Fong</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Assistant Vice President, Corporate Communications</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>StarHub</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.starhub.com</t>
         </is>
       </c>
       <c r="F55" t="inlineStr"/>
       <c r="G55" t="inlineStr"/>
       <c r="H55" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.starhub.com/business/products-and-services/hosting-my-business/data-centre/hyperscale-data-centre.html — Hyperscale Data Centre (AirTrunk SGP1 partnership at Loyang) designed to a PUE of 1.3 using highly efficient cooling systems, described as Singapore's largest carrier-neutral data centre</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -4671,16 +4719,28 @@
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L55" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>1a09d4fd94d0a043</t>
+        </is>
+      </c>
       <c r="N55" t="inlineStr"/>
-      <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>none</t>
@@ -4698,39 +4758,31 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Don MacNeil</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Chief Revenue Officer</t>
-        </is>
-      </c>
+          <t>contactus@nxera-dc.com</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr"/>
+      <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Nxera (Singtel)</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://www.nxera-dc.com</t>
         </is>
       </c>
       <c r="F56" t="inlineStr"/>
       <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.singtel.com/about-us/media-centre/news-releases/nxera-opens-data-centre — Opened DC Tuas, a 58MW AI-ready facility described as Singapore's highest power-density data center, hosting the country's largest direct-to-chip liquid cooling deployment (cross-checked via DCD, iTnews Asia, Capacity coverage of the same launch)</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4740,16 +4792,28 @@
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L56" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>1a09d4faa25350eb</t>
+        </is>
+      </c>
       <c r="N56" t="inlineStr"/>
-      <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
+      <c r="O56" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>none</t>
@@ -4767,39 +4831,35 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Gary Wu</t>
-        </is>
-      </c>
+          <t>corpcomms@m1.com.sg</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr"/>
       <c r="C57" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Corporate Communications</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>M1 Limited</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://www.m1.com.sg</t>
         </is>
       </c>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.m1.com.sg/business/products/data-center — Operates the M1 Data Centre with cold aisle containment racks and integrated temperature/power/humidity monitoring, recently expanded to approximately 900 server racks</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4809,16 +4869,28 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L57" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>1a09d4fde0396188</t>
+        </is>
+      </c>
       <c r="N57" t="inlineStr"/>
-      <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
+      <c r="O57" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q57" t="inlineStr">
         <is>
           <t>none</t>
@@ -4836,39 +4908,39 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>corporate.secretary@linknet.co.id</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Edward Sanusi</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>Director &amp; Chief Technology Officer</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Link Net</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://www.linknet.co.id</t>
         </is>
       </c>
       <c r="F58" t="inlineStr"/>
       <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.linknet.co.id/en/newsroom/article/link-net-dan-zte-bangun-data-center-baru-di-surabaya — Built a new TIA942-A Rate 2+ certified data center in Surabaya with ZTE (300 racks combined with the upgraded Jakarta facility), CTO Edward Sanusi quoted on ensuring the data centers meet industry quality/reliability standards via multiple active power and cooling distribution paths (N+1)</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -4878,16 +4950,28 @@
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L58" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>1a09d4f23b2dc806</t>
+        </is>
+      </c>
       <c r="N58" t="inlineStr"/>
-      <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
+      <c r="O58" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q58" t="inlineStr">
         <is>
           <t>none</t>
@@ -4905,27 +4989,19 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>corsec@elitery.com</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Astrid Erawan</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Corporate Secretary</t>
-        </is>
-      </c>
+          <t>corporate.secretary@mayapadahospital.com</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr"/>
+      <c r="C59" t="inlineStr"/>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Elitery</t>
+          <t>Mayapada Hospital</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://elitery.com</t>
+          <t>https://mayapadahospital.com</t>
         </is>
       </c>
       <c r="F59" t="inlineStr"/>
@@ -4937,7 +5013,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>web_research: https://ir.elitery.com/perusahaan/ and https://baxtel.com/data-center/elitery-bogor — Operates Southeast Asia's first Uptime Institute Tier III certified data center in Bogor and is scaling AI platforms (Elipedia, Elitementor) while expanding regionally to Malaysia/Europe, increasing compute density needs at its own facility</t>
+          <t>web_research: https://issuu.com/charlton_media/docs/hca-h1-2023/s/28475480 — Mayapada Healthcare Group (7 hospitals, 1,200+ beds) is deploying AI-driven diagnostics with GE HealthCare and building hospital-wide patient data integration across its network -- growing clinical AI compute demand across its facilities</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -4947,16 +5023,28 @@
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L59" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>1a09d4f608cafeb3</t>
+        </is>
+      </c>
       <c r="N59" t="inlineStr"/>
-      <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
+      <c r="O59" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q59" t="inlineStr">
         <is>
           <t>none</t>
@@ -4974,27 +5062,27 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>admin@idcloudhost.com</t>
+          <t>corporate.secretary@siloamhospitals.com</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Alfian Pamungkas Sakawiguna</t>
+          <t>David Utama</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Founder &amp; CEO</t>
+          <t>President Director</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>IDCloudHost</t>
+          <t>Siloam Hospitals</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>https://idcloudhost.com</t>
+          <t>https://www.siloamhospitals.com</t>
         </is>
       </c>
       <c r="F60" t="inlineStr"/>
@@ -5006,7 +5094,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>web_research: https://arenalte.com/life/teknologi/ekosistem-ai-saas-idcloudhost-dedicated-server-enterprise/ — Launched enterprise-class GPU-tier Dedicated Server line across its multi-location data center architecture (incl. its own Bogor facility) explicitly to support AI/ML and SaaS workloads</t>
+          <t>web_research: https://healthtechasia.co/technology-should-support-clinical-judgement-not-replace-it-inside-siloams-hospital-of-the-future/ — Building a centralised enterprise AI foundation model trained on its own clinical data held locally in Indonesia (not on external cloud infrastructure) for data-sovereignty reasons, targeted complete by Nov 2026 across its 41-hospital network -- implying on-prem/local GPU compute buildout</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
@@ -5016,16 +5104,28 @@
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L60" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>1a09d4f29abe608e</t>
+        </is>
+      </c>
       <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
+      <c r="O60" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>none</t>
@@ -5043,27 +5143,27 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>corporate.secretary@linknet.co.id</t>
+          <t>corsec@elitery.com</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Edward Sanusi</t>
+          <t>Astrid Erawan</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Director &amp; Chief Technology Officer</t>
+          <t>Corporate Secretary</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Link Net</t>
+          <t>Elitery</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>https://www.linknet.co.id</t>
+          <t>https://elitery.com</t>
         </is>
       </c>
       <c r="F61" t="inlineStr"/>
@@ -5075,7 +5175,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>web_research: https://www.linknet.co.id/en/newsroom/article/link-net-dan-zte-bangun-data-center-baru-di-surabaya — Built a new TIA942-A Rate 2+ certified data center in Surabaya with ZTE (300 racks combined with the upgraded Jakarta facility), CTO Edward Sanusi quoted on ensuring the data centers meet industry quality/reliability standards via multiple active power and cooling distribution paths (N+1)</t>
+          <t>web_research: https://ir.elitery.com/perusahaan/ and https://baxtel.com/data-center/elitery-bogor — Operates Southeast Asia's first Uptime Institute Tier III certified data center in Bogor and is scaling AI platforms (Elipedia, Elitementor) while expanding regionally to Malaysia/Europe, increasing compute density needs at its own facility</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5085,16 +5185,28 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L61" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>1a09d4f186498993</t>
+        </is>
+      </c>
       <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q61" t="inlineStr">
         <is>
           <t>none</t>
@@ -5112,27 +5224,19 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>corporate.secretary@siloamhospitals.com</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>David Utama</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>President Director</t>
-        </is>
-      </c>
+          <t>customer.care@pegadaian.co.id</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr"/>
+      <c r="C62" t="inlineStr"/>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Siloam Hospitals</t>
+          <t>Pegadaian</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>https://www.siloamhospitals.com</t>
+          <t>https://pegadaian.co.id</t>
         </is>
       </c>
       <c r="F62" t="inlineStr"/>
@@ -5144,7 +5248,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>web_research: https://healthtechasia.co/technology-should-support-clinical-judgement-not-replace-it-inside-siloams-hospital-of-the-future/ — Building a centralised enterprise AI foundation model trained on its own clinical data held locally in Indonesia (not on external cloud infrastructure) for data-sovereignty reasons, targeted complete by Nov 2026 across its 41-hospital network -- implying on-prem/local GPU compute buildout</t>
+          <t>web_research: https://www.nutanix.com/company/customers/pt-pegadaian — Pegadaian deployed the Nutanix Cloud Platform across 100+ consumer-facing applications and partnered with Telkom Indonesia for Data Center Colocation and DRC infrastructure, while building a private cloud for database-as-a-service to support its AI/ITOps initiatives</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5154,16 +5258,28 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L62" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>1a09d4f66adef359</t>
+        </is>
+      </c>
       <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
+      <c r="O62" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q62" t="inlineStr">
         <is>
           <t>none</t>
@@ -5181,31 +5297,35 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>info@omnidc.co.id</t>
+          <t>datacenters@ironmountain.com</t>
         </is>
       </c>
       <c r="B63" t="inlineStr"/>
-      <c r="C63" t="inlineStr"/>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Data Centers Sales</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Omni Data Center Indonesia</t>
+          <t>Iron Mountain Data Centers Singapore (SIN-1)</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>https://omnidc.co.id</t>
+          <t>https://www.ironmountain.com/en-sg/data-centers/locations/apac/singapore-data-center</t>
         </is>
       </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>web_research: https://omnidc.co.id/ and https://www.datacentermap.com/indonesia/batam/omni-dc/ — Operates Tier 3, carrier-neutral, N+1 redundant colocation data centers in Batam (BTM1) and Jakarta serving Singapore-spillover demand; no named executive found, general company inbox used</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/analysis/making-iron-mountain-singapore-asia/ — DCD's profile of Iron Mountain's Singapore SIN-1 facility (Serangoon, 7.3MW, Tier III, ISO27001, acquired from Credit Suisse) describes column-free data halls supporting tall racks up to 52U -- a real, operating high-density colocation facility.</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -5215,16 +5335,28 @@
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L63" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>1a09d5021c19f862</t>
+        </is>
+      </c>
       <c r="N63" t="inlineStr"/>
-      <c r="O63" t="inlineStr"/>
-      <c r="P63" t="inlineStr"/>
+      <c r="O63" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q63" t="inlineStr">
         <is>
           <t>none</t>
@@ -5242,39 +5374,39 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>investor.relations@mitratel.co.id</t>
+          <t>frances.teh@keppel.com</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Theodorus Ardi Hartoko</t>
+          <t>Frances Teh</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Direktur Utama (President Director)</t>
+          <t>Director, Corporate Communications, Keppel Ltd</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Mitratel</t>
+          <t>Keppel Data Centres</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.mitratel.co.id</t>
+          <t>https://www.keppel.com</t>
         </is>
       </c>
       <c r="F64" t="inlineStr"/>
       <c r="G64" t="inlineStr"/>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>web_research: https://kumparan.com/kumparanbisnis/mitratel-mau-bikin-mini-data-center-sebagai-ekosistem-digital-1yaHOjcri8E — President Director Theodorus Ardi Hartoko quoted on Mitratel's transformation into an integrated digital infrastructure provider building Mini Data Centers near mobile users as part of its 'Beyond Tower' edge infrastructure strategy</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/keppel-and-shell-to-launch-immersion-cooling-pilot-at-singapore-data-center/ — Piloting immersion cooling with Shell at a Singapore data center to explore high-efficiency cooling for future AI/HPC workloads; also building Keppel DC SGP9, a 25MW floating data centre using seawater cooling (cross-checked via jpt.spe.org and Keppel's own newsroom coverage of the SGP campus)</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5284,16 +5416,28 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L64" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>1a09d4f9f6feb20f</t>
+        </is>
+      </c>
       <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
+      <c r="O64" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>none</t>
@@ -5311,39 +5455,31 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>jong@digitalrealty.com</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Joyce Ng</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Senior Communications Lead, Asia Pacific</t>
-        </is>
-      </c>
+          <t>info@bukalapak.com</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr"/>
+      <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Digital Realty</t>
+          <t>Bukalapak</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>https://www.digitalrealty.com</t>
+          <t>https://www.bukalapak.com</t>
         </is>
       </c>
       <c r="F65" t="inlineStr"/>
       <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>web_research: https://investor.digitalrealty.com/news-releases/news-release-details/digital-realty-selected-develop-50-megawatts-new-data-center — Selected by Singapore's EDB/IMDA to develop 50MW of new data center capacity, part of a nearly S$7 billion investment to strengthen Singapore as an APAC AI hub</t>
+          <t>web_research: https://www.itb.ac.id/news/read/56978/home/itb-bukalapak-join-hands-to-establish-laboratory-for-artificial-intelligence-and-cloud — Bukalapak established and operates an Artificial Intelligence &amp; Cloud Computing Innovation Center at ITB providing dedicated servers/compute infrastructure for AI and cloud research, per then-CEO Achmad Zaky</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5353,16 +5489,28 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L65" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>1a09d4f6d0f481ca</t>
+        </is>
+      </c>
       <c r="N65" t="inlineStr"/>
-      <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
+      <c r="O65" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q65" t="inlineStr">
         <is>
           <t>none</t>
@@ -5380,27 +5528,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>frances.teh@keppel.com</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Frances Teh</t>
-        </is>
-      </c>
+          <t>info@cmi.chinamobile.com</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr"/>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Director, Corporate Communications, Keppel Ltd</t>
+          <t>Sales &amp; Technical Enquiries</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Keppel Data Centres</t>
+          <t>China Mobile International (Singapore)</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>https://www.keppel.com</t>
+          <t>https://www.cmi.chinamobile.com</t>
         </is>
       </c>
       <c r="F66" t="inlineStr"/>
@@ -5412,7 +5556,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/keppel-and-shell-to-launch-immersion-cooling-pilot-at-singapore-data-center/ — Piloting immersion cooling with Shell at a Singapore data center to explore high-efficiency cooling for future AI/HPC workloads; also building Keppel DC SGP9, a 25MW floating data centre using seawater cooling (cross-checked via jpt.spe.org and Keppel's own newsroom coverage of the SGP campus)</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/china-mobile-international-launches-singapore-dc/ — DCD reports CMI's Tai Seng facility is a 17,490 sqm, six-floor, 2,100+ rack Singapore data centre built to Uptime Tier III TCDD/TCCF standards and awarded IMDA-BCA Green Mark Platinum -- a purpose-built high-density colocation facility with formal green/efficiency certification.</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5422,16 +5566,28 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L66" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>1a09d501529a79a9</t>
+        </is>
+      </c>
       <c r="N66" t="inlineStr"/>
-      <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
+      <c r="O66" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>none</t>
@@ -5449,39 +5605,31 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>yi.chow@sttelemediagdc.com</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Chow Yi</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Media Contact, ST Telemedia Global Data Centres</t>
-        </is>
-      </c>
+          <t>info@omnidc.co.id</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr"/>
+      <c r="C67" t="inlineStr"/>
       <c r="D67" t="inlineStr">
         <is>
-          <t>ST Telemedia Global Data Centres</t>
+          <t>Omni Data Center Indonesia</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>https://www.sttelemediagdc.com</t>
+          <t>https://omnidc.co.id</t>
         </is>
       </c>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>web_research: https://www.sttelemediagdc.com/sg-en/newsroom/stt-gdc-launches-southeast-asia-first-hvdc-powered-ai-infrastructure-testbed — Launched Southeast Asia's first HVDC-powered AI infrastructure testbed (FutureGrid Accelerator) at NTU, designed to support ultra-high-density AI racks exceeding 1,000kW</t>
+          <t>web_research: https://omnidc.co.id/ and https://www.datacentermap.com/indonesia/batam/omni-dc/ — Operates Tier 3, carrier-neutral, N+1 redundant colocation data centers in Batam (BTM1) and Jakarta serving Singapore-spillover demand; no named executive found, general company inbox used</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5491,16 +5639,28 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L67" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>1a09d4f31cc7a67a</t>
+        </is>
+      </c>
       <c r="N67" t="inlineStr"/>
-      <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
+      <c r="O67" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>none</t>
@@ -5518,19 +5678,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>contactus@nxera-dc.com</t>
+          <t>info@tech.gov.sg</t>
         </is>
       </c>
       <c r="B68" t="inlineStr"/>
-      <c r="C68" t="inlineStr"/>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Media/General Enquiries</t>
+        </is>
+      </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Nxera (Singtel)</t>
+          <t>GovTech Singapore</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>https://www.nxera-dc.com</t>
+          <t>https://www.tech.gov.sg</t>
         </is>
       </c>
       <c r="F68" t="inlineStr"/>
@@ -5542,7 +5706,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>web_research: https://www.singtel.com/about-us/media-centre/news-releases/nxera-opens-data-centre — Opened DC Tuas, a 58MW AI-ready facility described as Singapore's highest power-density data center, hosting the country's largest direct-to-chip liquid cooling deployment (cross-checked via DCD, iTnews Asia, Capacity coverage of the same launch)</t>
+          <t>web_research: https://www.tech.gov.sg/about-us/what-we-do/our-digital-government-efforts/ai-and-data-driven-government/ — Runs Government on Commercial Cloud (GCC), with over 70% of eligible government systems now on commercial cloud infrastructure, unlocking AI capabilities (Gemini 2.5 Flash, Vertex AI Search) across public-sector agencies</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5552,16 +5716,28 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L68" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>1a09d4fecf627095</t>
+        </is>
+      </c>
       <c r="N68" t="inlineStr"/>
-      <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
+      <c r="O68" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>none</t>
@@ -5579,35 +5755,39 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>media@airtrunk.com</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr"/>
+          <t>investor.relations@cimbniaga.co.id</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Billie Setiawan</t>
+        </is>
+      </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Media Relations</t>
+          <t>Head of Data Analytics and AI</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>AirTrunk</t>
+          <t>CIMB Niaga</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>https://airtrunk.com</t>
+          <t>https://www.cimbniaga.co.id</t>
         </is>
       </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/singapore-selects-equinix-microsoft-airtrunk-and-gds-for-80mw-data-center-trial/ — AirTrunk-ByteDance consortium awarded new data center capacity by Singapore's EDB/IMDA under the DC-CFA pilot; AirTrunk separately developing SGP2, one of Singapore's largest upcoming data centers at 70MW+</t>
+          <t>web_research: https://www.googlecloudpresscorner.com/2026-04-14-CIMB-Niaga,-Google-Cloud,-and-Artefact-Debut-Enterprise-AI-Agents-to-Deliver-Life-Centric-Banking-for-Millions-of-Indonesians — Billie Setiawan, Head of Data Analytics and AI, quoted on CIMB Niaga's April 2026 launch (with Google Cloud and Artefact) of enterprise AI agents built by its in-house AI Center of Excellence on Google Cloud's full-stack AI infrastructure</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5617,16 +5797,28 @@
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L69" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>1a09d4f3c61cade3</t>
+        </is>
+      </c>
       <c r="N69" t="inlineStr"/>
-      <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
+      <c r="O69" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q69" t="inlineStr">
         <is>
           <t>none</t>
@@ -5644,39 +5836,39 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>laurenmy@microsoft.com</t>
+          <t>investor.relations@mitratel.co.id</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Lauren Myers Cavanagh</t>
+          <t>Theodorus Ardi Hartoko</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Senior Director of Communications, Asia</t>
+          <t>Direktur Utama (President Director)</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Microsoft Azure Singapore</t>
+          <t>Mitratel</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>https://www.microsoft.com</t>
+          <t>https://www.mitratel.co.id</t>
         </is>
       </c>
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr"/>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/microsoft-commits-to-55bn-ai-and-cloud-investment-in-singapore-by-2029/ — Committed $5.5B to AI and cloud infrastructure investment in Singapore through 2029; stood up approximately 1GW of data center capacity in the prior three months as of a January 2026 announcement</t>
+          <t>web_research: https://kumparan.com/kumparanbisnis/mitratel-mau-bikin-mini-data-center-sebagai-ekosistem-digital-1yaHOjcri8E — President Director Theodorus Ardi Hartoko quoted on Mitratel's transformation into an integrated digital infrastructure provider building Mini Data Centers near mobile users as part of its 'Beyond Tower' edge infrastructure strategy</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -5686,16 +5878,28 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L70" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>1a09d4f36fcce6f8</t>
+        </is>
+      </c>
       <c r="N70" t="inlineStr"/>
-      <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
+      <c r="O70" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q70" t="inlineStr">
         <is>
           <t>none</t>
@@ -5713,23 +5917,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>press@google.com</t>
+          <t>itcare@nus.edu.sg</t>
         </is>
       </c>
       <c r="B71" t="inlineStr"/>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Press/Media Relations</t>
+          <t>NUS IT Care</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Google Cloud Singapore</t>
+          <t>NUS IT (High Performance Computing)</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>https://cloud.google.com</t>
+          <t>https://nusit.nus.edu.sg/hpc/</t>
         </is>
       </c>
       <c r="F71" t="inlineStr"/>
@@ -5741,7 +5945,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/google-completes-expansion-of-singapore-data-center-and-cloud-region/ — Completed the latest phase of its Singapore data center and cloud region campus expansion, bringing total technical infrastructure investment in Singapore to US$5 billion</t>
+          <t>web_research: https://nusit.nus.edu.sg/hpc/ — NUS IT provides centralized HPC infrastructure services to support NUS faculty, researchers and students across campus for compute-intensive research workloads</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -5751,16 +5955,28 @@
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L71" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M71" t="inlineStr">
+        <is>
+          <t>1a09d4fff566fa27</t>
+        </is>
+      </c>
       <c r="N71" t="inlineStr"/>
-      <c r="O71" t="inlineStr"/>
-      <c r="P71" t="inlineStr"/>
+      <c r="O71" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q71" t="inlineStr">
         <is>
           <t>none</t>
@@ -5778,23 +5994,27 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>press@meta.com</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr"/>
+          <t>jong@digitalrealty.com</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Joyce Ng</t>
+        </is>
+      </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Press/Media Relations</t>
+          <t>Senior Communications Lead, Asia Pacific</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Meta Singapore</t>
+          <t>Digital Realty</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>https://datacenters.atmeta.com</t>
+          <t>https://www.digitalrealty.com</t>
         </is>
       </c>
       <c r="F72" t="inlineStr"/>
@@ -5806,7 +6026,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>web_research: https://www.metacareers.com/blog/singapore-data-center/ — Meta's Singapore Data Center is its first custom-built hyperscale facility in Asia and only APAC data center -- an 11-story, ~150MW building requiring purpose-built cooling design for Singapore's tropical climate</t>
+          <t>web_research: https://investor.digitalrealty.com/news-releases/news-release-details/digital-realty-selected-develop-50-megawatts-new-data-center — Selected by Singapore's EDB/IMDA to develop 50MW of new data center capacity, part of a nearly S$7 billion investment to strengthen Singapore as an APAC AI hub</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -5816,16 +6036,28 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L72" t="n">
-        <v>0</v>
-      </c>
-      <c r="M72" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M72" t="inlineStr">
+        <is>
+          <t>1a09d4f994acd464</t>
+        </is>
+      </c>
       <c r="N72" t="inlineStr"/>
-      <c r="O72" t="inlineStr"/>
-      <c r="P72" t="inlineStr"/>
+      <c r="O72" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>none</t>
@@ -5843,23 +6075,27 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>media@dayonedc.com</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr"/>
+          <t>laurenmy@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Lauren Myers Cavanagh</t>
+        </is>
+      </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Media Contact</t>
+          <t>Senior Director of Communications, Asia</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>DayOne Data Centers</t>
+          <t>Microsoft Azure Singapore</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>https://dayonedc.com</t>
+          <t>https://www.microsoft.com</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
@@ -5871,7 +6107,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>web_research: https://www.dbs.com/newsroom/DayOne_secures_SGD_530_million_green_loan_from_DBS_OCBC_and_UOB_for_its_first_Singapore_data_centre — Building its first Singapore data centre (20MW), incorporating hybrid air and liquid cooling technologies and on-site Solid Oxide Fuel Cell power generation; achieved BCA Green Mark Platinum (Provisional)</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/microsoft-commits-to-55bn-ai-and-cloud-investment-in-singapore-by-2029/ — Committed $5.5B to AI and cloud infrastructure investment in Singapore through 2029; stood up approximately 1GW of data center capacity in the prior three months as of a January 2026 announcement</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -5881,16 +6117,28 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L73" t="n">
-        <v>0</v>
-      </c>
-      <c r="M73" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>1a09d4fb77404f62</t>
+        </is>
+      </c>
       <c r="N73" t="inlineStr"/>
-      <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
+      <c r="O73" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>none</t>
@@ -5908,27 +6156,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>cassie@starhub.com</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>Cassie Fong</t>
-        </is>
-      </c>
+          <t>media@airtrunk.com</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr"/>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Assistant Vice President, Corporate Communications</t>
+          <t>Media Relations</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>StarHub</t>
+          <t>AirTrunk</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>https://www.starhub.com</t>
+          <t>https://airtrunk.com</t>
         </is>
       </c>
       <c r="F74" t="inlineStr"/>
@@ -5940,7 +6184,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>web_research: https://www.starhub.com/business/products-and-services/hosting-my-business/data-centre/hyperscale-data-centre.html — Hyperscale Data Centre (AirTrunk SGP1 partnership at Loyang) designed to a PUE of 1.3 using highly efficient cooling systems, described as Singapore's largest carrier-neutral data centre</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapore-selects-equinix-microsoft-airtrunk-and-gds-for-80mw-data-center-trial/ — AirTrunk-ByteDance consortium awarded new data center capacity by Singapore's EDB/IMDA under the DC-CFA pilot; AirTrunk separately developing SGP2, one of Singapore's largest upcoming data centers at 70MW+</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -5950,16 +6194,28 @@
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L74" t="n">
-        <v>0</v>
-      </c>
-      <c r="M74" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>1a09d4fb2595ebd7</t>
+        </is>
+      </c>
       <c r="N74" t="inlineStr"/>
-      <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
+      <c r="O74" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q74" t="inlineStr">
         <is>
           <t>none</t>
@@ -5977,23 +6233,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>corpcomms@m1.com.sg</t>
+          <t>media@dayonedc.com</t>
         </is>
       </c>
       <c r="B75" t="inlineStr"/>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Corporate Communications</t>
+          <t>Media Contact</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>M1 Limited</t>
+          <t>DayOne Data Centers</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>https://www.m1.com.sg</t>
+          <t>https://dayonedc.com</t>
         </is>
       </c>
       <c r="F75" t="inlineStr"/>
@@ -6005,7 +6261,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>web_research: https://www.m1.com.sg/business/products/data-center — Operates the M1 Data Centre with cold aisle containment racks and integrated temperature/power/humidity monitoring, recently expanded to approximately 900 server racks</t>
+          <t>web_research: https://www.dbs.com/newsroom/DayOne_secures_SGD_530_million_green_loan_from_DBS_OCBC_and_UOB_for_its_first_Singapore_data_centre — Building its first Singapore data centre (20MW), incorporating hybrid air and liquid cooling technologies and on-site Solid Oxide Fuel Cell power generation; achieved BCA Green Mark Platinum (Provisional)</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6015,16 +6271,28 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L75" t="n">
-        <v>0</v>
-      </c>
-      <c r="M75" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>1a09d4fd2937dd3a</t>
+        </is>
+      </c>
       <c r="N75" t="inlineStr"/>
-      <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
+      <c r="O75" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>none</t>
@@ -6042,39 +6310,31 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>qsm@imda.gov.sg</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Jo-Anne Tan</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>Quality Service Manager</t>
-        </is>
-      </c>
+          <t>pandawa@bpjs-kesehatan.go.id</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr"/>
+      <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Infocomm Media Development Authority (IMDA)</t>
+          <t>BPJS Kesehatan</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>https://www.imda.gov.sg</t>
+          <t>https://www.bpjs-kesehatan.go.id</t>
         </is>
       </c>
       <c r="F76" t="inlineStr"/>
       <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>web_research: https://isomer-user-content.by.gov.sg/38/c49f426a-8053-4c7f-bbaa-8437b743a18f/files-Speeches%202024-1__Factsheet_IMDA_Green_DC_Roadmap.pdf — IMDA's Green Data Centre Roadmap requires new data center capacity (DC-CFA2, 200MW+ call) to hit a PUE of 1.25 at 100% IT load, driving industry-wide adoption of liquid cooling (direct-to-chip, rear-door heat exchange, immersion) -- note: IMDA is the regulator setting these requirements, not an operator itself, so this is a policy-influence/we</t>
+          <t>web_research: https://www.cloudcomputing.id/berita/bpjs-kesehatan-tingkatkan-layanan-ai-big-data — BPJS Kesehatan invested in GPUs to build AI agents that verify hundreds of thousands of health claim documents for its 280 million participants nationwide -- a national-scale GPU compute deployment</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6084,16 +6344,28 @@
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L76" t="n">
-        <v>0</v>
-      </c>
-      <c r="M76" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>1a09d4f542a64b6a</t>
+        </is>
+      </c>
       <c r="N76" t="inlineStr"/>
-      <c r="O76" t="inlineStr"/>
-      <c r="P76" t="inlineStr"/>
+      <c r="O76" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>none</t>
@@ -6111,23 +6383,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>info@tech.gov.sg</t>
+          <t>press@google.com</t>
         </is>
       </c>
       <c r="B77" t="inlineStr"/>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Media/General Enquiries</t>
+          <t>Press/Media Relations</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>GovTech Singapore</t>
+          <t>Google Cloud Singapore</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>https://www.tech.gov.sg</t>
+          <t>https://cloud.google.com</t>
         </is>
       </c>
       <c r="F77" t="inlineStr"/>
@@ -6139,7 +6411,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>web_research: https://www.tech.gov.sg/about-us/what-we-do/our-digital-government-efforts/ai-and-data-driven-government/ — Runs Government on Commercial Cloud (GCC), with over 70% of eligible government systems now on commercial cloud infrastructure, unlocking AI capabilities (Gemini 2.5 Flash, Vertex AI Search) across public-sector agencies</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/google-completes-expansion-of-singapore-data-center-and-cloud-region/ — Completed the latest phase of its Singapore data center and cloud region campus expansion, bringing total technical infrastructure investment in Singapore to US$5 billion</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6149,16 +6421,28 @@
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L77" t="n">
-        <v>0</v>
-      </c>
-      <c r="M77" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>1a09d4fbc58598f8</t>
+        </is>
+      </c>
       <c r="N77" t="inlineStr"/>
-      <c r="O77" t="inlineStr"/>
-      <c r="P77" t="inlineStr"/>
+      <c r="O77" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q77" t="inlineStr">
         <is>
           <t>none</t>
@@ -6176,27 +6460,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>boyang.li@ntu.edu.sg</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>Li Boyang (Albert)</t>
-        </is>
-      </c>
+          <t>press@meta.com</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr"/>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Director, High Performance Computing Centre, NTU / Associate Professor, CCDS</t>
+          <t>Press/Media Relations</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NTU High Performance Computing Centre</t>
+          <t>Meta Singapore</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.ntu.edu.sg/hpcc</t>
+          <t>https://datacenters.atmeta.com</t>
         </is>
       </c>
       <c r="F78" t="inlineStr"/>
@@ -6208,7 +6488,7 @@
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>web_research: https://www.ntu.edu.sg/hpcc — Operates NTU's High Performance Computing Centre supporting compute- and data-intensive HPC/AI workloads for the university's research community; NTU also hosts the FutureGrid Accelerator HVDC-AI testbed with STT GDC supporting &gt;1,000kW density racks</t>
+          <t>web_research: https://www.metacareers.com/blog/singapore-data-center/ — Meta's Singapore Data Center is its first custom-built hyperscale facility in Asia and only APAC data center -- an 11-story, ~150MW building requiring purpose-built cooling design for Singapore's tropical climate</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6218,16 +6498,28 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L78" t="n">
-        <v>0</v>
-      </c>
-      <c r="M78" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>1a09d4fc3e651845</t>
+        </is>
+      </c>
       <c r="N78" t="inlineStr"/>
-      <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
+      <c r="O78" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q78" t="inlineStr">
         <is>
           <t>none</t>
@@ -6245,23 +6537,27 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>bizdev@nscc.sg</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr"/>
+          <t>qsm@imda.gov.sg</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Jo-Anne Tan</t>
+        </is>
+      </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Business Development</t>
+          <t>Quality Service Manager</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>National Supercomputing Centre (NSCC) Singapore</t>
+          <t>Infocomm Media Development Authority (IMDA)</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>https://www.nscc.sg</t>
+          <t>https://www.imda.gov.sg</t>
         </is>
       </c>
       <c r="F79" t="inlineStr"/>
@@ -6273,7 +6569,7 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>web_research: https://www.nscc.sg/portfolio/item/reimagining-the-future-with-high-performance-computing-hpc/ — Singapore's national high-performance computing facility, providing HPC resources for AI and research computing needs across NUS, NTU, A*STAR and industry</t>
+          <t>web_research: https://isomer-user-content.by.gov.sg/38/c49f426a-8053-4c7f-bbaa-8437b743a18f/files-Speeches%202024-1__Factsheet_IMDA_Green_DC_Roadmap.pdf — IMDA's Green Data Centre Roadmap requires new data center capacity (DC-CFA2, 200MW+ call) to hit a PUE of 1.25 at 100% IT load, driving industry-wide adoption of liquid cooling (direct-to-chip, rear-door heat exchange, immersion) -- note: IMDA is the regulator setting these requirements, not an operator itself, so this is a policy-influence/we</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6283,16 +6579,28 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L79" t="n">
-        <v>0</v>
-      </c>
-      <c r="M79" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>1a09d4fe79f5b578</t>
+        </is>
+      </c>
       <c r="N79" t="inlineStr"/>
-      <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
+      <c r="O79" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>none</t>
@@ -6310,23 +6618,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>itcare@nus.edu.sg</t>
+          <t>sales@1-net.com.sg</t>
         </is>
       </c>
       <c r="B80" t="inlineStr"/>
       <c r="C80" t="inlineStr">
         <is>
-          <t>NUS IT Care</t>
+          <t>Sales Enquiries</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NUS IT (High Performance Computing)</t>
+          <t>1-Net Singapore</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>https://nusit.nus.edu.sg/hpc/</t>
+          <t>https://www.1-net.com.sg</t>
         </is>
       </c>
       <c r="F80" t="inlineStr"/>
@@ -6338,7 +6646,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>web_research: https://nusit.nus.edu.sg/hpc/ — NUS IT provides centralized HPC infrastructure services to support NUS faculty, researchers and students across campus for compute-intensive research workloads</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/1-net-launches-new-data-center-in-singapore/ — DCD reports 1-Net North, a S$130m+ (with a further S$70m fit-out) purpose-built facility, became the first commercial data centre in Southeast Asia certified Tier III Constructed Facility by the Uptime Institute -- a real, capital-intensive high-density colocation build.</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6348,16 +6656,28 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L80" t="n">
-        <v>0</v>
-      </c>
-      <c r="M80" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>1a09d501ab3e936f</t>
+        </is>
+      </c>
       <c r="N80" t="inlineStr"/>
-      <c r="O80" t="inlineStr"/>
-      <c r="P80" t="inlineStr"/>
+      <c r="O80" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>none</t>
@@ -6375,27 +6695,27 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>investor.relations@cimbniaga.co.id</t>
+          <t>sales@bd-dc.com</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Billie Setiawan</t>
+          <t>Angelo Syailendra</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Head of Data Analytics and AI</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>CIMB Niaga</t>
+          <t>Bersama Digital Data Centers (Digital Realty Bersama)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>https://www.cimbniaga.co.id</t>
+          <t>https://www.bd-dc.com</t>
         </is>
       </c>
       <c r="F81" t="inlineStr"/>
@@ -6407,7 +6727,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>web_research: https://www.googlecloudpresscorner.com/2026-04-14-CIMB-Niaga,-Google-Cloud,-and-Artefact-Debut-Enterprise-AI-Agents-to-Deliver-Life-Centric-Banking-for-Millions-of-Indonesians — Billie Setiawan, Head of Data Analytics and AI, quoted on CIMB Niaga's April 2026 launch (with Google Cloud and Artefact) of enterprise AI agents built by its in-house AI Center of Excellence on Google Cloud's full-stack AI infrastructure</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/digital-realty-expands-into-indonesia-forms-jv-with-bersama-digital-infrastructure-asia/ and https://www.mingtiandi.com/real-estate/data-centres/digital-realty-enters-indonesia-data-centre-market-with-bersama/ — Digital Realty formed a 50:50 JV with Bersama Digital Infrastructure Asia in March 2025; CEO Angelo Syailendra continues leading BDDC's Jakarta campuses (CGK10/CGK11) scaling to 32MW with scalable power densities and advanced cooli</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
@@ -6417,16 +6737,28 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
-      </c>
-      <c r="M81" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>1a09d4f5a0396323</t>
+        </is>
+      </c>
       <c r="N81" t="inlineStr"/>
-      <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
+      <c r="O81" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:10+00:00</t>
+        </is>
+      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>none</t>
@@ -6444,31 +6776,35 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>aicenter@itb.ac.id</t>
+          <t>salessingapore@globalswitch.com</t>
         </is>
       </c>
       <c r="B82" t="inlineStr"/>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Sales &amp; Customer Service, Global Switch Singapore</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Institut Teknologi Bandung (ITB) Center for Artificial Intelligence</t>
+          <t>Global Switch Singapore</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://aicenter.itb.ac.id</t>
+          <t>https://www.globalswitch.com/data-centres/singapore/</t>
         </is>
       </c>
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr"/>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>web_research: https://itb.ac.id/center-for-artificial-intelligence and https://www.itb.ac.id/news/read/3055/home/optimizing-performance-and-efficiency-through-high-performance-computing — ITB operates a dedicated Center for Artificial Intelligence plus faculty-level High Performance Computing clusters supporting machine learning, NLP, computer vision and robotics research -- ongoing HPC capacity for AI research workloads</t>
+          <t>web_research: https://www.globalswitch.com/data-centres/singapore/ — Global Switch's own Singapore data centres page states the Tai Seng and Woodlands campuses 'support the full spectrum of density needs, from entry-level to AI-grade high-density with air or liquid cooling' -- a direct, self-described high-density/liquid-cooling capacity signal at two active Singapore facilities.</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6478,16 +6814,28 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>1a09d500fc7caa46</t>
+        </is>
+      </c>
       <c r="N82" t="inlineStr"/>
-      <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
+      <c r="O82" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>none</t>
@@ -6505,31 +6853,39 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>pandawa@bpjs-kesehatan.go.id</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr"/>
-      <c r="C83" t="inlineStr"/>
+          <t>yi.chow@sttelemediagdc.com</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Chow Yi</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Media Contact, ST Telemedia Global Data Centres</t>
+        </is>
+      </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>BPJS Kesehatan</t>
+          <t>ST Telemedia Global Data Centres</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>https://www.bpjs-kesehatan.go.id</t>
+          <t>https://www.sttelemediagdc.com</t>
         </is>
       </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>web_research: https://www.cloudcomputing.id/berita/bpjs-kesehatan-tingkatkan-layanan-ai-big-data — BPJS Kesehatan invested in GPUs to build AI agents that verify hundreds of thousands of health claim documents for its 280 million participants nationwide -- a national-scale GPU compute deployment</t>
+          <t>web_research: https://www.sttelemediagdc.com/sg-en/newsroom/stt-gdc-launches-southeast-asia-first-hvdc-powered-ai-infrastructure-testbed — Launched Southeast Asia's first HVDC-powered AI infrastructure testbed (FutureGrid Accelerator) at NTU, designed to support ultra-high-density AI racks exceeding 1,000kW</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -6539,16 +6895,28 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
-      </c>
-      <c r="M83" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>1a09d4fa4d6b6d00</t>
+        </is>
+      </c>
       <c r="N83" t="inlineStr"/>
-      <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
+      <c r="O83" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:25:16+00:00</t>
+        </is>
+      </c>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>2026-09-14T00:27:56+00:00</t>
+        </is>
+      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>none</t>
@@ -6566,39 +6934,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>sales@bd-dc.com</t>
+          <t>info@colovore.com</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Angelo Syailendra</t>
+          <t>Jeffrey Springborn</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Chief Executive Officer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Bersama Digital Data Centers (Digital Realty Bersama)</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://www.bd-dc.com</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/digital-realty-expands-into-indonesia-forms-jv-with-bersama-digital-infrastructure-asia/ and https://www.mingtiandi.com/real-estate/data-centres/digital-realty-enters-indonesia-data-centre-market-with-bersama/ — Digital Realty formed a 50:50 JV with Bersama Digital Infrastructure Asia in March 2025; CEO Angelo Syailendra continues leading BDDC's Jakarta campuses (CGK10/CGK11) scaling to 32MW with scalable power densities and advanced cooli</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6635,31 +7003,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>corporate.secretary@mayapadahospital.com</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr"/>
-      <c r="C85" t="inlineStr"/>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Mayapada Hospital</t>
+          <t>Nscale</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://mayapadahospital.com</t>
+          <t>https://nscale.com</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>web_research: https://issuu.com/charlton_media/docs/hca-h1-2023/s/28475480 — Mayapada Healthcare Group (7 hospitals, 1,200+ beds) is deploying AI-driven diagnostics with GE HealthCare and building hospital-wide patient data integration across its network -- growing clinical AI compute demand across its facilities</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -6696,31 +7072,39 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>customer.care@pegadaian.co.id</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr"/>
-      <c r="C86" t="inlineStr"/>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Pegadaian</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://pegadaian.co.id</t>
+          <t>https://coreweave.com</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Indonesia</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>web_research: https://www.nutanix.com/company/customers/pt-pegadaian — Pegadaian deployed the Nutanix Cloud Platform across 100+ consumer-facing applications and partnered with Telkom Indonesia for Data Center Colocation and DRC infrastructure, while building a private cloud for database-as-a-service to support its AI/ITOps initiatives</t>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -6757,31 +7141,27 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>info@bukalapak.com</t>
+          <t>deepinfra@scratchmm.com</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Bukalapak</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://www.bukalapak.com</t>
+          <t>https://deepinfra.com</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
-          <t>web_research: https://www.itb.ac.id/news/read/56978/home/itb-bukalapak-join-hands-to-establish-laboratory-for-artificial-intelligence-and-cloud — Bukalapak established and operates an Artificial Intelligence &amp; Cloud Computing Innovation Center at ITB providing dedicated servers/compute infrastructure for AI and cloud research, per then-CEO Achmad Zaky</t>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -6818,35 +7198,39 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>salessingapore@globalswitch.com</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr"/>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Sales &amp; Customer Service, Global Switch Singapore</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Global Switch Singapore</t>
+          <t>EdgeMode Inc.</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://www.globalswitch.com/data-centres/singapore/</t>
+          <t>https://edgemode.io</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>web_research: https://www.globalswitch.com/data-centres/singapore/ — Global Switch's own Singapore data centres page states the Tai Seng and Woodlands campuses 'support the full spectrum of density needs, from entry-level to AI-grade high-density with air or liquid cooling' -- a direct, self-described high-density/liquid-cooling capacity signal at two active Singapore facilities.</t>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6883,35 +7267,39 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>info@cmi.chinamobile.com</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr"/>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sales &amp; Technical Enquiries</t>
+          <t>Chief Revenue Officer</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>China Mobile International (Singapore)</t>
+          <t>EdgeConneX</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://www.cmi.chinamobile.com</t>
+          <t>https://edgeconnex.com</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/china-mobile-international-launches-singapore-dc/ — DCD reports CMI's Tai Seng facility is a 17,490 sqm, six-floor, 2,100+ rack Singapore data centre built to Uptime Tier III TCDD/TCCF standards and awarded IMDA-BCA Green Mark Platinum -- a purpose-built high-density colocation facility with formal green/efficiency certification.</t>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -6948,35 +7336,39 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>sales@1-net.com.sg</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr"/>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Sales Enquiries</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>1-Net Singapore</t>
+          <t>Fluidstack</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://www.1-net.com.sg</t>
+          <t>https://fluidstack.io</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/1-net-launches-new-data-center-in-singapore/ — DCD reports 1-Net North, a S$130m+ (with a further S$70m fit-out) purpose-built facility, became the first commercial data centre in Southeast Asia certified Tier III Constructed Facility by the Uptime Institute -- a real, capital-intensive high-density colocation build.</t>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7013,35 +7405,39 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>datacenters@ironmountain.com</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr"/>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Data Centers Sales</t>
+          <t>VP of Data Center Infrastructure</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Iron Mountain Data Centers Singapore (SIN-1)</t>
+          <t>Lambda, Inc.</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://www.ironmountain.com/en-sg/data-centers/locations/apac/singapore-data-center</t>
+          <t>https://lambda.ai</t>
         </is>
       </c>
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/analysis/making-iron-mountain-singapore-asia/ — DCD's profile of Iron Mountain's Singapore SIN-1 facility (Serangoon, 7.3MW, Tier III, ISO27001, acquired from Credit Suisse) describes column-free data halls supporting tall racks up to 52U -- a real, operating high-density colocation facility.</t>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -5489,28 +5489,24 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L65" t="n">
         <v>1</v>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>1a09d4f6d0f481ca</t>
-        </is>
-      </c>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr"/>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>550 5.1.1 The email account that you tried to reach does not exist. (mailer-daemon, Bukalapak)</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr">
         <is>
           <t>2026-09-14T00:25:16+00:00</t>
         </is>
       </c>
-      <c r="P65" t="inlineStr">
-        <is>
-          <t>2026-09-14T00:27:10+00:00</t>
-        </is>
-      </c>
+      <c r="P65" t="inlineStr"/>
       <c r="Q65" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U91"/>
+  <dimension ref="A1:U117"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6930,39 +6930,39 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
+          <t>andrea.ng@capitaland.com</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Jeffrey Springborn</t>
+          <t>Andrea Ng</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Investor Enquiries Contact</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>CapitaLand Ascendas REIT</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.capitaland.com</t>
         </is>
       </c>
       <c r="F84" t="inlineStr"/>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.capitaland.com/en/about-capitaland/newsroom/news-releases/international/2026/march/capitaland-ascendas-reit-acquires-two-assets-in-Singapore-and-enters-Japan-with-a-hyperscale-data-centre.html — CapitaLand Ascendas REIT expanded its Singapore high-density data-centre portfolio (Ascendas Tech Park Data Center targets hyperscale/enterprise high-density colocation demand) via a S$1.4B acquisition including its first hyperscale data centre entry in Japan</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -6972,16 +6972,28 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
-      </c>
-      <c r="M84" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>1a0a2de35a9b5215</t>
+        </is>
+      </c>
       <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
-      <c r="P84" t="inlineStr"/>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>none</t>
@@ -6999,39 +7011,39 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>corpcomms@micron.com</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Manish Bhatia</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Executive Vice President, Global Operations</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Micron Singapore</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.micron.com</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.globenewswire.com/news-release/2026/01/27/3226056/14450/en/micron-breaks-ground-on-advanced-wafer-fabrication-facility-in-singapore.html — Micron broke ground on a ~US$24B advanced wafer fabrication facility in Singapore (700,000 sq ft cleanroom) plus a separate ~US$7B HBM advanced packaging facility, both driven by AI/data-centric memory demand; EVP Global Operations Manish Bhatia quoted on the investment</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7041,16 +7053,28 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>1a0a2de15f84971f</t>
+        </is>
+      </c>
       <c r="N85" t="inlineStr"/>
-      <c r="O85" t="inlineStr"/>
-      <c r="P85" t="inlineStr"/>
+      <c r="O85" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>none</t>
@@ -7068,39 +7092,35 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Michael Intrator</t>
-        </is>
-      </c>
+          <t>corporate.secretary@mncland.com</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr"/>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Corporate Secretary</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>PT MNC Land Tbk</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://www.mncland.com</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/mnc-to-build-data-center-in-lido-resort-city-south-of-jakarta-indonesia/ — Partnering with PT Infokom Elektrindo to build a Techno Park with data center and AI center inside KEK MNC Lido City, part of a site with 450MW+ of total planned capacity</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7110,16 +7130,28 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L86" t="n">
-        <v>0</v>
-      </c>
-      <c r="M86" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>1a0a2dd9886fbd3b</t>
+        </is>
+      </c>
       <c r="N86" t="inlineStr"/>
-      <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
+      <c r="O86" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>none</t>
@@ -7137,27 +7169,31 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>cs@rspondokindah.co.id</t>
         </is>
       </c>
       <c r="B87" t="inlineStr"/>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>RS Pondok Indah Group</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.rspondokindah.co.id</t>
         </is>
       </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.healthcareitnews.com/news/asia/rs-pondok-indah-group-clinches-first-stage-7-emram-indonesia — First hospital group in Indonesia to achieve HIMSS EMRAM Stage 7, building fully digital EMR infrastructure with automated device connectivity across its 3 hospitals</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7167,16 +7203,28 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L87" t="n">
-        <v>0</v>
-      </c>
-      <c r="M87" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>1a0a2dd906b35ca1</t>
+        </is>
+      </c>
       <c r="N87" t="inlineStr"/>
-      <c r="O87" t="inlineStr"/>
-      <c r="P87" t="inlineStr"/>
+      <c r="O87" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>none</t>
@@ -7194,39 +7242,35 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Charlie Faulkner</t>
-        </is>
-      </c>
+          <t>feedback@dsta.gov.sg</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr"/>
       <c r="C88" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>General Feedback</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>DSTA (Defence Science and Technology Agency)</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.dsta.gov.sg</t>
         </is>
       </c>
       <c r="F88" t="inlineStr"/>
       <c r="G88" t="inlineStr"/>
       <c r="H88" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.oracle.com/news/announcement/dsta-selects-oracle-cloud-infrastructure-for-ministry-of-defence-singapore-2025-03-19/ — DSTA selected Oracle Cloud Infrastructure to build an air-gapped Oracle Cloud Isolated Region supporting MINDEF and the Singapore Armed Forces, giving them sovereign cloud computing, data management and AI infrastructure; DSTA's own InfoComm Infrastructure programme also designs/manages cloud data centres for MINDEF/SAF and Whole-of-Government C3 systems</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7236,16 +7280,28 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L88" t="n">
-        <v>0</v>
-      </c>
-      <c r="M88" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>1a0a2de5225ef463</t>
+        </is>
+      </c>
       <c r="N88" t="inlineStr"/>
-      <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
+      <c r="O88" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
       <c r="Q88" t="inlineStr">
         <is>
           <t>none</t>
@@ -7263,39 +7319,31 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Don MacNeil</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Chief Revenue Officer</t>
-        </is>
-      </c>
+          <t>gallant@gallantventure.com</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr"/>
+      <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Gallant Venture Ltd (Bintan Data Center Hub)</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://www.gallantventure.com</t>
         </is>
       </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.forbes.com/sites/ardianwibisono/2025/10/27/dci-indonesia-tycoon-anthoni-salims-gallant-venture-building-data-center-hub-near-singapore/ — Jointly building with DCI Indonesia a gigawatt-scale data center complex on a 700-hectare site on Bintan Island near Singapore, targeted ready by 2027</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7305,16 +7353,28 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L89" t="n">
-        <v>0</v>
-      </c>
-      <c r="M89" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>1a0a2dd8aa8fa00b</t>
+        </is>
+      </c>
       <c r="N89" t="inlineStr"/>
-      <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
       <c r="Q89" t="inlineStr">
         <is>
           <t>none</t>
@@ -7332,39 +7392,31 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Gary Wu</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>halo@ikn.go.id</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr"/>
+      <c r="C90" t="inlineStr"/>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>Otorita Ibu Kota Nusantara (IKN Authority)</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://www.ikn.go.id</t>
         </is>
       </c>
       <c r="F90" t="inlineStr"/>
       <c r="G90" t="inlineStr"/>
       <c r="H90" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://konstruksimedia.com/otorita-ikn-dan-ustda-perkuat-kolaborasi-ai-dan-data-untuk-wujudkan-nusantara-sebagai-kota-cerdas/ — Building AI/data-driven smart city infrastructure for Indonesia's new capital Nusantara, in collaboration with USTDA and tech partners (Honeywell, Cisco, IBM, Google) including a smart-city command center</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7374,16 +7426,28 @@
       </c>
       <c r="K90" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L90" t="n">
-        <v>0</v>
-      </c>
-      <c r="M90" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>1a0a2dda324ee80c</t>
+        </is>
+      </c>
       <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>none</t>
@@ -7401,39 +7465,35 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Ken Patchett</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>VP of Data Center Infrastructure</t>
-        </is>
-      </c>
+          <t>helpdesk@kemkes.go.id</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr"/>
+      <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Kementerian Kesehatan RI (SATUSEHAT)</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr"/>
+          <t>https://satusehat.kemkes.go.id</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>0811-1050-0567</t>
+        </is>
+      </c>
       <c r="G91" t="inlineStr"/>
       <c r="H91" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://satusehat.kemkes.go.id/data — Operates SATUSEHAT, a national health-data integration platform running on cloud infrastructure processing nationwide EMR/health facility data, with AI initiatives for 5 priority diseases</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7443,16 +7503,28 @@
       </c>
       <c r="K91" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L91" t="n">
-        <v>0</v>
-      </c>
-      <c r="M91" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>1a0a2dddfe0be885</t>
+        </is>
+      </c>
       <c r="N91" t="inlineStr"/>
-      <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
       <c r="Q91" t="inlineStr">
         <is>
           <t>none</t>
@@ -7466,6 +7538,1916 @@
       </c>
       <c r="T91" t="inlineStr"/>
       <c r="U91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>htx_contact@htx.gov.sg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr"/>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>HTX (Home Team Science and Technology Agency)</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.htx.gov.sg</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr"/>
+      <c r="G92" t="inlineStr"/>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>web_research: https://www.htx.gov.sg/who-we-are/what-we-do/the-htxai-movement — HTX built NGINE, the Ministry of Home Affairs' first enterprise-grade AI compute infrastructure, spanning 30+ integrated technologies across compute, orchestration, networking and observability to support LLM training/modelling/simulation at scale</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L92" t="n">
+        <v>1</v>
+      </c>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>1a0a2de584f514f6</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q92" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R92" t="inlineStr"/>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T92" t="inlineStr"/>
+      <c r="U92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>humas@bmkg.go.id</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr"/>
+      <c r="C93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>BMKG (Badan Meteorologi, Klimatologi, dan Geofisika)</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr"/>
+      <c r="G93" t="inlineStr"/>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>web_research: https://www.bmkg.go.id/berita/bmkg-luncurkan-superkomputer-smong-perkuat-sistem-peringatan-dini-multi-hazards — Launched SMONG supercomputer (5 PFlops combined CPU+GPU across HPC MMS and HPC SMONG clusters) for multi-hazard early warning and AI-based weather modeling, one of the fastest HPC systems in Southeast Asia</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L93" t="n">
+        <v>1</v>
+      </c>
+      <c r="M93" t="inlineStr">
+        <is>
+          <t>1a0a2ddaf337367c</t>
+        </is>
+      </c>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q93" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R93" t="inlineStr"/>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T93" t="inlineStr"/>
+      <c r="U93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>humas@bpbatam.go.id</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr"/>
+      <c r="C94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>BP Batam (Badan Pengusahaan Batam)</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://bpbatam.go.id</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr"/>
+      <c r="G94" t="inlineStr"/>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>web_research: https://ptsp.bpbatam.go.id/en/bp-batam-kawal-investasi-rp88-triliun-ai-data-centre-untuk-transformasi-digital-batam/ — Government authority fast-tracking and overseeing a USD 5 billion (Rp88 trillion) High-Density AI Data Centre investment in Nongsa, Batam</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K94" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L94" t="n">
+        <v>1</v>
+      </c>
+      <c r="M94" t="inlineStr">
+        <is>
+          <t>1a0a2dde425c1176</t>
+        </is>
+      </c>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q94" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R94" t="inlineStr"/>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T94" t="inlineStr"/>
+      <c r="U94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>humas@unud.ac.id</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Universitas Udayana (UCEAI - Pusat Kajian Kecerdasan Artifisial)</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>https://uceai.unud.ac.id</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>web_research: https://uceai.unud.ac.id/ — Runs a dedicated AI research center (UCEAI) focused on AI development, research and application for Bali and Eastern Indonesia</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K95" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L95" t="n">
+        <v>1</v>
+      </c>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>1a0a2dda98245850</t>
+        </is>
+      </c>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q95" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T95" t="inlineStr"/>
+      <c r="U95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>info@big.go.id</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr"/>
+      <c r="C96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>Badan Informasi Geospasial (BIG)</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>https://www.big.go.id</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr"/>
+      <c r="G96" t="inlineStr"/>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>web_research: https://www.antaranews.com/berita/409549/big-bangun-data-center-raksasa-geospasial — Built a large-scale geospatial data center (300TB, expanding toward 1000TB) with Fujitsu and is developing an Integrated Map Production Center using HPC infrastructure</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K96" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L96" t="n">
+        <v>1</v>
+      </c>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>1a0a2ddcda6c321e</t>
+        </is>
+      </c>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q96" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T96" t="inlineStr"/>
+      <c r="U96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>info@biofarma.co.id</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr"/>
+      <c r="C97" t="inlineStr"/>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>PT Bio Farma (Persero)</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>https://www.biofarma.co.id</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr"/>
+      <c r="G97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>web_research: https://www.biofarma.co.id/en/latest-news/detail/bio-farma-and-google-cloud-indonesia-agree-on-the-mou-for-cooperation-in-healthcare-digital-transformation — Signed MoU with Google Cloud Indonesia for IaaS/PaaS/SaaS infrastructure supporting AI/ML for bioinformatics R&amp;D (vaccine and compound modeling)</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L97" t="n">
+        <v>1</v>
+      </c>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>1a0a2ddd2fdeb81e</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q97" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R97" t="inlineStr"/>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T97" t="inlineStr"/>
+      <c r="U97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>info@kpu.go.id</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr"/>
+      <c r="C98" t="inlineStr"/>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>Komisi Pemilihan Umum (KPU) Republik Indonesia</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.kpu.go.id</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr"/>
+      <c r="G98" t="inlineStr"/>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>web_research: https://www.kpu.go.id/berita/baca/12716/kpu-siapkan-data-center-pemantauan-sirekap-pilkada — Preparing a dedicated data center to monitor the Sirekap election-recapitulation system for Pilkada, processing nationwide vote data</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K98" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L98" t="n">
+        <v>1</v>
+      </c>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>1a0a2ddd8ffd8b99</t>
+        </is>
+      </c>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q98" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R98" t="inlineStr"/>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T98" t="inlineStr"/>
+      <c r="U98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>info@pupuk-indonesia.com</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr"/>
+      <c r="C99" t="inlineStr"/>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>PT Pupuk Indonesia (Persero)</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>https://www.pupuk-indonesia.com</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>0811 1000 1959</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr"/>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>web_research: https://cloud.google.com/customers/pupuk — Runs Data Center (DC) and Disaster Recovery Center (DRC) infrastructure and uses AI/Vision AI (Google Cloud) plus 32,000 factory sensors across its fertilizer manufacturing operations</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K99" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L99" t="n">
+        <v>1</v>
+      </c>
+      <c r="M99" t="inlineStr">
+        <is>
+          <t>1a0a2ddc1b478c4f</t>
+        </is>
+      </c>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q99" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T99" t="inlineStr"/>
+      <c r="U99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>janice.yeo@silicon-box.com</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Janice Yeo</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Press Contact</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Silicon Box</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://www.silicon-box.com</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr"/>
+      <c r="G100" t="inlineStr"/>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>web_research: https://www.silicon-box.com/silicon-box-launches-2-billion-state-of-the-art-advanced-semiconductor-packaging-fab-in-singapore-to-accelerate-the-future-of-computing-and-the-ai-era — Launched a $2B advanced semiconductor packaging (chiplet interconnection) fab at Tampines Wafer Fab Park, Singapore -- a 73,000 sqm facility built specifically to accelerate AI-era computing, now shipping 250M+ units</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L100" t="n">
+        <v>1</v>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>1a0a2de1abdf8fb7</t>
+        </is>
+      </c>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q100" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T100" t="inlineStr"/>
+      <c r="U100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>jtc_comms_div@jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Christine Wong</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Assistant Chief Executive (Cluster Group)</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>JTC Corporation</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>web_research: https://www.jtc.gov.sg/jurongisland/story-articles/nus-and-jtc-join-forces-to-power-jurong-island-green-transition — JTC has set aside 20 hectares on Jurong Island for Singapore's largest low-carbon Data Centre Park (up to 700MW); JTC signed an MOU with NUS to study a Sustainable Tropical Data Centre Testbed Phase 2.0 piloting direct-to-chip and immersion liquid cooling plus seawater-based heat rejection for AI-class density, with Assistant CEO Christine Wong presenting the MOU</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L101" t="n">
+        <v>1</v>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>1a0a2de0eca46360</t>
+        </is>
+      </c>
+      <c r="N101" t="inlineStr"/>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q101" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R101" t="inlineStr"/>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T101" t="inlineStr"/>
+      <c r="U101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>kominfo@jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr"/>
+      <c r="C102" t="inlineStr"/>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Diskominfo Provinsi Jawa Timur</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>https://kominfo.jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr"/>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>web_research: https://kominfo.jatimprov.go.id/berita/diskominfo-jatim-peroleh-sertifikasi-iso-27001-2022-untuk-data-center — Operates a provincial data center (with Disaster Recovery Center) serving all Pemprov Jatim agencies plus 16 district/city governments, ISO 27001:2022 certified</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L102" t="n">
+        <v>1</v>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>1a0a2dd9ca0ed4a8</t>
+        </is>
+      </c>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q102" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R102" t="inlineStr"/>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T102" t="inlineStr"/>
+      <c r="U102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>lily.ho@sgx.com</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Ho Lily</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Marketing &amp; Communications</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Singapore Exchange (SGX)</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>https://www.sgx.com</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr"/>
+      <c r="G103" t="inlineStr"/>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>web_research: https://investorrelations.sgx.com/news-releases/news-release-details/sgx-offers-fastest-connection-its-markets — SGX's own 'Reach' initiative was a $250M project to build a world-class data centre with the world's fastest trading engine and lowest trading latency for its Singapore co-location infrastructure, which continues to host SGX's critical trading systems</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L103" t="n">
+        <v>1</v>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>1a0a2de4bdd5b10c</t>
+        </is>
+      </c>
+      <c r="N103" t="inlineStr"/>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q103" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R103" t="inlineStr"/>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T103" t="inlineStr"/>
+      <c r="U103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>marilyn.tan@mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Marilyn Tan</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Assistant Manager, Corporate Communications</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Mapletree Investments</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>https://www.mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr"/>
+      <c r="G104" t="inlineStr"/>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>web_research: https://www.mapletree.com.sg/newsroom/mapletree-investments-and-mapletree-industrial-trust-to-acquire-us1-4-billion-data-centre-portfolio-in-north-america-from-digital-realty/ — Mapletree develops and owns purpose-built high-tech data centres in Singapore (STT Tai Seng 1, Equinix SG3, Mapletree Sunview 1) and continues expanding its global data-centre portfolio, including a US$1.4B North American DC acquisition</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L104" t="n">
+        <v>1</v>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>1a0a2de457e92620</t>
+        </is>
+      </c>
+      <c r="N104" t="inlineStr"/>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q104" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R104" t="inlineStr"/>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T104" t="inlineStr"/>
+      <c r="U104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>partnership@apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr"/>
+      <c r="C105" t="inlineStr"/>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Angkasa Pura Sarana Digital (APSD)</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>https://apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr"/>
+      <c r="G105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>web_research: https://investor.id/business/314676/angkasa-pura-ii-jajaki-pembangunan-data-center-di-bandara-soekarno-hatta — Angkasa Pura II's digital subsidiary exploring construction of a data center at Soekarno-Hatta Airport as part of a 'Smart Connected Airport' strategy</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L105" t="n">
+        <v>1</v>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>1a0a2ddc6ec22fdb</t>
+        </is>
+      </c>
+      <c r="N105" t="inlineStr"/>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:20:52+00:00</t>
+        </is>
+      </c>
+      <c r="Q105" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R105" t="inlineStr"/>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T105" t="inlineStr"/>
+      <c r="U105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>sales@leaseweb.com</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr"/>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Sales</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>Leaseweb Singapore</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://www.leaseweb.com</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr"/>
+      <c r="G106" t="inlineStr"/>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>web_research: https://www.leaseweb.com/en/press/releases/significant-momentum-in-singapore-with-continued-apac-expansion — Leaseweb operates multiple Singapore data centres (SIN-01, SIN-12) offering colocation (rack/full rack/cage), reporting significant momentum and continued APAC expansion out of Singapore</t>
+        </is>
+      </c>
+      <c r="J106" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K106" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L106" t="n">
+        <v>1</v>
+      </c>
+      <c r="M106" t="inlineStr">
+        <is>
+          <t>1a0a2de5f104a385</t>
+        </is>
+      </c>
+      <c r="N106" t="inlineStr"/>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q106" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R106" t="inlineStr"/>
+      <c r="S106" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T106" t="inlineStr"/>
+      <c r="U106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>sales@telehouse.com</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr"/>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Sales Enquiries</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>Telehouse Singapore</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>https://www.telehouse.com</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>web_research: https://www.telehouse.com/global-data-centers/asia/singapore-data-centers/telehouse-singapore/ — Telehouse's Tier 3+ Chai Chee, Singapore facility runs an N+2 redundancy climate-control cooling system with rack power extendable up to 5kVA, part of its carrier-neutral colocation offering in Singapore</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K107" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L107" t="n">
+        <v>1</v>
+      </c>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>1a0a2de2ffffd072</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr"/>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q107" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R107" t="inlineStr"/>
+      <c r="S107" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T107" t="inlineStr"/>
+      <c r="U107" t="inlineStr"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>sales@utacgroup.com</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Sales Enquiries</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>UTAC Group</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>https://utacgroup.com</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>web_research: https://www.plasmatherm.com/repeat-order-with-utac/ — UTAC's Singapore advanced packaging and test facility purchased a repeat Singulator 300 plasma dicing system to expand die-singulation/advanced-packaging capacity, supporting growing WLCSP packaging demand at its Singapore site</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L108" t="n">
+        <v>1</v>
+      </c>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>1a0a2de28cb6b15f</t>
+        </is>
+      </c>
+      <c r="N108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P108" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q108" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T108" t="inlineStr"/>
+      <c r="U108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>vis_pr@vis.com.tw</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr"/>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Media Relations (Vanguard International Semiconductor, majority JV partner)</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>VSMC (VisionPower Semiconductor Manufacturing Company)</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>https://www.vis.com.tw</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr"/>
+      <c r="G109" t="inlineStr"/>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>web_research: https://www.globenewswire.com/news-release/2024/12/04/2991195/0/en/VSMC-Celebrates-Breaking-Ground-on-300mm-Fab-in-Singapore.html — VSMC (JV between Vanguard International Semiconductor and NXP) broke ground on a ~US$6.7-7.8B 300mm wafer fab in Tampines, Singapore, targeting 44,000 wafers/month for automotive, industrial and power semiconductor demand</t>
+        </is>
+      </c>
+      <c r="J109" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K109" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L109" t="n">
+        <v>1</v>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>1a0a2de229c3f27c</t>
+        </is>
+      </c>
+      <c r="N109" t="inlineStr"/>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:19:24+00:00</t>
+        </is>
+      </c>
+      <c r="P109" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:21:23+00:00</t>
+        </is>
+      </c>
+      <c r="Q109" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T109" t="inlineStr"/>
+      <c r="U109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>Colovore</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>https://colovore.com</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr"/>
+      <c r="G110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K110" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L110" t="n">
+        <v>0</v>
+      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
+      <c r="P110" t="inlineStr"/>
+      <c r="Q110" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R110" t="inlineStr"/>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T110" t="inlineStr"/>
+      <c r="U110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr"/>
+      <c r="G111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J111" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K111" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L111" t="n">
+        <v>0</v>
+      </c>
+      <c r="M111" t="inlineStr"/>
+      <c r="N111" t="inlineStr"/>
+      <c r="O111" t="inlineStr"/>
+      <c r="P111" t="inlineStr"/>
+      <c r="Q111" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R111" t="inlineStr"/>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T111" t="inlineStr"/>
+      <c r="U111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J112" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L112" t="n">
+        <v>0</v>
+      </c>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
+      <c r="P112" t="inlineStr"/>
+      <c r="Q112" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T112" t="inlineStr"/>
+      <c r="U112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr"/>
+      <c r="G113" t="inlineStr"/>
+      <c r="H113" t="inlineStr"/>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J113" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L113" t="n">
+        <v>0</v>
+      </c>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr"/>
+      <c r="O113" t="inlineStr"/>
+      <c r="P113" t="inlineStr"/>
+      <c r="Q113" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T113" t="inlineStr"/>
+      <c r="U113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr"/>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L114" t="n">
+        <v>0</v>
+      </c>
+      <c r="M114" t="inlineStr"/>
+      <c r="N114" t="inlineStr"/>
+      <c r="O114" t="inlineStr"/>
+      <c r="P114" t="inlineStr"/>
+      <c r="Q114" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T114" t="inlineStr"/>
+      <c r="U114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J115" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K115" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L115" t="n">
+        <v>0</v>
+      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
+      <c r="O115" t="inlineStr"/>
+      <c r="P115" t="inlineStr"/>
+      <c r="Q115" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T115" t="inlineStr"/>
+      <c r="U115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K116" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L116" t="n">
+        <v>0</v>
+      </c>
+      <c r="M116" t="inlineStr"/>
+      <c r="N116" t="inlineStr"/>
+      <c r="O116" t="inlineStr"/>
+      <c r="P116" t="inlineStr"/>
+      <c r="Q116" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T116" t="inlineStr"/>
+      <c r="U116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L117" t="n">
+        <v>0</v>
+      </c>
+      <c r="M117" t="inlineStr"/>
+      <c r="N117" t="inlineStr"/>
+      <c r="O117" t="inlineStr"/>
+      <c r="P117" t="inlineStr"/>
+      <c r="Q117" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T117" t="inlineStr"/>
+      <c r="U117" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7478,7 +9460,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L124"/>
+  <dimension ref="A1:L161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7726,7 +9708,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J5" t="inlineStr">
         <is>
           <t>Rolled out direct liquid-to-chip cooling for high-density colocation across 170 data centers globally to support AI workloads; a press contact email could not be independently confirmed, so routed via contact form</t>
@@ -7902,7 +9888,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr">
         <is>
           <t>Signed a 511MVA (~450MW) power purchase agreement with PT PLN Batam -- Indonesia's largest single-facility utility deal -- to power a new hyperscale campus in Kabil Industrial Tech Park, Batam; no verifiable published business-contact email found</t>
@@ -11536,7 +13526,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr"/>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J86" t="inlineStr">
         <is>
           <t>Tier III certified data center in Bogor; regional AI/cloud expansion</t>
@@ -11628,7 +13622,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J88" t="inlineStr">
         <is>
           <t>Multi-location data center architecture with GPU-power dedicated servers for AI workloads</t>
@@ -11670,7 +13668,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr"/>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr">
         <is>
           <t>New Surabaya data center + upgraded Jakarta facility, TIA942-A Rate 2+, N+1 power/cooling redundancy</t>
@@ -11712,7 +13714,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr"/>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J90" t="inlineStr">
         <is>
           <t>Local (non-cloud) AI foundation model training on clinical data for data sovereignty</t>
@@ -11754,7 +13760,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr"/>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J91" t="inlineStr">
         <is>
           <t>Tier 3, N+1 redundant Batam/Jakarta colocation facility</t>
@@ -11796,7 +13806,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
           <t>Edge Mini Data Center buildout as part of 'Beyond Tower' strategy</t>
@@ -11838,7 +13852,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J93" t="inlineStr">
         <is>
           <t>Immersion cooling pilot with Shell; SGP9 25MW floating data centre with seawater cooling</t>
@@ -11880,7 +13898,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J94" t="inlineStr">
         <is>
           <t>FutureGrid Accelerator HVDC AI testbed supporting &gt;1,000kW density racks</t>
@@ -11922,7 +13944,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J95" t="inlineStr">
         <is>
           <t>DC Tuas 58MW AI-ready facility, largest direct-to-chip liquid cooling deployment in Singapore</t>
@@ -11964,7 +13990,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J96" t="inlineStr">
         <is>
           <t>AirTrunk-ByteDance IMDA/EDB capacity award; SGP2 70MW+ facility under development</t>
@@ -12006,7 +14036,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr">
         <is>
           <t>$5.5B AI/cloud investment in Singapore through 2029, ~1GW capacity stood up recently</t>
@@ -12048,7 +14082,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>Completed Singapore data center/cloud region expansion, US$5B total technical infrastructure investment</t>
@@ -12090,7 +14128,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J99" t="inlineStr">
         <is>
           <t>First Singapore data centre (20MW), hybrid air/liquid cooling, SOFC power generation</t>
@@ -12132,7 +14174,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J100" t="inlineStr">
         <is>
           <t>Hyperscale Data Centre PUE 1.3, highly efficient cooling systems, AirTrunk SGP1 partnership</t>
@@ -12174,7 +14220,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I101" t="inlineStr"/>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J101" t="inlineStr">
         <is>
           <t>M1 Data Centre: cold aisle containment, ~900 server racks, temp/power/humidity monitoring</t>
@@ -12216,7 +14266,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I102" t="inlineStr"/>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J102" t="inlineStr">
         <is>
           <t>Green Data Centre Roadmap: PUE 1.25 requirement for new capacity, liquid cooling adoption push</t>
@@ -12258,7 +14312,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J103" t="inlineStr">
         <is>
           <t>Government on Commercial Cloud, 70%+ eligible systems migrated, AI capability rollout</t>
@@ -12300,7 +14358,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr"/>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J104" t="inlineStr">
         <is>
           <t>National HPC facility for AI/research computing needs</t>
@@ -12636,7 +14698,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I112" t="inlineStr"/>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J112" t="inlineStr">
         <is>
           <t>See prospects.csv row -- CIMB Niaga AI agents deployment with Google Cloud/Artefact</t>
@@ -12720,7 +14786,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr">
         <is>
           <t>See prospects.csv row -- Mayapada AI diagnostics and data integration across network</t>
@@ -12762,7 +14832,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J115" t="inlineStr">
         <is>
           <t>See prospects.csv row -- Pegadaian Nutanix private cloud + Telkom DC colocation</t>
@@ -12804,7 +14878,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J116" t="inlineStr">
         <is>
           <t>See prospects.csv row -- Bukalapak AI &amp; Cloud Computing Innovation Center at ITB</t>
@@ -12888,7 +14966,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I118" t="inlineStr"/>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J118" t="inlineStr">
         <is>
           <t>Own site states Tai Seng/Woodlands campuses support AI-grade high-density with air or liquid cooling.</t>
@@ -12930,7 +15012,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I119" t="inlineStr"/>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr">
         <is>
           <t>17,490 sqm Tier III, Green Mark Platinum Singapore data centre at Tai Seng.</t>
@@ -13014,7 +15100,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I121" t="inlineStr"/>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr">
         <is>
           <t>Tier III Constructed Facility certified 1-Net North data centre build, first of its kind in Southeast Asia.</t>
@@ -13154,6 +15244,1600 @@
       <c r="L124" t="inlineStr">
         <is>
           <t>2026-09-13T19:18:50+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Mark Fong</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Chief Executive Officer</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Empyrion Digital</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>https://empyriondigital.com</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr"/>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://empyriondigital.com/contact/</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>Empyrion Digital (Singapore-HQ'd since 2021) is investing over S$1.1B to expand Singapore data-centre capacity for high-density AI/cloud workloads; its SG1 Dodid facility targets PUE below 1.20 and Green Mark Platinum certification. CEO Mark Fong quoted: 'Singapore is the foundation of everything we are building across Asia.' No domain-matched email found, only a contact form.</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>https://empyriondigital.com/quantum-safe-and-ai-ready-empyrion-digitals-singapore-hub-expands-local-footprint-with-over-s1-1-billion-investment-302747926.html</t>
+        </is>
+      </c>
+      <c r="L125" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr"/>
+      <c r="B126" t="inlineStr"/>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Synapxe</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>https://www.synapxe.sg</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr"/>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.synapxe.sg/contact-us</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>Synapxe, Singapore's national HealthTech agency, built H-Cloud to rationalise and consolidate local hospital data centres into a modernised, nation-wide private cloud serving all public hospitals, specialty centres, polyclinics and nursing homes. No domain-matched named-individual email found, only a contact form.</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>https://www.synapxe.sg/healthtech/cloud/h-cloud</t>
+        </is>
+      </c>
+      <c r="L126" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>Tim Rosenfield</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Co-Founder &amp; Co-CEO</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Sustainable Metal Cloud (SMC)</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>https://smc.co</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://smc.co/about-us</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>Singapore-founded and HQ'd SMC runs fully immersion-cooled NVIDIA GPU clusters (SIN01/SIN02 availability zones at STT GDC) for AI training/inference, with co-CEO Tim Rosenfield stating immersion cooling 'enables high density hosting for GPUs...the sort of hosting we need to see for platforms like [Nvidia's] Grace Blackwell.' No domain-matched published email found (only third-party guessed patterns, not used); routed via contact form.</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/singapores-sustainable-metal-cloud-outlines-global-expansion-plans/</t>
+        </is>
+      </c>
+      <c r="L127" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr"/>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>SSMC (Systems on Silicon Manufacturing Company)</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>https://www.ssmc.com</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr"/>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.ssmc.com/ContactUs</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>SSMC (NXP/TSMC JV) built a S$300M Annex 10 cleanroom extension at its Pasir Ris, Singapore fab -- a 34% increase in cleanroom space for automotive and specialty chip manufacturing capacity. No domain-matched email found, only a contact form.</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>https://semiwiki.com/forum/threads/vsmc-new-fab-going-up-in-singapore-video.23542/</t>
+        </is>
+      </c>
+      <c r="L128" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr"/>
+      <c r="B129" t="inlineStr"/>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Soitec Singapore</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>https://www.soitec.com</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr"/>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.soitec.com/en/contact</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>Soitec is investing EUR400M (~$430M) to double capacity at its Pasir Ris, Singapore wafer fab (+45,000 sqm), recently qualifying the facility for high-volume Photonics SOI manufacturing to supply substrates for AI-focused data centers. No domain-matched email found, only a contact form.</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>https://www.edb.gov.sg/en/about-edb/media-releases-publications/soitec-breaks-ground-on-singapore-fab-extension-to-grow-its-global-semiconductor-wafer-production-capacity.html</t>
+        </is>
+      </c>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Luana Low</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Public Relations, Singapore</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>GlobalFoundries Singapore</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>https://gf.com</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr"/>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://gf.com/about-gf/contact-us/</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>GlobalFoundries officially opened its US$4B expansion fab in Singapore (23,000 sqm), its most advanced Singapore semiconductor facility to date, raising overall Singapore capacity to ~1.5M 300mm wafers/year. Named PR contact Luana Low (Public Relations, Singapore) found on GF's own newsroom page, but exact email text was obscured/unrenderable in search results, so not used as a verified address; routed via contact form.</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>https://www.edb.gov.sg/en/about-edb/media-releases-publications/globalfoundries-opens-us4-billion-expansion-facility-in-singapore.html</t>
+        </is>
+      </c>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Christine Wong</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Assistant Chief Executive (Cluster Group)</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>JTC Corporation</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr"/>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg/Pages/contact-us.aspx</t>
+        </is>
+      </c>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr"/>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>Jurong Island Data Centre Park (up to 700MW), liquid/seawater cooling testbed with NUS.</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>https://www.jtc.gov.sg/jurongisland/story-articles/nus-and-jtc-join-forces-to-power-jurong-island-green-transition</t>
+        </is>
+      </c>
+      <c r="L131" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr"/>
+      <c r="B132" t="inlineStr"/>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Micron Singapore</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>https://sg.micron.com</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr"/>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://sg.micron.com/forms/contact-us</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr"/>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>$24B advanced wafer fab + $7B HBM packaging facility investment in Singapore.</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/01/27/3226056/14450/en/micron-breaks-ground-on-advanced-wafer-fabrication-facility-in-singapore.html</t>
+        </is>
+      </c>
+      <c r="L132" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>VSMC (VisionPower Semiconductor Manufacturing Company)</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>https://www.vis.com.tw</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.vis.com.tw/en/about_contact</t>
+        </is>
+      </c>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>$6.7-7.8B 300mm wafer fab JV under construction in Tampines, Singapore.</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2024/12/04/2991195/0/en/VSMC-Celebrates-Breaking-Ground-on-300mm-Fab-in-Singapore.html</t>
+        </is>
+      </c>
+      <c r="L133" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr"/>
+      <c r="B134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>UTAC Group</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>https://utacgroup.com</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr"/>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://utacgroup.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>Advanced packaging/plasma-dicing capacity expansion at Singapore facility.</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>https://www.plasmatherm.com/repeat-order-with-utac/</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr"/>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Telehouse Singapore</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>https://www.telehouse.com</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr"/>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.telehouse.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>Tier 3+ facility with N+2 cooling redundancy in Singapore.</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>https://www.telehouse.com/global-data-centers/asia/singapore-data-centers/telehouse-singapore/</t>
+        </is>
+      </c>
+      <c r="L135" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr"/>
+      <c r="B136" t="inlineStr"/>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CapitaLand Ascendas REIT</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>https://www.capitaland.com</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr"/>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.capitaland.com/en/invest/clar/en/contact-us.html</t>
+        </is>
+      </c>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>S$1.4B acquisition expanding high-density Singapore data-centre portfolio.</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>https://www.capitaland.com/en/about-capitaland/newsroom/news-releases/international/2026/march/capitaland-ascendas-reit-acquires-two-assets-in-Singapore-and-enters-Japan-with-a-hyperscale-data-centre.html</t>
+        </is>
+      </c>
+      <c r="L136" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr"/>
+      <c r="B137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Mapletree Investments</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>https://www.mapletree.com.sg</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr"/>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.mapletree.com.sg/contact-us/</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>Develops/owns purpose-built high-tech data centres in Singapore.</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>https://www.mapletree.com.sg/newsroom/mapletree-investments-and-mapletree-industrial-trust-to-acquire-us1-4-billion-data-centre-portfolio-in-north-america-from-digital-realty/</t>
+        </is>
+      </c>
+      <c r="L137" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Singapore Exchange (SGX)</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>https://www.sgx.com</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.sgx.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>SGX 'Reach' initiative: $250M world-class low-latency data centre for its own trading infrastructure.</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>https://investorrelations.sgx.com/news-releases/news-release-details/sgx-offers-fastest-connection-its-markets</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr"/>
+      <c r="B139" t="inlineStr"/>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>DSTA (Defence Science and Technology Agency)</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>https://www.dsta.gov.sg</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr"/>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.dsta.gov.sg/contact</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Isolated Region for MINDEF/SAF sovereign cloud/AI infrastructure.</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/news/announcement/dsta-selects-oracle-cloud-infrastructure-for-ministry-of-defence-singapore-2025-03-19/</t>
+        </is>
+      </c>
+      <c r="L139" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr"/>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>HTX (Home Team Science and Technology Agency)</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>https://www.htx.gov.sg</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr"/>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.htx.gov.sg/contact-us</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>NGINE AI compute infrastructure for LLM training/modelling/simulation at scale.</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>https://www.htx.gov.sg/who-we-are/what-we-do/the-htxai-movement</t>
+        </is>
+      </c>
+      <c r="L140" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr"/>
+      <c r="B141" t="inlineStr"/>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Leaseweb Singapore</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>https://www.leaseweb.com</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.leaseweb.com/en/contact</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>Multiple Singapore colocation data centres (SIN-01, SIN-12), continued APAC expansion.</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>https://www.leaseweb.com/en/press/releases/significant-momentum-in-singapore-with-continued-apac-expansion</t>
+        </is>
+      </c>
+      <c r="L141" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:16:53+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>EdgeConneX Indonesia</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>https://www.edgeconnex.com/locations/asia-pacific/jakarta/</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.edgeconnex.com/locations/asia-pacific/jakarta/</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>Hyperscale data center campus entry into Jakarta via GTN acquisition</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/edgeconnex-acquires-gtn-in-indonesia/</t>
+        </is>
+      </c>
+      <c r="L142" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr"/>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Gallant Venture Ltd (Bintan Data Center Hub)</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>https://www.gallantventure.com</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr"/>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>http://gallantventure.listedcompany.com/ir_contact.html</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>Gigawatt-scale Bintan data center complex with DCI Indonesia</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>https://www.forbes.com/sites/ardianwibisono/2025/10/27/dci-indonesia-tycoon-anthoni-salims-gallant-venture-building-data-center-hub-near-singapore/</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr"/>
+      <c r="B144" t="inlineStr"/>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>RS Pondok Indah Group</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>https://www.rspondokindah.co.id</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr"/>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.rspondokindah.co.id/en/contact</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>HIMSS EMRAM Stage 7 digital hospital infrastructure buildout</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>https://www.healthcareitnews.com/news/asia/rs-pondok-indah-group-clinches-first-stage-7-emram-indonesia</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr"/>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>PT MNC Land Tbk</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>https://www.mncland.com</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr"/>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.mncland.com/investor</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>Techno Park / data center + AI center development at KEK MNC Lido City</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/mnc-to-build-data-center-in-lido-resort-city-south-of-jakarta-indonesia/</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr"/>
+      <c r="B146" t="inlineStr"/>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Diskominfo Provinsi Jawa Timur</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>https://kominfo.jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr"/>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://kominfo.jatimprov.go.id</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>Provincial government data center serving Pemprov Jatim + 16 district/city governments</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>https://kominfo.jatimprov.go.id/berita/diskominfo-jatim-peroleh-sertifikasi-iso-27001-2022-untuk-data-center</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Otorita Ibu Kota Nusantara (IKN Authority)</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>https://www.ikn.go.id</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.ikn.go.id</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>Nusantara smart city AI/data infrastructure buildout</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>https://konstruksimedia.com/otorita-ikn-dan-ustda-perkuat-kolaborasi-ai-dan-data-untuk-wujudkan-nusantara-sebagai-kota-cerdas/</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr"/>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Universitas Udayana (UCEAI - Pusat Kajian Kecerdasan Artifisial)</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>https://uceai.unud.ac.id</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr"/>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.unud.ac.id/en/contact/</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>Named university AI research center (UCEAI)</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>https://uceai.unud.ac.id/</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr"/>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>BMKG (Badan Meteorologi, Klimatologi, dan Geofisika)</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr"/>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/profil/?p=kontak-kami</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>SMONG supercomputer / HPC cluster for weather and disaster modeling</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>https://www.bmkg.go.id/berita/bmkg-luncurkan-superkomputer-smong-perkuat-sistem-peringatan-dini-multi-hazards</t>
+        </is>
+      </c>
+      <c r="L149" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr"/>
+      <c r="B150" t="inlineStr"/>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>PT Pupuk Indonesia (Persero)</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>https://www.pupuk-indonesia.com</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>0811 1000 1959</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.pupuk-indonesia.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>Data Center / DRC infrastructure and AI-driven smart factory operations</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>https://cloud.google.com/customers/pupuk</t>
+        </is>
+      </c>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Angkasa Pura Sarana Digital (APSD)</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>https://apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://apsdigital.co.id</t>
+        </is>
+      </c>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>Planned airport data center at Soekarno-Hatta</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>https://investor.id/business/314676/angkasa-pura-ii-jajaki-pembangunan-data-center-di-bandara-soekarno-hatta</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr"/>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Badan Informasi Geospasial (BIG)</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>https://www.big.go.id</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr"/>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://big.go.id/site/contact</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>Geospatial data center + HPC-based Integrated Map Production Center</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/409549/big-bangun-data-center-raksasa-geospasial</t>
+        </is>
+      </c>
+      <c r="L152" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr"/>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>PT Bio Farma (Persero)</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>https://www.biofarma.co.id</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr"/>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.biofarma.co.id/en/contact-us</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>Google Cloud AI/ML infrastructure for bioinformatics R&amp;D</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>https://www.biofarma.co.id/en/latest-news/detail/bio-farma-and-google-cloud-indonesia-agree-on-the-mou-for-cooperation-in-healthcare-digital-transformation</t>
+        </is>
+      </c>
+      <c r="L153" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr"/>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Komisi Pemilihan Umum (KPU) Republik Indonesia</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>https://www.kpu.go.id</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr"/>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.kpu.go.id/page/read/1107/kontak-pengaduan</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>Sirekap election data center monitoring infrastructure</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>https://www.kpu.go.id/berita/baca/12716/kpu-siapkan-data-center-pemantauan-sirekap-pilkada</t>
+        </is>
+      </c>
+      <c r="L154" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Kementerian Kesehatan RI (SATUSEHAT)</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>https://satusehat.kemkes.go.id</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>0811-1050-0567</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://satusehat.kemkes.go.id/contact-us/mobile</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>SATUSEHAT national health-data cloud platform</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>https://satusehat.kemkes.go.id/data</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr"/>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>BP Batam (Badan Pengusahaan Batam)</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>https://bpbatam.go.id</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr"/>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://bpbatam.go.id/en/profile/contact-us/</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>Oversight of $5B High-Density AI Data Centre investment in Batam</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>https://ptsp.bpbatam.go.id/en/bp-batam-kawal-investasi-rp88-triliun-ai-data-centre-untuk-transformasi-digital-batam/</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr"/>
+      <c r="B157" t="inlineStr"/>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>PT Freeport Indonesia</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>https://ptfi.co.id</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr"/>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://ptfi.co.id/id/contact</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>Smart mining digitalization with 80% cloud computing adoption and 200+ servers supporting operations (email found, ptfi_communications@fmi.com, did not match ptfi.co.id domain so routed to contact form only)</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>https://www.antaranews.com/berita/4656825/ptfi-tingkatkan-keamanan-tekan-biaya-melalui-teknologi-smart-mining</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr"/>
+      <c r="B158" t="inlineStr"/>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>PT Infokom Elektrindo</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>https://www.infokom.id</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr"/>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.infokom.id</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>Appointed as ICT infrastructure provider (core IT infra, backbone, fiber, data center) for MNC Land's Techno Park at KEK MNC Lido City</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>https://market.bisnis.com/read/20211011/192/1452860/mnc-land-gandeng-infokom-bangun-techno-park-di-kek-mnc-lido-city</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>PT Sinergi Informatika Semen Indonesia (SISI)</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>https://sisi.id</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://sisi.id/about-us/</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>Semen Indonesia Group's ICT subsidiary providing data center, network infrastructure and cloud/managed services for the SIG cement conglomerate</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>https://sisi.id/about-us/</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr"/>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>CoreWeave Indonesia</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>https://www.coreweave.com</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr"/>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>https://www.coreweave.com/news/coreweave-expands-cloud-ai-platform-to-indonesia-marking-first-move-into-asia-pacific-region</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>First APAC expansion: 3 new Indonesia data centers totaling 360MW of contracted IT power, announced by COO Sachin Jain (press@coreweave.com already used for a separate US-market row, so this Indonesia signal is routed to contact-form queue only)</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>https://www.coreweave.com/news/coreweave-expands-cloud-ai-platform-to-indonesia-marking-first-move-into-asia-pacific-region</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr"/>
+      <c r="B161" t="inlineStr"/>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>SM+ (SMX01 Data Center, Sinar Mas-backed)</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>https://smplus.com</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr"/>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>https://smplus.com/about-us/</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>Building SMX01, a US$300M Tier IV AI-ready data center in Jakarta's CBD (18MW scalable to 60MW) with high-density racks and liquid cooling, JV with Korea Investment Real Asset Management</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>https://dssa.co.id/en/press-release/sm-breaks-ground-on-flagship-data-center-in-jakartas-central-business-district-1741262984710</t>
+        </is>
+      </c>
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>2026-09-15T02:17:02+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -7130,28 +7130,24 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L86" t="n">
         <v>1</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>1a0a2dd9886fbd3b</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr"/>
+      <c r="M86" t="inlineStr"/>
+      <c r="N86" t="inlineStr">
+        <is>
+          <t>550 5.1.1 No Such User Here (mailer-daemon, PT MNC Land Tbk)</t>
+        </is>
+      </c>
       <c r="O86" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:20:52+00:00</t>
-        </is>
-      </c>
+      <c r="P86" t="inlineStr"/>
       <c r="Q86" t="inlineStr">
         <is>
           <t>none</t>
@@ -8492,28 +8488,24 @@
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L104" t="n">
         <v>1</v>
       </c>
-      <c r="M104" t="inlineStr">
-        <is>
-          <t>1a0a2de457e92620</t>
-        </is>
-      </c>
-      <c r="N104" t="inlineStr"/>
+      <c r="M104" t="inlineStr"/>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>550 5.4.1 Recipient address rejected: Access denied (mailer-daemon, Mapletree Investments)</t>
+        </is>
+      </c>
       <c r="O104" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P104" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:21:23+00:00</t>
-        </is>
-      </c>
+      <c r="P104" t="inlineStr"/>
       <c r="Q104" t="inlineStr">
         <is>
           <t>none</t>
@@ -8565,28 +8557,24 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L105" t="n">
         <v>1</v>
       </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>1a0a2ddc6ec22fdb</t>
-        </is>
-      </c>
-      <c r="N105" t="inlineStr"/>
+      <c r="M105" t="inlineStr"/>
+      <c r="N105" t="inlineStr">
+        <is>
+          <t>550 5.1.2 DNS Error: domain apsdigital.co.id not found / NXDOMAIN (mailer-daemon, Angkasa Pura Sarana Digital)</t>
+        </is>
+      </c>
       <c r="O105" t="inlineStr">
         <is>
           <t>2026-09-15T02:19:24+00:00</t>
         </is>
       </c>
-      <c r="P105" t="inlineStr">
-        <is>
-          <t>2026-09-15T02:20:52+00:00</t>
-        </is>
-      </c>
+      <c r="P105" t="inlineStr"/>
       <c r="Q105" t="inlineStr">
         <is>
           <t>none</t>
@@ -15556,7 +15544,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr">
         <is>
           <t>Jurong Island Data Centre Park (up to 700MW), liquid/seawater cooling testbed with NUS.</t>
@@ -15598,7 +15590,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>$24B advanced wafer fab + $7B HBM packaging facility investment in Singapore.</t>
@@ -15640,7 +15636,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J133" t="inlineStr">
         <is>
           <t>$6.7-7.8B 300mm wafer fab JV under construction in Tampines, Singapore.</t>
@@ -15682,7 +15682,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I134" t="inlineStr"/>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr">
         <is>
           <t>Advanced packaging/plasma-dicing capacity expansion at Singapore facility.</t>
@@ -15724,7 +15728,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr">
         <is>
           <t>Tier 3+ facility with N+2 cooling redundancy in Singapore.</t>
@@ -15766,7 +15774,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I136" t="inlineStr"/>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr">
         <is>
           <t>S$1.4B acquisition expanding high-density Singapore data-centre portfolio.</t>
@@ -15808,7 +15820,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I137" t="inlineStr"/>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J137" t="inlineStr">
         <is>
           <t>Develops/owns purpose-built high-tech data centres in Singapore.</t>
@@ -15850,7 +15866,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr"/>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr">
         <is>
           <t>SGX 'Reach' initiative: $250M world-class low-latency data centre for its own trading infrastructure.</t>
@@ -15892,7 +15912,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I139" t="inlineStr"/>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>Oracle Cloud Isolated Region for MINDEF/SAF sovereign cloud/AI infrastructure.</t>
@@ -15934,7 +15958,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I140" t="inlineStr"/>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J140" t="inlineStr">
         <is>
           <t>NGINE AI compute infrastructure for LLM training/modelling/simulation at scale.</t>
@@ -15976,7 +16004,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr">
         <is>
           <t>Multiple Singapore colocation data centres (SIN-01, SIN-12), continued APAC expansion.</t>
@@ -16060,7 +16092,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J143" t="inlineStr">
         <is>
           <t>Gigawatt-scale Bintan data center complex with DCI Indonesia</t>
@@ -16102,7 +16138,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I144" t="inlineStr"/>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J144" t="inlineStr">
         <is>
           <t>HIMSS EMRAM Stage 7 digital hospital infrastructure buildout</t>
@@ -16144,7 +16184,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I145" t="inlineStr"/>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J145" t="inlineStr">
         <is>
           <t>Techno Park / data center + AI center development at KEK MNC Lido City</t>
@@ -16186,7 +16230,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I146" t="inlineStr"/>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J146" t="inlineStr">
         <is>
           <t>Provincial government data center serving Pemprov Jatim + 16 district/city governments</t>
@@ -16228,7 +16276,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr"/>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr">
         <is>
           <t>Nusantara smart city AI/data infrastructure buildout</t>
@@ -16270,7 +16322,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J148" t="inlineStr">
         <is>
           <t>Named university AI research center (UCEAI)</t>
@@ -16312,7 +16368,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I149" t="inlineStr"/>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J149" t="inlineStr">
         <is>
           <t>SMONG supercomputer / HPC cluster for weather and disaster modeling</t>
@@ -16358,7 +16418,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I150" t="inlineStr"/>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J150" t="inlineStr">
         <is>
           <t>Data Center / DRC infrastructure and AI-driven smart factory operations</t>
@@ -16400,7 +16464,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr"/>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J151" t="inlineStr">
         <is>
           <t>Planned airport data center at Soekarno-Hatta</t>
@@ -16442,7 +16510,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I152" t="inlineStr"/>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J152" t="inlineStr">
         <is>
           <t>Geospatial data center + HPC-based Integrated Map Production Center</t>
@@ -16484,7 +16556,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J153" t="inlineStr">
         <is>
           <t>Google Cloud AI/ML infrastructure for bioinformatics R&amp;D</t>
@@ -16526,7 +16602,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr">
         <is>
           <t>Sirekap election data center monitoring infrastructure</t>
@@ -16572,7 +16652,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr">
         <is>
           <t>SATUSEHAT national health-data cloud platform</t>
@@ -16614,7 +16698,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr">
         <is>
           <t>Oversight of $5B High-Density AI Data Centre investment in Batam</t>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U117"/>
+  <dimension ref="A1:U119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8900,39 +8900,35 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
+          <t>bd@aseglobal.com.sg</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr"/>
       <c r="C110" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Business Development</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>ASE Singapore Pte Ltd</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.aseglobal.com.sg</t>
         </is>
       </c>
       <c r="F110" t="inlineStr"/>
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.digitimes.com/news/a20250519PD208/ase-singapore-testing-investment-siph.html — ASE is expanding and reinventing its Singapore chip-testing operations, investing in silicon photonics and co-packaged optics (CPO) test capability, positioning its Singapore site within Southeast Asia's AI data-center supply chain</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -8942,16 +8938,28 @@
       </c>
       <c r="K110" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L110" t="n">
-        <v>0</v>
-      </c>
-      <c r="M110" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>1a0a801752096178</t>
+        </is>
+      </c>
       <c r="N110" t="inlineStr"/>
-      <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:47+00:00</t>
+        </is>
+      </c>
       <c r="Q110" t="inlineStr">
         <is>
           <t>none</t>
@@ -8969,39 +8977,39 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>media@esr.com</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Philemon Foo</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Group Communications Manager, ESR</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>ESR Group</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.esr.com</t>
         </is>
       </c>
       <c r="F111" t="inlineStr"/>
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.esr.com/news/esr-appoints-dalmar-sheikh-ceo-data-centres/ — ESR appointed Dalmar Sheikh as CEO of ESR Data Centres (effective 1 Sept 2026), based in Singapore, to lead the group's data centre platform, which carries a pipeline of more than 3.2GW across major Asia-Pacific markets amid rising hyperscaler and enterprise AI demand</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
@@ -9011,16 +9019,28 @@
       </c>
       <c r="K111" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L111" t="n">
-        <v>0</v>
-      </c>
-      <c r="M111" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>1a0a8016ebbaec1e</t>
+        </is>
+      </c>
       <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
-      <c r="P111" t="inlineStr"/>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:36+00:00</t>
+        </is>
+      </c>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:17:47+00:00</t>
+        </is>
+      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>none</t>
@@ -9038,12 +9058,12 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>info@colovore.com</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Jeffrey Springborn</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -9053,12 +9073,12 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
@@ -9070,7 +9090,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9107,27 +9127,39 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr"/>
-      <c r="C113" t="inlineStr"/>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Nscale</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://nscale.com</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
-      <c r="H113" t="inlineStr"/>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9164,12 +9196,12 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>press@coreweave.com</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Michael Intrator</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -9179,12 +9211,12 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://coreweave.com</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
@@ -9196,7 +9228,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9233,39 +9265,27 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Don MacNeil</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Chief Revenue Officer</t>
-        </is>
-      </c>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr"/>
+      <c r="C115" t="inlineStr"/>
       <c r="D115" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://deepinfra.com</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="H115" t="inlineStr"/>
       <c r="I115" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9302,12 +9322,12 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>hello@edgemode.io</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Charlie Faulkner</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -9317,12 +9337,12 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>EdgeMode Inc.</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://edgemode.io</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
@@ -9334,7 +9354,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9371,27 +9391,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>press@edgeconnex.com</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Don MacNeil</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>Chief Revenue Officer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>EdgeConneX</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://edgeconnex.com</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -9403,7 +9423,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9436,6 +9456,144 @@
       </c>
       <c r="T117" t="inlineStr"/>
       <c r="U117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr"/>
+      <c r="G118" t="inlineStr"/>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J118" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K118" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L118" t="n">
+        <v>0</v>
+      </c>
+      <c r="M118" t="inlineStr"/>
+      <c r="N118" t="inlineStr"/>
+      <c r="O118" t="inlineStr"/>
+      <c r="P118" t="inlineStr"/>
+      <c r="Q118" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R118" t="inlineStr"/>
+      <c r="S118" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T118" t="inlineStr"/>
+      <c r="U118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr"/>
+      <c r="G119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K119" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L119" t="n">
+        <v>0</v>
+      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
+      <c r="O119" t="inlineStr"/>
+      <c r="P119" t="inlineStr"/>
+      <c r="Q119" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R119" t="inlineStr"/>
+      <c r="S119" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T119" t="inlineStr"/>
+      <c r="U119" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9448,7 +9606,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L161"/>
+  <dimension ref="A1:L165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16926,6 +17084,174 @@
       <c r="L161" t="inlineStr">
         <is>
           <t>2026-09-15T02:17:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr"/>
+      <c r="B162" t="inlineStr"/>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>ESR Group</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>https://www.esr.com</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr"/>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>https://www.esr.com/connect-with-us/</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>ESR appointed Dalmar Sheikh as CEO of ESR Data Centres (Singapore-based), leading a &gt;3.2GW APAC data-centre development pipeline amid hyperscaler/enterprise AI demand</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>https://www.esr.com/news/esr-appoints-dalmar-sheikh-ceo-data-centres/</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:13:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Applied Materials (Singapore)</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>https://www.appliedmaterials.com/sg/en</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>https://www.appliedmaterials.com/sg/en/contact.html</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>Opened a US$500M Tampines campus in Singapore more than doubling advanced cleanroom capacity for AI-chip manufacturing, with power/performance/thermal complexity cited as a customer focus</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>https://www.theedgesingapore.com/digitaledge/semiconductor/applied-materials-opens-new-us500-mil-facility-singapore-ai-chip-demand</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:13:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr"/>
+      <c r="B164" t="inlineStr"/>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>ASE Singapore Pte Ltd</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>https://www.aseglobal.com.sg</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr"/>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>https://www.aseglobal.com.sg/index.php/contact-us/</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>ASE Singapore expanding chip-testing operations and investing in silicon photonics/co-packaged optics (CPO) test capability for AI hardware, positioning the site within SE Asia's AI data-centre supply chain</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20250519PD208/ase-singapore-testing-investment-siph.html</t>
+        </is>
+      </c>
+      <c r="L164" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:13:11+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr"/>
+      <c r="B165" t="inlineStr"/>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Nusantara Data Center (NDC)</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>https://nusantaradatacenter.com</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr"/>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>http://nusantaradatacenter.com/contact-page/</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>Operates Indonesia's largest open-network, carrier-neutral colocation platform with 8 data centers across 6 cities (Batam, Jakarta, Medan, Palembang, Surabaya, Bali), Tier II/III (TIA-942 Rated 3) certified facilities with 99.98% SLA -- a multi-site physical colocation operator with an ongoing cooling/facilities need across its network</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>https://nusantaradatacenter.com/about-ndc.html</t>
+        </is>
+      </c>
+      <c r="L165" t="inlineStr">
+        <is>
+          <t>2026-09-16T02:16:29+00:00</t>
         </is>
       </c>
     </row>
@@ -16940,7 +17266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17221,6 +17547,44 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Applied Materials (Singapore)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>media_relations@amat.com</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theedgesingapore.com/digitaledge/semiconductor/applied-materials-opens-new-us500-mil-facility-singapore-ai-chip-demand — Opened a US$500M Tampines manufacturing and R&amp;D campus in Singapore that more than doubles the company advanced cleanroom capacity to meet surging AI-chip demand, deploying autonomous mobile robots and AI-assisted quality inspection amid rising power/performance and thermal complexity of AI chip architectures</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Email domain (amat.com) does not match the company Website field recorded (appliedmaterials.com/sg/en). Both domains have real, distinctly-hosted, professionally-managed mail servers (amat.com via Proofpoint, appliedmaterials.com via Google Workspace) so neither looks like a parked/guessed domain, and AMAT is publicly known as Applied Materials stock ticker -- but the source (theedgesingapore.com) is third-party and does not itself confirm amat.com belongs to Applied Materials, and WebFetch access to a first-party Applied Materials page to confirm directly is blocked this session. Same near-miss-domain pattern flagged before (Telkomsel, Kredivo, Bank OCBC NISP) and applied consistently rather than trusting general knowledge over verifiable sourcing.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -6733,28 +6733,24 @@
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L81" t="n">
         <v>1</v>
       </c>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>1a09d4f5a0396323</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr"/>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr">
+        <is>
+          <t>SMTP 4.4.1: The recipient server did not accept our requests to connect (bd-dc.com timed out on all MX hosts); Gmail gave up after retrying, final DSN Action: failed, Last-Attempt-Date Wed 16 Sep 2026 21:16:49 -0700</t>
+        </is>
+      </c>
       <c r="O81" t="inlineStr">
         <is>
           <t>2026-09-14T00:25:16+00:00</t>
         </is>
       </c>
-      <c r="P81" t="inlineStr">
-        <is>
-          <t>2026-09-14T00:27:10+00:00</t>
-        </is>
-      </c>
+      <c r="P81" t="inlineStr"/>
       <c r="Q81" t="inlineStr">
         <is>
           <t>none</t>
@@ -9606,7 +9602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L165"/>
+  <dimension ref="A1:L167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17112,7 +17108,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I162" t="inlineStr"/>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>Attempted 2026-09-16T02:xx: browser navigation blocked by this session's network egress policy. Confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403 for the target host itself (www.esr.com / www.aseglobal.com.sg / nusantaradatacenter.com respectively), and proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.google.com moments earlier -- confirming a session-wide policy block, not a site-specific issue, consistent with every prior</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr">
         <is>
           <t>ESR appointed Dalmar Sheikh as CEO of ESR Data Centres (Singapore-based), leading a &gt;3.2GW APAC data-centre development pipeline amid hyperscaler/enterprise AI demand</t>
@@ -17196,7 +17196,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I164" t="inlineStr"/>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>Attempted 2026-09-16T02:xx: browser navigation blocked by this session's network egress policy. Confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403 for the target host itself (www.esr.com / www.aseglobal.com.sg / nusantaradatacenter.com respectively), and proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.google.com moments earlier -- confirming a session-wide policy block, not a site-specific issue, consistent with every prior</t>
+        </is>
+      </c>
       <c r="J164" t="inlineStr">
         <is>
           <t>ASE Singapore expanding chip-testing operations and investing in silicon photonics/co-packaged optics (CPO) test capability for AI hardware, positioning the site within SE Asia's AI data-centre supply chain</t>
@@ -17238,7 +17242,11 @@
           <t>pending</t>
         </is>
       </c>
-      <c r="I165" t="inlineStr"/>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>Attempted 2026-09-16T02:xx: browser navigation blocked by this session's network egress policy. Confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403 for the target host itself (www.esr.com / www.aseglobal.com.sg / nusantaradatacenter.com respectively), and proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.google.com moments earlier -- confirming a session-wide policy block, not a site-specific issue, consistent with every prior</t>
+        </is>
+      </c>
       <c r="J165" t="inlineStr">
         <is>
           <t>Operates Indonesia's largest open-network, carrier-neutral colocation platform with 8 data centers across 6 cities (Batam, Jakarta, Medan, Palembang, Surabaya, Bali), Tier II/III (TIA-942 Rated 3) certified facilities with 99.98% SLA -- a multi-site physical colocation operator with an ongoing cooling/facilities need across its network</t>
@@ -17252,6 +17260,90 @@
       <c r="L165" t="inlineStr">
         <is>
           <t>2026-09-16T02:16:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr"/>
+      <c r="B166" t="inlineStr"/>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>ST Engineering (Singapore Technologies Engineering Ltd)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>https://www.stengg.com</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr"/>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>https://www.stengg.com/en/contact/</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>ST Engineering data centre at Jalan Boon Lay (7.5MW, opening 2026, S$120M investment) built for &gt;20kW/rack AI/GPU workloads with Airbitat DC Cooling System, liquid cooling and immersion cooling, PUE target 1.25.</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>https://www.stengg.com/en/newsroom/news-releases/st-engineering-breaks-ground-on-new-data-centre/</t>
+        </is>
+      </c>
+      <c r="L166" t="inlineStr">
+        <is>
+          <t>2026-09-17T02:10:23+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr"/>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Polibeli Group Ltd</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>https://www.polibeli.id</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr"/>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>https://m.polibeli.id/contactus</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>Signed non-binding MOU (July 15, 2026) with PT Grosirone Prima Nusantara to jointly evaluate a potential AI data center in Indonesia (up to 10MW, initial phase 2-5MW); evaluation scope explicitly includes power availability, cooling systems, and network connectivity feasibility.</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>https://www.globenewswire.com/news-release/2026/07/15/3327699/0/en/polibeli-signs-non-binding-mou-to-evaluate-potential-ai-data-center-opportunity-in-indonesia.html</t>
+        </is>
+      </c>
+      <c r="L167" t="inlineStr">
+        <is>
+          <t>2026-09-17T02:10:24+00:00</t>
         </is>
       </c>
     </row>
@@ -17266,7 +17358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17585,6 +17677,44 @@
         </is>
       </c>
     </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Corporate Communications / Media Relations</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ST Engineering (Singapore Technologies Engineering Ltd)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>news@stengg.com</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stengg.com/en/newsroom/news-releases/st-engineering-breaks-ground-on-new-data-centre/ — ST Engineering broke ground on its fourth Singapore data centre (Jalan Boon Lay, S$120M investment, 7.5MW, opening 2026), deploying its own proprietary Airbitat DC Cooling System alongside liquid and immersion cooling, targeting PUE 1.25</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Not a data-integrity issue (email is real, domain-matched, verified) -- a targeting/fit issue: ST Engineering manufactures and sells its own Airbitat DC Cooling System, and this exact facility already deploys it as the primary cooling solution. An earlier Singapore batch (day 2) explicitly rejected ST Engineering for the same reason ("sells its own cooling system -- a vendor, not a buyer"). Pitching Borealis cooling systems to a company that makes and has already deployed a competing in-house product at the facility in question is a near-certain wasted send, so held out of the sendable pool despite passing every fabrication check.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U119"/>
+  <dimension ref="A1:U120"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9054,39 +9054,35 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
+          <t>sales@gorilla-technology.com</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr"/>
       <c r="C112" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Sales</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>Gorilla Technology Group</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.gorilla-technology.com</t>
         </is>
       </c>
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/gorilla-technology-secures-25bn-gpuaas-contract-in-indonesia/ — Signed a transformational US$2.5B, 5-year AI GPUaaS compute contract anchored at NeutraDC's Batam, Indonesia data center; first phase (~1,000 NVIDIA B300 GPU servers) targets deployment in September 2026, a high-density GPU buildout requiring serious thermal management</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9096,16 +9092,28 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
-      </c>
-      <c r="M112" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M112" t="inlineStr">
+        <is>
+          <t>1a0c34a3062b0171</t>
+        </is>
+      </c>
       <c r="N112" t="inlineStr"/>
-      <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:26:42+00:00</t>
+        </is>
+      </c>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:26:59+00:00</t>
+        </is>
+      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>none</t>
@@ -9123,39 +9131,39 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>info@colovore.com</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Jeffrey Springborn</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>US</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9192,39 +9200,39 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>press@nscale.com</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Nidhi Chappell</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>President, AI Infrastructure</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Nscale</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://nscale.com</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9261,27 +9269,39 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr"/>
-      <c r="C115" t="inlineStr"/>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://coreweave.com</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
-      <c r="H115" t="inlineStr"/>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9318,39 +9338,27 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Charlie Faulkner</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr"/>
+      <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://deepinfra.com</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="H116" t="inlineStr"/>
       <c r="I116" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9387,27 +9395,27 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>hello@edgemode.io</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Charlie Faulkner</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>EdgeMode Inc.</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://edgemode.io</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
@@ -9419,7 +9427,7 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9456,27 +9464,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>press@edgeconnex.com</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Don MacNeil</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Chief Revenue Officer</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>EdgeConneX</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://edgeconnex.com</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -9488,7 +9496,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9525,27 +9533,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>press@fluidstack.io</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Gary Wu</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Fluidstack</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://fluidstack.io</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
@@ -9557,7 +9565,7 @@
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9590,6 +9598,75 @@
       </c>
       <c r="T119" t="inlineStr"/>
       <c r="U119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K120" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L120" t="n">
+        <v>0</v>
+      </c>
+      <c r="M120" t="inlineStr"/>
+      <c r="N120" t="inlineStr"/>
+      <c r="O120" t="inlineStr"/>
+      <c r="P120" t="inlineStr"/>
+      <c r="Q120" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T120" t="inlineStr"/>
+      <c r="U120" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9602,7 +9679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L167"/>
+  <dimension ref="A1:L168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17344,6 +17421,48 @@
       <c r="L167" t="inlineStr">
         <is>
           <t>2026-09-17T02:10:24+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr"/>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Gorilla Technology Group</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>https://www.gorilla-technology.com</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr"/>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>https://www.gorilla-technology.com/about-us/contact/</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Signed a transformational US$2.5B, 5-year AI GPUaaS compute contract anchored at NeutraDC's Batam, Indonesia data center; first phase (~1,000 NVIDIA B300 GPU servers) targets deployment September 2026</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/gorilla-technology-secures-25bn-gpuaas-contract-in-indonesia/</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:25:13+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U120"/>
+  <dimension ref="A1:U123"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9131,39 +9131,31 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>business@balifiber.id</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr"/>
+      <c r="C113" t="inlineStr"/>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>PT Bali Towerindo Sentra Tbk (Balitower / Balifiber Data Center)</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.balifiber.id</t>
         </is>
       </c>
       <c r="F113" t="inlineStr"/>
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.balifiber.id/home/bt_datacenter ; cross-checked via https://tiaonline.org/942-datacenter/pt-bali-towerindo-sentra-tbk-bali-tower-sentra-data-center-jl-batu-ceper-no-53-kebon-kelapa-gambir-jakarta-pusat-10120/ and https://www.idnfinancials.com/archive/45596/bali-towerindo-sentra-reinforce-data-centre-cctv-business — IDX-listed tower/infrastructure operator (BALI) runs Balitower/Balifiber Data Center in Jakarta Pusat, a TIA-942 Rated 3 certified facility that has expanded</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9173,16 +9165,28 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L113" t="n">
-        <v>0</v>
-      </c>
-      <c r="M113" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>1a0c6dfee1d86767</t>
+        </is>
+      </c>
       <c r="N113" t="inlineStr"/>
-      <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
       <c r="Q113" t="inlineStr">
         <is>
           <t>none</t>
@@ -9200,39 +9204,39 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>ir@gds-services.com</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Laura Chen</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Investor Relations, GDS Holdings Limited</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>GDS International (GDS Holdings)</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.gds-services.com</t>
         </is>
       </c>
       <c r="F114" t="inlineStr"/>
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/gds-acquires-singapore-warehouse-plans-data-center-redevelopment/ — GDS International (CEO Jamie Khoo) acquired a S$112.8M / 39,978 sqm site at 21 Jalan Buroh, Jurong East, Singapore for a new hyperscale data center, part of an 80MW EDB/IMDA capacity award shared with Equinix, Microsoft and AirTrunk</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9242,16 +9246,28 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L114" t="n">
-        <v>0</v>
-      </c>
-      <c r="M114" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M114" t="inlineStr">
+        <is>
+          <t>1a0c6dfe66d4f732</t>
+        </is>
+      </c>
       <c r="N114" t="inlineStr"/>
-      <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
       <c r="Q114" t="inlineStr">
         <is>
           <t>none</t>
@@ -9269,39 +9285,39 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>junhong@nus.edu.sg</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Wang Junhong</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Senior Manager (HPC-AI), NUS Information Technology</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>NUS IT (High Performance Computing)</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://nusit.nus.edu.sg/hpc/</t>
         </is>
       </c>
       <c r="F115" t="inlineStr"/>
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://nusit.nus.edu.sg/hpc/wang-jun-hong (cross-checked via independent WebSearch query returning the same address, per this session's WebFetch-egress-blocked fallback protocol) — Named Senior Manager for NUS's centralized HPC-AI computing infrastructure (multi-core clusters, GPU accelerators) supporting compute-intensive research workloads across NUS -- a facilities/technical-operations-tier contact, not the general IT helpdesk inbox already on file</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9311,16 +9327,28 @@
       </c>
       <c r="K115" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L115" t="n">
-        <v>0</v>
-      </c>
-      <c r="M115" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M115" t="inlineStr">
+        <is>
+          <t>1a0c6dfdf93c8b16</t>
+        </is>
+      </c>
       <c r="N115" t="inlineStr"/>
-      <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
+      <c r="O115" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:08:54+00:00</t>
+        </is>
+      </c>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>2026-09-22T02:09:24+00:00</t>
+        </is>
+      </c>
       <c r="Q115" t="inlineStr">
         <is>
           <t>none</t>
@@ -9338,27 +9366,39 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr"/>
-      <c r="C116" t="inlineStr"/>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
-      <c r="H116" t="inlineStr"/>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9395,39 +9435,39 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>press@nscale.com</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Nidhi Chappell</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>President, AI Infrastructure</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Nscale</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://nscale.com</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9464,27 +9504,27 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>press@coreweave.com</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Michael Intrator</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://coreweave.com</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
@@ -9496,7 +9536,7 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9533,39 +9573,27 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Gary Wu</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr"/>
+      <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>DeepInfra</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://deepinfra.com</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
+      <c r="H119" t="inlineStr"/>
       <c r="I119" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9602,27 +9630,27 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>hello@edgemode.io</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Charlie Faulkner</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>EdgeMode Inc.</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://edgemode.io</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
@@ -9634,7 +9662,7 @@
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -9667,6 +9695,213 @@
       </c>
       <c r="T120" t="inlineStr"/>
       <c r="U120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J121" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K121" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L121" t="n">
+        <v>0</v>
+      </c>
+      <c r="M121" t="inlineStr"/>
+      <c r="N121" t="inlineStr"/>
+      <c r="O121" t="inlineStr"/>
+      <c r="P121" t="inlineStr"/>
+      <c r="Q121" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T121" t="inlineStr"/>
+      <c r="U121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr"/>
+      <c r="G122" t="inlineStr"/>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J122" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K122" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L122" t="n">
+        <v>0</v>
+      </c>
+      <c r="M122" t="inlineStr"/>
+      <c r="N122" t="inlineStr"/>
+      <c r="O122" t="inlineStr"/>
+      <c r="P122" t="inlineStr"/>
+      <c r="Q122" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R122" t="inlineStr"/>
+      <c r="S122" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T122" t="inlineStr"/>
+      <c r="U122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J123" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K123" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L123" t="n">
+        <v>0</v>
+      </c>
+      <c r="M123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
+      <c r="O123" t="inlineStr"/>
+      <c r="P123" t="inlineStr"/>
+      <c r="Q123" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R123" t="inlineStr"/>
+      <c r="S123" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T123" t="inlineStr"/>
+      <c r="U123" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9679,7 +9914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:L170"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17446,23 +17681,119 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>2026-09-21: dual-channel contact-form attempt for Gorilla Technology Group (paired with today's real email to sales@gorilla-technology.com) blocked before fill was attempted -- this session's network egress policy rejects the CONNECT to www.gorilla-technology.com:443 with 403 (confirmed via curl and via /__agentproxy/status recentRelayFailures, same root cause as every other blocked batch this campaign). No fill was faked; row left for retry from an unrestricted session or manual visit.</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>Signed a transformational US$2.5B, 5-year AI GPUaaS compute contract anchored at NeutraDC's Batam, Indonesia data center; first phase (~1,000 NVIDIA B300 GPU servers) targets deployment September 2026</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/gorilla-technology-secures-25bn-gpuaas-contract-in-indonesia/</t>
+        </is>
+      </c>
+      <c r="L168" t="inlineStr">
+        <is>
+          <t>2026-09-21T09:25:13+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Stanley Go</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Operations Manager (BCxP - ASHRAE-certified Building Commissioning Professional)</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Digital Hyperspace Indonesia (DHI)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>https://dh-indonesia.com</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr"/>
+      <c r="F169" t="inlineStr"/>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>https://dh-indonesia.com/contact/</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
           <t>pending</t>
         </is>
       </c>
-      <c r="I168" t="inlineStr"/>
-      <c r="J168" t="inlineStr">
-        <is>
-          <t>Signed a transformational US$2.5B, 5-year AI GPUaaS compute contract anchored at NeutraDC's Batam, Indonesia data center; first phase (~1,000 NVIDIA B300 GPU servers) targets deployment September 2026</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>https://www.datacenterdynamics.com/en/news/gorilla-technology-secures-25bn-gpuaas-contract-in-indonesia/</t>
-        </is>
-      </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>2026-09-21T09:25:13+00:00</t>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>Tier III (Uptime Institute) 20MW greenfield hyperscale data center in Cikarang/Jakarta with 2N UPS redundancy and N+1 cooling infrastructure, expandable to 80MW on a 68,000 sqm campus (GTC Fund/China Telecom-backed); Operations Manager Stanley Go holds ASHRAE BCxP (building/mechanical commissioning) credential, a real facilities-engineering signal.</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>https://uptimeinstitute.com/component/tierachievement/datacenter/digital-hyperspace-jkt1a/1913 ; cross-checked via https://baxtel.com/data-center/digital-hyperspace-jakarta and https://datacenterhawk.com/marketplace/providers/digital-hyperspace/pasirranji-central-cikarang-bekasi-regency-west-java-indonesia/dhi</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>2026-09-21T10:46:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr"/>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>PT Bali Towerindo Sentra Tbk (Balitower / Balifiber Data Center)</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>https://www.balitower.co.id</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr"/>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>https://www.balitower.co.id/contact</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>TIA-942 Rated 3 certified Balitower/Balifiber Data Center in Jakarta Pusat, expanding colocation capacity beyond original NOC use; actively hiring Data Center Engineers.</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>https://www.balifiber.id/home/bt_datacenter ; https://tiaonline.org/942-datacenter/pt-bali-towerindo-sentra-tbk-bali-tower-sentra-data-center-jl-batu-ceper-no-53-kebon-kelapa-gambir-jakarta-pusat-10120/</t>
+        </is>
+      </c>
+      <c r="L170" t="inlineStr">
+        <is>
+          <t>2026-09-21T10:52:42+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -9165,28 +9165,24 @@
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L113" t="n">
         <v>1</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>1a0c6dfee1d86767</t>
-        </is>
-      </c>
-      <c r="N113" t="inlineStr"/>
+      <c r="M113" t="inlineStr"/>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>550 5.1.1 &lt;business@balifiber.id&gt;: Recipient address rejected: balifiber.id (mailer-daemon, 2026-09-22)</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr">
         <is>
           <t>2026-09-22T02:08:54+00:00</t>
         </is>
       </c>
-      <c r="P113" t="inlineStr">
-        <is>
-          <t>2026-09-22T02:09:24+00:00</t>
-        </is>
-      </c>
+      <c r="P113" t="inlineStr"/>
       <c r="Q113" t="inlineStr">
         <is>
           <t>none</t>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U123"/>
+  <dimension ref="A1:U132"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9362,39 +9362,39 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
+          <t>ad_wibawa@its.ac.id</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Jeffrey Springborn</t>
+          <t>Prof. Dr. Ir. Adhi Dharma Wibawa, S.T., M.T.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Head (Kepala Pusat), Center of AI and Digital Technology (AIDT/KATD)</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>ITS</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.its.ac.id/katd/</t>
         </is>
       </c>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.its.ac.id/katd/en/prof-dr-ir-adhi-dharma-wibawa-s-t-m-t/ ; cross-checked via a second independently-worded WebSearch query confirming ad_wibawa@its.ac.id appears on the AIDT/KATD centers own webinar content pages (per WebFetch-egress-blocked fallback protocol) -- Head of the ITS center that itself operates the NVIDIA DGX-A100 AI supercomputer cited in the existing ITS prospects.csv row (https://www.its.ac.id/komputer/id/launching-nvidia-dgx-a100-artificial-intelligence-</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9404,16 +9404,28 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L116" t="n">
-        <v>0</v>
-      </c>
-      <c r="M116" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d60f76f22a</t>
+        </is>
+      </c>
       <c r="N116" t="inlineStr"/>
-      <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
+      <c r="O116" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
       <c r="Q116" t="inlineStr">
         <is>
           <t>none</t>
@@ -9431,39 +9443,39 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>jacqueline_poh@jtc.gov.sg</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Jacqueline Poh</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>JTC Corporation</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.jtc.gov.sg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.mingtiandi.com/real-estate/data-centres/singapore-plans-700mw-data-centre-park-on-jurong-island/ — JTC set aside 20 hectares on Jurong Island for Singapore's largest low-carbon Data Centre Park (up to 700MW); CEO Jacqueline Poh personally quoted on the project as JTC's bold step to build infrastructure for this new low-carbon data-centre hub</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9473,16 +9485,28 @@
       </c>
       <c r="K117" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L117" t="n">
-        <v>0</v>
-      </c>
-      <c r="M117" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d6c7aa1d75</t>
+        </is>
+      </c>
       <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>none</t>
@@ -9500,39 +9524,39 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>mardhani@ugm.ac.id</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Dr. Mardhani Riasetiawan</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Head of Digital Transformation Bureau (Kepala Biro Transformasi Digital)</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Universitas Gadjah Mada</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://ugm.ac.id</t>
         </is>
       </c>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://ugm.ac.id/en/news/ugm-partners-with-nvidia-and-indosat-to-advance-ai-research/ ; cross-checked via https://acadstaff.ugm.ac.id/mardhaniriasetiawan and https://mardhani.staff.ugm.ac.id/ (per WebFetch-egress-blocked fallback protocol, two independently-worded WebSearch queries both returned mardhani@ugm.ac.id) — Coordinated the UGM Indosat NVIDIA AI Technology Center launch (NVIDIA DGX Station AI supercomputer at Faculty of Engineering/Faculty of Mathematics and Natural Scien</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
@@ -9542,16 +9566,28 @@
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L118" t="n">
-        <v>0</v>
-      </c>
-      <c r="M118" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d59d1eafe3</t>
+        </is>
+      </c>
       <c r="N118" t="inlineStr"/>
-      <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
+      <c r="O118" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
       <c r="Q118" t="inlineStr">
         <is>
           <t>none</t>
@@ -9569,27 +9605,35 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>media@bridgedatacentres.com</t>
         </is>
       </c>
       <c r="B119" t="inlineStr"/>
-      <c r="C119" t="inlineStr"/>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Media Enquiries</t>
+        </is>
+      </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Bridge Data Centres</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.bridgedatacentres.com</t>
         </is>
       </c>
       <c r="F119" t="inlineStr"/>
       <c r="G119" t="inlineStr"/>
-      <c r="H119" t="inlineStr"/>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t xml:space="preserve">web_research: https://www.datacenterdynamics.com/en/news/bridge-data-centres-plans-to-invest-23bn-4bn-in-singapores-digital-infrastructure/ — CEO Eric Fan stated Bridge Data Centres plans to invest up to S$5B (~US$3.9B) in Singapore AI infrastructure, with research programs and facilities tied to advanced power architectures, next-generation cooling systems, AI-enabled operations, and energy optimization for high-density computing (cross-checked via Bloomberg and Mingtiandi coverage of the same </t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9599,16 +9643,28 @@
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L119" t="n">
-        <v>0</v>
-      </c>
-      <c r="M119" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M119" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d66a738f75</t>
+        </is>
+      </c>
       <c r="N119" t="inlineStr"/>
-      <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
+      <c r="O119" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>none</t>
@@ -9626,39 +9682,39 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>phoebe.ewe@empyriondigital.com</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Phoebe Ewe</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>VP, Marketing &amp; Communications</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Empyrion Digital</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://empyriondigital.com</t>
         </is>
       </c>
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://empyriondigital.com/quantum-safe-and-ai-ready-empyrion-digitals-singapore-hub-expands-local-footprint-with-over-s1-1-billion-investment/ — Empyrion Digital (Singapore-HQ'd) investing over S$1.1B to expand Singapore data-centre capacity for high-density AI/cloud workloads; SG1 facility targets PUE below 1.20 and Green Mark Platinum certification; Phoebe Ewe is the named press contact on the company's own Singapore and Taiwan groundbreaking release boilerplate</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -9668,16 +9724,28 @@
       </c>
       <c r="K120" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L120" t="n">
-        <v>0</v>
-      </c>
-      <c r="M120" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc0d739efeb23</t>
+        </is>
+      </c>
       <c r="N120" t="inlineStr"/>
-      <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
+      <c r="O120" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:16:46+00:00</t>
+        </is>
+      </c>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:17:13+00:00</t>
+        </is>
+      </c>
       <c r="Q120" t="inlineStr">
         <is>
           <t>none</t>
@@ -9695,39 +9763,39 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>fariz@ui.ac.id</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Fariz Darari, S.Kom., M.Sc., Ph.D.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>Faculty in Charge, Tokopedia-UI AI Center of Excellence</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Universitas Indonesia - Fasilkom (Tokopedia-UI AI Center)</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://tokopedia-ai.cs.ui.ac.id</t>
         </is>
       </c>
       <c r="F121" t="inlineStr"/>
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://cs.ui.ac.id/personnel/fariz-darari/ ; cross-checked via a second independently-worded WebSearch query returning the same fariz@ui.ac.id address consistently (per this session's WebFetch-egress-blocked fallback protocol) — Faculty lead at the Tokopedia-UI AI Center of Excellence, Indonesia's first AI development center, built around an NVIDIA DGX-1 deep-learning supercomputer hosted at Fasilkom UI -- a named, domain-matched (ui.ac.id) technical contact for a company already</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -9737,16 +9805,28 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L121" t="n">
-        <v>0</v>
-      </c>
-      <c r="M121" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc179ddc13238</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
-      <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
+      <c r="O121" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:17+00:00</t>
+        </is>
+      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>none</t>
@@ -9764,39 +9844,35 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Gary Wu</t>
-        </is>
-      </c>
+          <t>info@worldvueribyond.com</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr"/>
       <c r="C122" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>General Enquiries</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>WorldVuer iByond (Quantum AI Data Center, Batam)</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://www.worldvueribyond.com</t>
         </is>
       </c>
       <c r="F122" t="inlineStr"/>
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://bkpm.go.id/id/info/siaran-pers/ri-siap-fasilitasi-investasi-data-center-ai-pertama-di-asia-senilai-rp6-t ; cross-checked via https://kepri.antaranews.com/berita/228541/bkpm-fasilitasi-investasi-pusat-data-ai-pertama-di-asia-senilai-rp6-triliun-di-batam and a second independently-worded WebSearch query confirming info@worldvueribyond.com on the company's own worldvueribyond.com site (per WebFetch-egress-blocked fallback protocol) — BKPM-facilitated US$400M (~Rp6 trillion) jo</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -9806,16 +9882,28 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L122" t="n">
-        <v>0</v>
-      </c>
-      <c r="M122" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17cb57f253f</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
-      <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:29+00:00</t>
+        </is>
+      </c>
       <c r="Q122" t="inlineStr">
         <is>
           <t>none</t>
@@ -9833,39 +9921,39 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>msudarma@unud.ac.id</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Prof. Dr. Ir. Made Sudarma, MASc., IPU., ASEAN Eng.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>Head, Udayana Center of Excellence for Artificial Intelligence (UCEAI)</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Universitas Udayana</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://uceai.unud.ac.id</t>
         </is>
       </c>
       <c r="F123" t="inlineStr"/>
       <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://udayananetworking.unud.ac.id/lecturer/credential/3002-made-sudarma ; cross-checked via a second independently-worded WebSearch query returning the same msudarma@unud.ac.id address (per WebFetch-egress-blocked fallback protocol) — Heads UCEAI, Udayana's dedicated AI research center focused on AI development/application for Bali and Eastern Indonesia (same center already cited as the technology-need signal for the existing generic humas@unud.ac.id row) -- a named, domain-matc</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -9875,16 +9963,28 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L123" t="n">
-        <v>0</v>
-      </c>
-      <c r="M123" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17b2788383b</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
-      <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
+      <c r="O123" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:23+00:00</t>
+        </is>
+      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>none</t>
@@ -9898,6 +9998,627 @@
       </c>
       <c r="T123" t="inlineStr"/>
       <c r="U123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>sally.comollo@global.ntt</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Sally Comollo</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Director of Communications, NTT Global Data Centers</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NTT Global Data Centers (Singapore)</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>https://services.global.ntt</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr"/>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr">
+        <is>
+          <t>web_research: https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific/serangoon-data-center — NTT operates Serangoon Data Center (SG1) in Singapore, its first self-built/self-managed DC outside Japan, running an N+1 chilled-water cooling system; NTT Global Data Centers own AI-and-HPC-ready-data-centers page (services.global.ntt) describes actively deploying liquid cooling and direct-to-chip cold plates across its portfolio including Asia-Pacific</t>
+        </is>
+      </c>
+      <c r="J124" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K124" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L124" t="n">
+        <v>1</v>
+      </c>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>gmail:1a0cc17e133672d6</t>
+        </is>
+      </c>
+      <c r="N124" t="inlineStr"/>
+      <c r="O124" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:10+00:00</t>
+        </is>
+      </c>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:28:34+00:00</t>
+        </is>
+      </c>
+      <c r="Q124" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T124" t="inlineStr"/>
+      <c r="U124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>Colovore</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>https://colovore.com</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr"/>
+      <c r="G125" t="inlineStr"/>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+        </is>
+      </c>
+      <c r="J125" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K125" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L125" t="n">
+        <v>0</v>
+      </c>
+      <c r="M125" t="inlineStr"/>
+      <c r="N125" t="inlineStr"/>
+      <c r="O125" t="inlineStr"/>
+      <c r="P125" t="inlineStr"/>
+      <c r="Q125" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T125" t="inlineStr"/>
+      <c r="U125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr"/>
+      <c r="G126" t="inlineStr"/>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J126" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K126" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L126" t="n">
+        <v>0</v>
+      </c>
+      <c r="M126" t="inlineStr"/>
+      <c r="N126" t="inlineStr"/>
+      <c r="O126" t="inlineStr"/>
+      <c r="P126" t="inlineStr"/>
+      <c r="Q126" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R126" t="inlineStr"/>
+      <c r="S126" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T126" t="inlineStr"/>
+      <c r="U126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J127" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K127" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L127" t="n">
+        <v>0</v>
+      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R127" t="inlineStr"/>
+      <c r="S127" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T127" t="inlineStr"/>
+      <c r="U127" t="inlineStr"/>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr"/>
+      <c r="C128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr"/>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J128" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K128" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="inlineStr"/>
+      <c r="N128" t="inlineStr"/>
+      <c r="O128" t="inlineStr"/>
+      <c r="P128" t="inlineStr"/>
+      <c r="Q128" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T128" t="inlineStr"/>
+      <c r="U128" t="inlineStr"/>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr"/>
+      <c r="H129" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K129" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="inlineStr"/>
+      <c r="N129" t="inlineStr"/>
+      <c r="O129" t="inlineStr"/>
+      <c r="P129" t="inlineStr"/>
+      <c r="Q129" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T129" t="inlineStr"/>
+      <c r="U129" t="inlineStr"/>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr"/>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L130" t="n">
+        <v>0</v>
+      </c>
+      <c r="M130" t="inlineStr"/>
+      <c r="N130" t="inlineStr"/>
+      <c r="O130" t="inlineStr"/>
+      <c r="P130" t="inlineStr"/>
+      <c r="Q130" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T130" t="inlineStr"/>
+      <c r="U130" t="inlineStr"/>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr"/>
+      <c r="G131" t="inlineStr"/>
+      <c r="H131" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K131" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L131" t="n">
+        <v>0</v>
+      </c>
+      <c r="M131" t="inlineStr"/>
+      <c r="N131" t="inlineStr"/>
+      <c r="O131" t="inlineStr"/>
+      <c r="P131" t="inlineStr"/>
+      <c r="Q131" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T131" t="inlineStr"/>
+      <c r="U131" t="inlineStr"/>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr"/>
+      <c r="G132" t="inlineStr"/>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K132" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L132" t="n">
+        <v>0</v>
+      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
+      <c r="P132" t="inlineStr"/>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T132" t="inlineStr"/>
+      <c r="U132" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9910,7 +10631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L170"/>
+  <dimension ref="A1:L172"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11481,12 +12202,12 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-08T13:13:14.278333+00:00: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.datacomm.co.id and also for a generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue). Not a code bug - left as pending, needs retry from a session/environment without</t>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -12141,12 +12862,12 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-09T07:27Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for indosatooredoo.com and www.peruri.co.id, confirming a session-wide policy block, not a site-specific issue, consistent with the last 2 batches). Not a code bug - left as pending, needs retry from a session/environment without this res</t>
+          <t xml:space="preserve">2026-09-22 dual-channel-backup run (3 real emails sent today: Wang Junhong/NUS IT, Laura Chen/GDS International, PT Bali Towerindo Sentra Tbk): NOT attempted. This session's network egress policy is still blocking outbound CONNECT -- confirmed via agentproxy status moments before this batch (recentRelayFailures: connect_rejected / 'gateway answered 403 to CONNECT', for www.google.com and www.dci-indonesia.com), consistent with every prior batch in this campaign and the parent agent's own direct </t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -13451,10 +14172,14 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr">
         <is>
           <t>Operates Indonesia's first AI/deep-learning research center built around an NVIDIA DGX-1 supercomputer, hosted at Fasilkom UI, a high-density GPU compute facility</t>
@@ -14893,10 +15618,14 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
+        </is>
+      </c>
       <c r="J106" t="inlineStr">
         <is>
           <t>Plans to invest up to S$5 billion (~US$3.9B) in Singapore to advance AI-ready data centre developments and strengthen the country's position as APAC's leading AI hub (cross-checked via TNGlobal, Mingtiandi coverage of the same announcement); no domain-matched email confirmed, only a redacted media-contact address found</t>
@@ -15727,10 +16456,14 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I125" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr">
+        <is>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
+        </is>
+      </c>
       <c r="J125" t="inlineStr">
         <is>
           <t>Empyrion Digital (Singapore-HQ'd since 2021) is investing over S$1.1B to expand Singapore data-centre capacity for high-density AI/cloud workloads; its SG1 Dodid facility targets PUE below 1.20 and Green Mark Platinum certification. CEO Mark Fong quoted: 'Singapore is the foundation of everything we are building across Asia.' No domain-matched email found, only a contact form.</t>
@@ -16003,12 +16736,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -16781,12 +17514,12 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>2026-09-15 dual-channel-backup run (day 2, batch 2, 26 emails sent): NOT attempted. This session network egress policy blocked outbound CONNECT -- confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT", e.g. to www.google.com) and via a direct fill_contact_form test on rspondokindah.co.id which failed navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Same root cause documented for Playwright/WebFetch in this environment on 2026-09-14. No navigat</t>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -17773,10 +18506,14 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I170" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2026-09-22 dual-channel-backup run (3 real emails sent today: Wang Junhong/NUS IT, Laura Chen/GDS International, PT Bali Towerindo Sentra Tbk): NOT attempted. This session's network egress policy is still blocking outbound CONNECT -- confirmed via agentproxy status moments before this batch (recentRelayFailures: connect_rejected / 'gateway answered 403 to CONNECT', for www.google.com and www.dci-indonesia.com), consistent with every prior batch in this campaign and the parent agent's own direct </t>
+        </is>
+      </c>
       <c r="J170" t="inlineStr">
         <is>
           <t>TIA-942 Rated 3 certified Balitower/Balifiber Data Center in Jakarta Pusat, expanding colocation capacity beyond original NOC use; actively hiring Data Center Engineers.</t>
@@ -17790,6 +18527,110 @@
       <c r="L170" t="inlineStr">
         <is>
           <t>2026-09-21T10:52:42+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Yee May Leong</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Managing Director, Equinix South Asia</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Equinix Singapore</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>https://www.equinix.com/data-centers/asia-pacific-colocation/singapore-colocation</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr"/>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>https://www.equinix.com/data-centers/asia-pacific-colocation/singapore-colocation/singapore-data-center</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>Equinix is developing SG6, a US$260M+ sixth Singapore IBX data center explicitly positioned to accelerate AI innovation capacity in Singapore, following the US$86M SG5 expansion (MD Yee May Leong quoted on rapidly increasing digital infrastructure demand); no verifiable non-masked personal email found for Yee May Leong, and the generic press@equinix.com address is already recorded for Equinix Indonesia, so routed via the Singapore-specific colocation contact page.</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>https://www.mingtiandi.com/real-estate/data-centres/equinix-developing-260m-data-centre-as-sixth-singapore-facility/</t>
+        </is>
+      </c>
+      <c r="L171" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:21:01+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr"/>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Public Affairs and Communications Department</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Huawei Cloud Singapore</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>https://www.huaweicloud.com/intl/en-us</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr"/>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>https://www.huaweicloud.com/intl/en-us/contact-sales.html</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>2026-09-23 run: NOT filled. Confirmed via curl through the agent proxy (status endpoint) and a live fill_contact_form test that this session's network egress policy blocks outbound browser CONNECT to this host: ERR_TUNNEL_CONNECTION_FAILED, proxy recorded connect_rejected / "gateway answered 403 to CONNECT" for this host and also for a generic control host (www.google.com), confirming a session-wide policy block, not a site-specific issue. Not a code bug. Left pending for retry from a session/en</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>Huawei Cloud launched a new Singapore cloud region serving government, financial-services and large local enterprise customers, currently running from one data center with a disclosed plan to expand to three facilities for active-active failover, positioning Singapore as one of Huawei Clouds largest regions outside China; no verifiable published email found (only a general Singapore office phone number), so routed via contact form.</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/huawei-cloud-launched-singapore/</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-09-23T02:23:43+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U132"/>
+  <dimension ref="A1:U139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10083,39 +10083,35 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
+          <t>college_central@ite.edu.sg</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr"/>
       <c r="C125" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>General Enquiries</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>Institute of Technical Education (ITE) College Central - AiTE</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.ite.edu.sg</t>
         </is>
       </c>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://thetechrevolutionist.com/2022/01/ite-and-nvidia-launch-ai-workforce-readiness-programme.html</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10125,16 +10121,28 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L125" t="n">
-        <v>0</v>
-      </c>
-      <c r="M125" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f59380c75d</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
-      <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q125" t="inlineStr">
         <is>
           <t>none</t>
@@ -10152,39 +10160,35 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Nidhi Chappell</t>
-        </is>
-      </c>
+          <t>humas@pajak.go.id</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr"/>
       <c r="C126" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Public Relations (Humas), Direktorat Jenderal Pajak</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Direktorat Jenderal Pajak (DJP) - Kementerian Keuangan RI</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.pajak.go.id</t>
         </is>
       </c>
       <c r="F126" t="inlineStr"/>
       <c r="G126" t="inlineStr"/>
       <c r="H126" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.liputan6.com/tekno/read/8295162/bangun-coretax-hingga-pusat-data-ai-lg-cns-sabet-penghargaan-dari-djp-kemenkeu</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10194,16 +10198,28 @@
       </c>
       <c r="K126" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L126" t="n">
-        <v>0</v>
-      </c>
-      <c r="M126" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f3bd0a204d</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
-      <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
+      <c r="O126" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>none</t>
@@ -10221,39 +10237,35 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Michael Intrator</t>
-        </is>
-      </c>
+          <t>info@smplus.com</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr"/>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>General/Corporate Contact</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>SM+ Data Centers (PT DSST Mas Gemilang / Sinar Mas)</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://smplus.com</t>
         </is>
       </c>
       <c r="F127" t="inlineStr"/>
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://w.media/sm-data-centers-kira-and-lg-sinar-mas-top-out-smx01-in-jakarta/</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10263,16 +10275,28 @@
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L127" t="n">
-        <v>0</v>
-      </c>
-      <c r="M127" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f35364a40f</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
-      <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
+      <c r="O127" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>none</t>
@@ -10290,27 +10314,35 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>media@singaporetech.edu.sg</t>
         </is>
       </c>
       <c r="B128" t="inlineStr"/>
-      <c r="C128" t="inlineStr"/>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Singapore Institute of Technology (SIT)</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.singaporetech.edu.sg</t>
         </is>
       </c>
       <c r="F128" t="inlineStr"/>
       <c r="G128" t="inlineStr"/>
-      <c r="H128" t="inlineStr"/>
+      <c r="H128" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.singaporetech.edu.sg/news/sit-marks-opening-its-flagship-ai-centre-sit-punggol-campus-key-initiatives-and-partnerships-advance</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10320,16 +10352,28 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f3eecdf3b7</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
-      <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P128" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q128" t="inlineStr">
         <is>
           <t>none</t>
@@ -10347,39 +10391,35 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Charlie Faulkner</t>
-        </is>
-      </c>
+          <t>nuhs_media@nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr"/>
       <c r="C129" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Media Relations</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>National University Health System (NUHS)</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.nuhs.edu.sg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.nuhs.edu.sg/about-nuhs/contact-us</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10389,16 +10429,28 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M129" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f44088ec51</t>
+        </is>
+      </c>
       <c r="N129" t="inlineStr"/>
-      <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P129" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q129" t="inlineStr">
         <is>
           <t>none</t>
@@ -10416,39 +10468,39 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>pohseng@nus.edu.sg</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Assoc Prof Lee Poh Seng</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>Programme Director, Sustainable Tropical Data Centre Testbed (STDCT); Head, Dept of Mechanical Engineering, NUS</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>National University of Singapore (NUS) - Sustainable Tropical Data Centre Testbed</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://cde.nus.edu.sg/me/staff/lee-poh-seng/</t>
         </is>
       </c>
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://news.nus.edu.sg/worlds-first-tropical-climate-data-centre-testbed/</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
@@ -10458,16 +10510,28 @@
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f4a13d159b</t>
+        </is>
+      </c>
       <c r="N130" t="inlineStr"/>
-      <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
+      <c r="O130" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P130" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>none</t>
@@ -10485,39 +10549,39 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>ygwen@ntu.edu.sg</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Prof Wen Yonggang</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Programme Co-Director, Sustainable Tropical Data Centre Testbed (STDCT); Professor, NTU</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>Nanyang Technological University (NTU) - Sustainable Tropical Data Centre Testbed</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://personal.ntu.edu.sg/ygwen/</t>
         </is>
       </c>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://news.nus.edu.sg/worlds-first-tropical-climate-data-centre-testbed/</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10527,16 +10591,28 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>gmail:1a0d13f53f00af9b</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
-      <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:30+00:00</t>
+        </is>
+      </c>
+      <c r="P131" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:29:49+00:00</t>
+        </is>
+      </c>
       <c r="Q131" t="inlineStr">
         <is>
           <t>none</t>
@@ -10554,27 +10630,27 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>info@colovore.com</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Jeffrey Springborn</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
@@ -10586,7 +10662,7 @@
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10619,6 +10695,477 @@
       </c>
       <c r="T132" t="inlineStr"/>
       <c r="U132" t="inlineStr"/>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J133" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K133" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L133" t="n">
+        <v>0</v>
+      </c>
+      <c r="M133" t="inlineStr"/>
+      <c r="N133" t="inlineStr"/>
+      <c r="O133" t="inlineStr"/>
+      <c r="P133" t="inlineStr"/>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T133" t="inlineStr"/>
+      <c r="U133" t="inlineStr"/>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr"/>
+      <c r="G134" t="inlineStr"/>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L134" t="n">
+        <v>0</v>
+      </c>
+      <c r="M134" t="inlineStr"/>
+      <c r="N134" t="inlineStr"/>
+      <c r="O134" t="inlineStr"/>
+      <c r="P134" t="inlineStr"/>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T134" t="inlineStr"/>
+      <c r="U134" t="inlineStr"/>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr"/>
+      <c r="C135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr"/>
+      <c r="G135" t="inlineStr"/>
+      <c r="H135" t="inlineStr"/>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K135" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
+      <c r="O135" t="inlineStr"/>
+      <c r="P135" t="inlineStr"/>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T135" t="inlineStr"/>
+      <c r="U135" t="inlineStr"/>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
+      <c r="O136" t="inlineStr"/>
+      <c r="P136" t="inlineStr"/>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R136" t="inlineStr"/>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T136" t="inlineStr"/>
+      <c r="U136" t="inlineStr"/>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I137" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J137" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K137" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
+      <c r="O137" t="inlineStr"/>
+      <c r="P137" t="inlineStr"/>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R137" t="inlineStr"/>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T137" t="inlineStr"/>
+      <c r="U137" t="inlineStr"/>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J138" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L138" t="n">
+        <v>0</v>
+      </c>
+      <c r="M138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
+      <c r="O138" t="inlineStr"/>
+      <c r="P138" t="inlineStr"/>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R138" t="inlineStr"/>
+      <c r="S138" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T138" t="inlineStr"/>
+      <c r="U138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K139" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L139" t="n">
+        <v>0</v>
+      </c>
+      <c r="M139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
+      <c r="O139" t="inlineStr"/>
+      <c r="P139" t="inlineStr"/>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R139" t="inlineStr"/>
+      <c r="S139" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T139" t="inlineStr"/>
+      <c r="U139" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10631,7 +11178,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L172"/>
+  <dimension ref="A1:L179"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -18104,10 +18651,14 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I161" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
       <c r="J161" t="inlineStr">
         <is>
           <t>Building SMX01, a US$300M Tier IV AI-ready data center in Jakarta's CBD (18MW scalable to 60MW) with high-density racks and liquid cooling, JV with Korea Investment Real Asset Management</t>
@@ -18631,6 +19182,328 @@
       <c r="L172" t="inlineStr">
         <is>
           <t>2026-09-23T02:23:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Singapore Institute of Technology (SIT)</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>https://www.singaporetech.edu.sg</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>https://www.singaporetech.edu.sg/contact-us</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>SIT x NVIDIA AI Centre (SNAIC), DGX H200-based facility at Punggol Campus</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>https://www.singaporetech.edu.sg/news/sit-marks-opening-its-flagship-ai-centre-sit-punggol-campus-key-initiatives-and-partnerships-advance</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:17:36+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr"/>
+      <c r="B174" t="inlineStr"/>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>National University Health System (NUHS)</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>https://www.nuhs.edu.sg</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr"/>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.nuhs.edu.sg/about-nuhs/contact-us</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>Prescience supercomputer, NVIDIA DGX A100 GPU nodes, healthcare AI/LLM training</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>https://www.healthcareitnews.com/news/asia/nuhs-build-supercomputing-infrastructure-hospital-ai</t>
+        </is>
+      </c>
+      <c r="L174" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:17:36+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr"/>
+      <c r="B175" t="inlineStr"/>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>EdgeConneX Singapore</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>https://www.edgeconnex.com/asia-pacific/</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr"/>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.edgeconnex.com/asia-pacific/</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>Joined Singapore's Sustainable Tropical Data Centre Testbed (STDCT) Phase 2.0 as top-tier anchor partner (announced 2026-09-22), a multi-year commitment funding research into advanced liquid cooling and grid-responsive operations for ultra-high-density racks in tropical conditions, contributing its own high-density data center solution 'Ingenuity'. EdgeConneX Singapore Pte Ltd is a real locally-registered entity and the company's APAC HQ is based in Singapore (Marina Square).</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>https://thetechcapital.com/edgeconnex-joins-singapore-tropical-data-centre-testbed/</t>
+        </is>
+      </c>
+      <c r="L175" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:18:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>A*STAR Genome Institute of Singapore (GIS)</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/gis</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/gis/contact-us</t>
+        </is>
+      </c>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>GIS's own Scientific Computing Platform is described by GIS itself as the only local entity capable of supporting genomics research/analysis at a petabyte scale, combining on-premise HPC infrastructure at GIS with NSCC and A*CRC GPU/FPGA computing resources -- a real physical compute-and-storage infrastructure need distinct from the already-queued A*STAR IHPC/A*CRC entry (led on the AI/compute side by Dr Jonathan Goeke, Assistant Director AI &amp; Compute; no domain-resolving personal or media email could be confirmed -- gis.a-star.edu.sg subdomain used in press boilerplate does not resolve via DNS -- so routed here as contact-form only rather than risk an unresolving/unverifiable address).</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/gis/our-science/scientific-computing</t>
+        </is>
+      </c>
+      <c r="L176" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:20:43+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr"/>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Direktorat Jenderal Pajak (DJP) - Kementerian Keuangan RI</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>https://www.pajak.go.id</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr"/>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://pajak.go.id/en/form/contact</t>
+        </is>
+      </c>
+      <c r="H177" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>DJP operates a newly built AI-based data center in Jakarta (~Rp1.3 trillion, built by LG CNS) powering its Coretax national tax administration system; backup contact-form channel alongside the humas@pajak.go.id email already on file</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>https://www.liputan6.com/tekno/read/8295162/bangun-coretax-hingga-pusat-data-ai-lg-cns-sabet-penghargaan-dari-djp-kemenkeu</t>
+        </is>
+      </c>
+      <c r="L177" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:21:08+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr"/>
+      <c r="B178" t="inlineStr"/>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Republic Polytechnic (RP) - AI Technology Centre (AITC)</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>https://www.rp.edu.sg</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.rp.edu.sg/about-us/contact-us/</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>Republic Polytechnic's AI Technology Centre (AITC) is a real physical facility backed by NVIDIA, NSCC and YooZoo providing AI/cyber/cloud/immersive-tech labs with NVIDIA GPU resources for student and industry AI projects. A specific named media contact (vimala_christie@rp.edu.sg) surfaced but could not be independently corroborated by a second search, so routed here as contact-form only per the mandatory cross-check protocol rather than risk an unverified address.</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>https://mothership.sg/2021/09/nvidia-republic-poly-applied-artificial-intelligence/</t>
+        </is>
+      </c>
+      <c r="L178" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:22:49+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr"/>
+      <c r="B179" t="inlineStr"/>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Institute of Technical Education (ITE) College Central - AiTE</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>https://www.ite.edu.sg</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr"/>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.ite.edu.sg/about-ite/contact-us/</t>
+        </is>
+      </c>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>AiTE facility at ITE College Central hosting NVIDIA's supercomputing platform</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>https://thetechrevolutionist.com/2022/01/ite-and-nvidia-launch-ai-workforce-readiness-programme.html</t>
+        </is>
+      </c>
+      <c r="L179" t="inlineStr">
+        <is>
+          <t>2026-09-24T02:23:20+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U139"/>
+  <dimension ref="A1:U147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10630,39 +10630,39 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
+          <t>audrey.lau.l.p@singhealth.com.sg</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Jeffrey Springborn</t>
+          <t>Audrey Lau</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Group Chief Communications Officer</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>SingHealth (Singapore General Hospital Campus)</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.singhealth.com.sg</t>
         </is>
       </c>
       <c r="F132" t="inlineStr"/>
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.singhealth.com.sg/news/announcements/supercomputer-for-complex-health-research-at-new-centre</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10672,16 +10672,28 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>1a0d65fddfe6c101</t>
+        </is>
+      </c>
       <c r="N132" t="inlineStr"/>
-      <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
+      <c r="O132" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P132" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q132" t="inlineStr">
         <is>
           <t>none</t>
@@ -10699,39 +10711,35 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Nidhi Chappell</t>
-        </is>
-      </c>
+          <t>help-occ@rp.edu.sg</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr"/>
       <c r="C133" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Office of Corporate Communications</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Republic Polytechnic (RP) - AI Technology Centre (AITC)</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.rp.edu.sg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.rp.edu.sg/about-us/contact-us/</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -10741,16 +10749,28 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M133" t="inlineStr">
+        <is>
+          <t>1a0d65fe2e523eb5</t>
+        </is>
+      </c>
       <c r="N133" t="inlineStr"/>
-      <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
+      <c r="O133" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P133" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>none</t>
@@ -10768,39 +10788,39 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>ir@digitalcorereit.com</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Mabel Tan</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director, Capital Markets &amp; Investor Relations</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Digital Core REIT</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://www.digitalcorereit.com</t>
         </is>
       </c>
       <c r="F134" t="inlineStr"/>
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.digitalcorereit.com/investor-relations/email-alerts-and-ir-contact/default.aspx</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
@@ -10810,16 +10830,28 @@
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>1a0d65fea7d8bcae</t>
+        </is>
+      </c>
       <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P134" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>none</t>
@@ -10837,27 +10869,35 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>ir@superx.sg</t>
         </is>
       </c>
       <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>SuperX AI Technology Limited</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.superx.sg</t>
         </is>
       </c>
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/ai-compute-simplified-st-telemedia-global-data-centres-and-super-x-0cmut4phmwuj.html</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -10867,16 +10907,28 @@
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M135" t="inlineStr">
+        <is>
+          <t>1a0d65fefbbb0c20</t>
+        </is>
+      </c>
       <c r="N135" t="inlineStr"/>
-      <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P135" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>none</t>
@@ -10894,39 +10946,39 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>marketing@bitera-dc.com</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Tedy Harjanto</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Chief Executive Officer</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Bitera Data Center (PT Mitra Informatika Gemilang)</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.bitera-dc.com/</t>
         </is>
       </c>
       <c r="F136" t="inlineStr"/>
       <c r="G136" t="inlineStr"/>
       <c r="H136" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/bitera-data-center-in-jakarta-indonesia-launches-operations/</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -10936,16 +10988,28 @@
       </c>
       <c r="K136" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M136" t="inlineStr">
+        <is>
+          <t>1a0d65fca086c963</t>
+        </is>
+      </c>
       <c r="N136" t="inlineStr"/>
-      <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P136" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q136" t="inlineStr">
         <is>
           <t>none</t>
@@ -10963,39 +11027,35 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Don MacNeil</t>
-        </is>
-      </c>
+          <t>media@certisgroup.com</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr"/>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>Media Contact</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Certis Group</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://www.certisgroup.com</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://servers.asus.com/stories/Certis</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11005,16 +11065,28 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>1a0d65ff49a422a6</t>
+        </is>
+      </c>
       <c r="N137" t="inlineStr"/>
-      <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P137" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>none</t>
@@ -11032,39 +11104,39 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>sales@dtp.net.id</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Michael Alifen</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director &amp; CEO</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>DTP (PT Dwi Tunggal Putra)</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://www.dtp.net.id/</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.dtp.net.id/en/data-center-services/data-center</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
@@ -11074,16 +11146,28 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L138" t="n">
-        <v>0</v>
-      </c>
-      <c r="M138" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M138" t="inlineStr">
+        <is>
+          <t>1a0d65fd53ad6410</t>
+        </is>
+      </c>
       <c r="N138" t="inlineStr"/>
-      <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
+      <c r="O138" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P138" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>none</t>
@@ -11101,39 +11185,39 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>sales@mettadc.com</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Sukoco Halim</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>President Director &amp; CEO</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>MettaDC (PT MettaDC Teknologi Indonesia)</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://mettadc.com/</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr"/>
       <c r="H139" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.theiconomics.com/market-expansion/proyek-pertama-resmi-beroperasi-mettadc-akan-terus-bangun-data-center-hingga-500-mw/</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
@@ -11143,16 +11227,28 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L139" t="n">
-        <v>0</v>
-      </c>
-      <c r="M139" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>1a0d65fd1d7dced6</t>
+        </is>
+      </c>
       <c r="N139" t="inlineStr"/>
-      <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
+      <c r="O139" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:13+00:00</t>
+        </is>
+      </c>
+      <c r="P139" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:23:32+00:00</t>
+        </is>
+      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>none</t>
@@ -11166,6 +11262,546 @@
       </c>
       <c r="T139" t="inlineStr"/>
       <c r="U139" t="inlineStr"/>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>Colovore</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>https://colovore.com</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+        </is>
+      </c>
+      <c r="J140" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K140" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L140" t="n">
+        <v>0</v>
+      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
+      <c r="O140" t="inlineStr"/>
+      <c r="P140" t="inlineStr"/>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T140" t="inlineStr"/>
+      <c r="U140" t="inlineStr"/>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr"/>
+      <c r="G141" t="inlineStr"/>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K141" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L141" t="n">
+        <v>0</v>
+      </c>
+      <c r="M141" t="inlineStr"/>
+      <c r="N141" t="inlineStr"/>
+      <c r="O141" t="inlineStr"/>
+      <c r="P141" t="inlineStr"/>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T141" t="inlineStr"/>
+      <c r="U141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K142" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L142" t="n">
+        <v>0</v>
+      </c>
+      <c r="M142" t="inlineStr"/>
+      <c r="N142" t="inlineStr"/>
+      <c r="O142" t="inlineStr"/>
+      <c r="P142" t="inlineStr"/>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R142" t="inlineStr"/>
+      <c r="S142" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T142" t="inlineStr"/>
+      <c r="U142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr"/>
+      <c r="C143" t="inlineStr"/>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr"/>
+      <c r="G143" t="inlineStr"/>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L143" t="n">
+        <v>0</v>
+      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
+      <c r="P143" t="inlineStr"/>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R143" t="inlineStr"/>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T143" t="inlineStr"/>
+      <c r="U143" t="inlineStr"/>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L144" t="n">
+        <v>0</v>
+      </c>
+      <c r="M144" t="inlineStr"/>
+      <c r="N144" t="inlineStr"/>
+      <c r="O144" t="inlineStr"/>
+      <c r="P144" t="inlineStr"/>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R144" t="inlineStr"/>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T144" t="inlineStr"/>
+      <c r="U144" t="inlineStr"/>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr"/>
+      <c r="G145" t="inlineStr"/>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
+      <c r="O145" t="inlineStr"/>
+      <c r="P145" t="inlineStr"/>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R145" t="inlineStr"/>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T145" t="inlineStr"/>
+      <c r="U145" t="inlineStr"/>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr"/>
+      <c r="G146" t="inlineStr"/>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L146" t="n">
+        <v>0</v>
+      </c>
+      <c r="M146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
+      <c r="O146" t="inlineStr"/>
+      <c r="P146" t="inlineStr"/>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R146" t="inlineStr"/>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T146" t="inlineStr"/>
+      <c r="U146" t="inlineStr"/>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L147" t="n">
+        <v>0</v>
+      </c>
+      <c r="M147" t="inlineStr"/>
+      <c r="N147" t="inlineStr"/>
+      <c r="O147" t="inlineStr"/>
+      <c r="P147" t="inlineStr"/>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T147" t="inlineStr"/>
+      <c r="U147" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11178,7 +11814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L179"/>
+  <dimension ref="A1:L194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19442,7 +20078,7 @@
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>2026-09-24 Day 12 run: NOT attempted (filled) beyond one confirmation test. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 and www.singaporetech.edu.sg:443, the latter from a live fill_contact_form() test on this row) and a live fill_contact_form() call against this batch returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED. Session-wide poli</t>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
@@ -19504,6 +20140,704 @@
       <c r="L179" t="inlineStr">
         <is>
           <t>2026-09-24T02:23:20+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Bitera Data Center (PT Mitra Informatika Gemilang)</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>https://www.bitera-dc.com/</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.bitera-dc.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>20MW Tier III Jakarta colocation facility, ~4,000 racks, ISO 27001 certified.</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/bitera-data-center-in-jakarta-indonesia-launches-operations/</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:28+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr"/>
+      <c r="B181" t="inlineStr"/>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>MettaDC (PT MettaDC Teknologi Indonesia)</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>https://mettadc.com/</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr"/>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://mettadc.com/support</t>
+        </is>
+      </c>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>35MW Jakarta-area facility live, targeting 500MW total capacity expansion.</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>https://www.theiconomics.com/market-expansion/proyek-pertama-resmi-beroperasi-mettadc-akan-terus-bangun-data-center-hingga-500-mw/</t>
+        </is>
+      </c>
+      <c r="L181" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:28+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr"/>
+      <c r="B182" t="inlineStr"/>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>DTP (PT Dwi Tunggal Putra)</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>https://www.dtp.net.id/</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>+62 822-9999-9387</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>+62 21 27096900</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.dtp.net.id/en/support/customer-care</t>
+        </is>
+      </c>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>Operates 4 Jakarta-area colocation data centers with cold-containment rack rows.</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>https://www.dtp.net.id/en/data-center-services/data-center</t>
+        </is>
+      </c>
+      <c r="L182" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr"/>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>K2 Strategic Indonesia (Kuok Group / Sinar Mas Land JV)</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>https://k2strategic.co/indonesia/</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr"/>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://k2strategic.co/contact-us/</t>
+        </is>
+      </c>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>JV with Sinar Mas Land developing hyperscale data center campuses in Bekasi (K2 JKT1, 58.8MW IT capacity at full build-out, Tier III + LEED Gold) with a second 100MW+ campus planned in Karawang.</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/kuok-groups-k2-partners-with-sinar-mas-for-jakarta-data-center-campuses/</t>
+        </is>
+      </c>
+      <c r="L183" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Pure Data Centres (PureDC Jakarta)</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>https://puredc.com/</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr">
+        <is>
+          <t>https://puredc.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>Operational 20MW hyperscale facility in the LOGOS Metrolink Logistics Hub, Bekasi/Jakarta (JKT01), 100% renewable-powered, Zero Waste-to-Landfill certified.</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>https://www.datacenterdynamics.com/en/news/pure-dc-launches-data-center-in-jakarta-indonesia/</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr"/>
+      <c r="B185" t="inlineStr"/>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>IDC Indonesia (PT Internetindo Data Centra Indonesia)</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>https://www.idc.co.id/</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>+62 215269988</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.idc.co.id/</t>
+        </is>
+      </c>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>Indonesia's first carrier-neutral data center operator, now operating 6 facilities across Jakarta, Batam, Bandung, Surabaya and Makassar carrying over 95% of Indonesian internet traffic.</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>https://www.idc.co.id/</t>
+        </is>
+      </c>
+      <c r="L185" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:12:29+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr"/>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>SingHealth (Singapore General Hospital Campus)</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>https://www.singhealth.com.sg</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr"/>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>https://www.singhealth.com.sg/patient-services/contact-us</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>CHROMA supercomputer (NVIDIA DGX A100 systems) deployed at SGH Campus for large-scale medical AI research.</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>https://www.singhealth.com.sg/news/announcements/supercomputer-for-complex-health-research-at-new-centre</t>
+        </is>
+      </c>
+      <c r="L186" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Digital Core REIT</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>https://www.digitalcorereit.com</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.digitalcorereit.com/contact-us/default.aspx</t>
+        </is>
+      </c>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>Digital Core REIT's maiden Singapore acquisition, a stake in Digital Loyang 2 data center (Aug 2026).</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>https://www.digitalcorereit.com/investor-relations/email-alerts-and-ir-contact/default.aspx</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr"/>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Keppel DC REIT</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>https://www.keppeldcreit.com</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr"/>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.keppeldcreit.com/en/investor-relations/ir-contact/</t>
+        </is>
+      </c>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr"/>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>Keppel DC Singapore 9 construction (mid-2026 start), AI-ready Genting Lane campus expansion.</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>https://datacentremagazine.com/news/major-data-centre-operators-awarded-50-mw-each-in-singapore</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr"/>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>SuperX AI Technology Limited</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>https://www.superx.sg</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr"/>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.superx.sg/contact?language=en</t>
+        </is>
+      </c>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>AI Innovation Centre at STT GDC Singapore 5, NVIDIA Blackwell GPU infrastructure deployment.</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>https://www.prnewswire.com/news-releases/ai-compute-simplified-st-telemedia-global-data-centres-and-super-x-0cmut4phmwuj.html</t>
+        </is>
+      </c>
+      <c r="L189" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr"/>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Certis Group</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>https://www.certisgroup.com</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr"/>
+      <c r="F190" t="inlineStr"/>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.certisgroup.com/connect-with-us/</t>
+        </is>
+      </c>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>800 sqm Centre for Applied Intelligence + ASUS-built data center for AI security operations.</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>https://servers.asus.com/stories/Certis</t>
+        </is>
+      </c>
+      <c r="L190" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>OVHcloud Singapore</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>https://www.ovhcloud.com</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.ovhcloud.com/en/contact/</t>
+        </is>
+      </c>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>OVHcloud launched its second Singapore data center (SGP2), described as its most sustainable data centre in Asia Pacific -- no domain-matched personal/generic email found, contact-form only.</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>https://corporate.ovhcloud.com/en/newsroom/ovhcloud-expands-singapore/</t>
+        </is>
+      </c>
+      <c r="L191" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr"/>
+      <c r="B192" t="inlineStr"/>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Infrastructure Singapore</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/sg/</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr"/>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/sg/news/media-contacts.html</t>
+        </is>
+      </c>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>Oracle opened a second Oracle Cloud Region in Singapore to meet rapidly growing AI/cloud demand, enabling customers to migrate mission-critical AI workloads -- distinct from the already-queued Oracle Indonesia row; no domain-matched named contact found, contact-form only.</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>https://blogs.oracle.com/cloud-infrastructure/oracle-opens-second-cloud-region-in-singapore</t>
+        </is>
+      </c>
+      <c r="L192" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr"/>
+      <c r="B193" t="inlineStr"/>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>NUS Medicine (Biological Data Center prototype)</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>https://medicine.nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr"/>
+      <c r="F193" t="inlineStr"/>
+      <c r="G193" t="inlineStr">
+        <is>
+          <t>https://medicine.nus.edu.sg/contact-us/</t>
+        </is>
+      </c>
+      <c r="H193" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I193" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>NUS Medicine, DayOne and Cortical Labs unveiled Singapore's first biological data center prototype (July/Aug 2026): a 20-unit CL1 rack of 16 million living human neurons requiring precise thermal/life-support environmental control, hosted within infrastructure designed and supported by DayOne at the NUS Life Sciences Institute -- distinct entity/facility from the already-covered DayOne row.</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>https://medicine.nus.edu.sg/news/nus-medicine-dayone-and-cortical-labs-unveil-biological-data-center-prototype-in-singapore/</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>A*STAR Institute of Advanced Intelligence and Computing (IAIC)</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/iaic/about-iaic</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr">
+        <is>
+          <t>https://www.a-star.edu.sg/Contact-Us.aspx</t>
+        </is>
+      </c>
+      <c r="H194" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I194" t="inlineStr">
+        <is>
+          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+        </is>
+      </c>
+      <c r="J194" t="inlineStr">
+        <is>
+          <t>A*STAR formed IAIC (began operations 1 July 2026) by merging the Institute for Infocomm Research (I2R) and Institute of High Performance Computing (IHPC), consolidating AI, HPC/GPU, FPGA, quantum and modelling/simulation compute capabilities under one institute -- no domain-matched named contact found, contact-form only.</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr">
+        <is>
+          <t>https://www.frontier-enterprise.com/astar-launches-new-research-institute-to-push-ai-data-and-computing-applications/</t>
+        </is>
+      </c>
+      <c r="L194" t="inlineStr">
+        <is>
+          <t>2026-09-25T02:15:39+00:00</t>
         </is>
       </c>
     </row>
@@ -19518,7 +20852,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -19875,6 +21209,48 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Renee Goh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Senior Manager, Investor Relations &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Keppel DC REIT</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>renee.goh@keppel.com</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>web_research: https://www.keppeldcreit.com/en/investor-relations/ir-contact/ — Keppel DC REIT (SGX-listed, separately managed from Keppel Data Centres) owns the Keppel DC Singapore portfolio; Keppel is beginning construction of Keppel DC Singapore 9 in mid-2026 as part of its AI-ready Genting Lane campus expansion, alongside its publicly stated SGP9 floating-data-center seawater-cooling vision.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Email domain (keppel.com) does not match the source/website domain (keppeldcreit.com). Plausible explanation - SGX REIT managers are commonly staffed by the parent corporation and may retain the parent's email domain - but this was not independently confirmed against a first-party page (WebFetch blocked this session), and the campaign applied the same domain-mismatch standard to two other rows this same batch (K2 Strategic, Pure Data Centres), so held to the same bar rather than making an exception.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U147"/>
+  <dimension ref="A1:U152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9882,7 +9882,7 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L122" t="n">
@@ -9893,17 +9893,17 @@
           <t>gmail:1a0cc17cb57f253f</t>
         </is>
       </c>
-      <c r="N122" t="inlineStr"/>
+      <c r="N122" t="inlineStr">
+        <is>
+          <t>4.4.1 The recipient server did not accept our requests to connect (timed out after 45h retry window); [worldvueribyond.com 2606:4700:3034::ac43:951d: timed out] [worldvueribyond.com 2606:4700:3032::6815:21c8: timed out] [worldvueribyond.com 172.67.149.29: timed out] [worldvueribyond.com 104.21.33.200: timed out]</t>
+        </is>
+      </c>
       <c r="O122" t="inlineStr">
         <is>
           <t>2026-09-23T02:28:10+00:00</t>
         </is>
       </c>
-      <c r="P122" t="inlineStr">
-        <is>
-          <t>2026-09-23T02:28:29+00:00</t>
-        </is>
-      </c>
+      <c r="P122" t="inlineStr"/>
       <c r="Q122" t="inlineStr">
         <is>
           <t>none</t>
@@ -11266,39 +11266,31 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>info@inti.co.id</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr"/>
+      <c r="C140" t="inlineStr"/>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>PT INTI (Persero)</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.inti.co.id</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.inti.co.id/?p=13158 — State-owned telecom manufacturer PT INTI (Persero) is developing an AI GPU-based Data Center on its 8-hectare Bandung headquarters site (3,888 sqm operational facility), per its own site news and a May 2024 MoU with PT Jagat Bali Lestari to build and operate the facility, corroborated by a second independent report (i-portal.inti.co.id/post/4379/bandung-punya-ai-data-center) confirming the AI GPU data center is being developed there.</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11308,16 +11300,28 @@
       </c>
       <c r="K140" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L140" t="n">
-        <v>0</v>
-      </c>
-      <c r="M140" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M140" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4b636224a8</t>
+        </is>
+      </c>
       <c r="N140" t="inlineStr"/>
-      <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
+      <c r="O140" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P140" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
       <c r="Q140" t="inlineStr">
         <is>
           <t>none</t>
@@ -11335,39 +11339,39 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>kee_yuan_ngiam@nuhs.edu.sg</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>A/Prof Ngiam Kee Yuan</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Group Chief Technology Officer &amp; Head, AI Office, NUHS</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>NUHS</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.nuhs.edu.sg</t>
         </is>
       </c>
       <c r="F141" t="inlineStr"/>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.biospectrumasia.com/company-results/54/22939/singapores-nuhs-launches-first-ai-driven-supercomputer-to-empower-healthcare-projects.html ; contact confirmed via https://discovery.nuhs.edu.sg/2737-kee-yuan-ngiam and https://www.sgdi.gov.sg/ministries/moh/others/nuhs/departments/gito/Departments/aio — Leads NUHS's AI Office and the Prescience supercomputer initiative -- Singapore's third national supercomputer and first in healthcare, running multiple NVIDIA DGX A100 nodes for medical LLM training, built with NSCC -- a genuinely on-point named lead for the facility already cited as NUHS's technology-need signal</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11377,16 +11381,28 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L141" t="n">
-        <v>0</v>
-      </c>
-      <c r="M141" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4bc6a7e193</t>
+        </is>
+      </c>
       <c r="N141" t="inlineStr"/>
-      <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
+      <c r="O141" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P141" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
       <c r="Q141" t="inlineStr">
         <is>
           <t>none</t>
@@ -11404,39 +11420,39 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
+          <t>media@ovhcloud.com</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Michael Intrator</t>
+          <t>Marie Vaillaud</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Communications and PR Manager</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>OVHcloud Singapore</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://www.ovhcloud.com/en-sg/</t>
         </is>
       </c>
       <c r="F142" t="inlineStr"/>
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/ovhcloud-launches-data-center-in-singapore/ ; press contact confirmed via corporate.ovhcloud.com newsroom boilerplate — OVHcloud launched SGP2, its second Singapore data center, billed as its most sustainable APAC facility, expanding Bare Metal/dedicated server capacity to meet regional AI and cloud demand</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -11446,16 +11462,28 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L142" t="n">
-        <v>0</v>
-      </c>
-      <c r="M142" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4c0d85fdf2</t>
+        </is>
+      </c>
       <c r="N142" t="inlineStr"/>
-      <c r="O142" t="inlineStr"/>
-      <c r="P142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>none</t>
@@ -11473,27 +11501,39 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr"/>
-      <c r="C143" t="inlineStr"/>
+          <t>rickie.patani@nus.edu.sg</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Prof Rickie Patani</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Professor of Neuroscience &amp; Director, Neurobiology Programme, Life Sciences Institute, NUS Medicine</t>
+        </is>
+      </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>NUS Medicine</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://medicine.nus.edu.sg</t>
         </is>
       </c>
       <c r="F143" t="inlineStr"/>
       <c r="G143" t="inlineStr"/>
-      <c r="H143" t="inlineStr"/>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://medicine.nus.edu.sg/news/nus-medicine-dayone-and-cortical-labs-unveil-biological-data-center-prototype-in-singapore/ ; contact confirmed via https://www.nus.edu.sg/lsi/principal-investigators-3/prof-rickie-patani/ — NUS Medicine, DayOne Data Centers and Cortical Labs unveiled a Biological Data Centre prototype in Singapore (Aug 2026) -- 20 CL1 biological-computing units powered by 16 million living human neurons, requiring precise thermal/environmental control per rack; Prof Patani supervises the neuron cultures used in the deployment as Director of NUS LSI's Neurobiology Programme</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
@@ -11503,16 +11543,28 @@
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L143" t="n">
-        <v>0</v>
-      </c>
-      <c r="M143" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4b9cc3375b</t>
+        </is>
+      </c>
       <c r="N143" t="inlineStr"/>
-      <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>none</t>
@@ -11530,39 +11582,39 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>zhengkui.wang@singaporetech.edu.sg</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Daniel Zhengkui Wang</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Director, SIT x NVIDIA AI Centre (SNAIC) &amp; Associate Professor, Infocomm Technology Cluster</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Singapore Institute of Technology</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.singaporetech.edu.sg</t>
         </is>
       </c>
       <c r="F144" t="inlineStr"/>
       <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.singaporetech.edu.sg/news/sit-marks-opening-its-flagship-ai-centre-sit-punggol-campus-key-initiatives-and-partnerships-advance ; contact confirmed via https://www.singaporetech.edu.sg/directory/faculty/daniel-zhengkui-wang — Director of SIT's flagship SNAIC facility at Punggol Campus, a ~250 sqm AI centre built around an NVIDIA DGX H200 serving 50+ research engineers/students and 20+ industry partners -- a real, named lead for the same facility already cited as SIT's technology-need signal</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -11572,16 +11624,28 @@
       </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L144" t="n">
-        <v>0</v>
-      </c>
-      <c r="M144" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>gmail:1a0e5d4ba7fdb5f0</t>
+        </is>
+      </c>
       <c r="N144" t="inlineStr"/>
-      <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:06+00:00</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:25:25+00:00</t>
+        </is>
+      </c>
       <c r="Q144" t="inlineStr">
         <is>
           <t>none</t>
@@ -11599,27 +11663,27 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>info@colovore.com</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Jeffrey Springborn</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Colovore</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://colovore.com</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
@@ -11631,7 +11695,7 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -11668,39 +11732,39 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>press@nscale.com</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Nidhi Chappell</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>President, AI Infrastructure</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>Nscale</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://nscale.com</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -11737,27 +11801,27 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>press@coreweave.com</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Michael Intrator</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>CEO</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>CoreWeave</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://coreweave.com</t>
         </is>
       </c>
       <c r="F147" t="inlineStr"/>
@@ -11769,7 +11833,7 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11802,6 +11866,339 @@
       </c>
       <c r="T147" t="inlineStr"/>
       <c r="U147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr"/>
+      <c r="C148" t="inlineStr"/>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr"/>
+      <c r="G148" t="inlineStr"/>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J148" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L148" t="n">
+        <v>0</v>
+      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
+      <c r="P148" t="inlineStr"/>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T148" t="inlineStr"/>
+      <c r="U148" t="inlineStr"/>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr"/>
+      <c r="G149" t="inlineStr"/>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J149" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K149" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L149" t="n">
+        <v>0</v>
+      </c>
+      <c r="M149" t="inlineStr"/>
+      <c r="N149" t="inlineStr"/>
+      <c r="O149" t="inlineStr"/>
+      <c r="P149" t="inlineStr"/>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T149" t="inlineStr"/>
+      <c r="U149" t="inlineStr"/>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr"/>
+      <c r="G150" t="inlineStr"/>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J150" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L150" t="n">
+        <v>0</v>
+      </c>
+      <c r="M150" t="inlineStr"/>
+      <c r="N150" t="inlineStr"/>
+      <c r="O150" t="inlineStr"/>
+      <c r="P150" t="inlineStr"/>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T150" t="inlineStr"/>
+      <c r="U150" t="inlineStr"/>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I151" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J151" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L151" t="n">
+        <v>0</v>
+      </c>
+      <c r="M151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
+      <c r="O151" t="inlineStr"/>
+      <c r="P151" t="inlineStr"/>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T151" t="inlineStr"/>
+      <c r="U151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr"/>
+      <c r="H152" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I152" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L152" t="n">
+        <v>0</v>
+      </c>
+      <c r="M152" t="inlineStr"/>
+      <c r="N152" t="inlineStr"/>
+      <c r="O152" t="inlineStr"/>
+      <c r="P152" t="inlineStr"/>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T152" t="inlineStr"/>
+      <c r="U152" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -11814,7 +12211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L194"/>
+  <dimension ref="A1:L195"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -20838,6 +21235,52 @@
       <c r="L194" t="inlineStr">
         <is>
           <t>2026-09-25T02:15:39+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr"/>
+      <c r="B195" t="inlineStr"/>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>PT INTI (Persero)</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>https://www.inti.co.id</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr"/>
+      <c r="F195" t="inlineStr"/>
+      <c r="G195" t="inlineStr">
+        <is>
+          <t>https://www.inti.co.id/?page_id=1250</t>
+        </is>
+      </c>
+      <c r="H195" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I195" t="inlineStr">
+        <is>
+          <t>2026-09-28 Day 14 run: NOT filled. This session network egress policy blocks outbound browser CONNECT: confirmed via agentproxy status (recentRelayFailures: connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host, recorded seconds before this batch) and a live fill_contact_form() call against this row returning navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then also recording connect_rejected / 403-to-CONNECT for www.i</t>
+        </is>
+      </c>
+      <c r="J195" t="inlineStr">
+        <is>
+          <t>State-owned telecom manufacturer developing an AI GPU-based Data Center at its Bandung HQ (8-hectare site, 3,888 sqm operational facility), per MoU with PT Jagat Bali Lestari.</t>
+        </is>
+      </c>
+      <c r="K195" t="inlineStr">
+        <is>
+          <t>https://www.inti.co.id/?p=13158</t>
+        </is>
+      </c>
+      <c r="L195" t="inlineStr">
+        <is>
+          <t>2026-09-28T02:18:56+00:00</t>
         </is>
       </c>
     </row>
@@ -20852,7 +21295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21251,6 +21694,66 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr"/>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>DTC Netconnect (PT Adhitya Mandiri Pratama)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>web_research: https://www.dtcnetconnect.com/ and https://dtcnetconnect.com/about-us — DTC Netconnect sells its own DTC Smart Series data center products, explicitly including a Liquid Cooling System, Modular Smart Containment, and Hot/Cold Containment, and is expanding this cooling product line for AI-based data centers via a partnership with ASRock Rack Inc.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Vendor conflict — DTC Netconnect manufactures/distributes its own competing liquid-cooling and containment systems for data centers, the same product category Borealis sells. Not a prospect; excluded per the campaign vendor-conflict rule (same category as ST Engineering/Airbitat, Johnson Controls).</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Data Center First Pte Ltd (Gaw Capital / Wong Ka Vin JV — Nongsa One, Batam)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/data-center-first-to-build-30mw-data-center-in-batam-indonesia/ and https://www.sgpbusiness.com/company/Data-Center-First-Pte-Ltd — 30MW Nongsa One data center campus (Uptime Tier III) built in Nongsa Digital Park, Batam, Indonesia; real cooling-relevant AI/hyperscale colocation buildout.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Real facility and real technology-need signal (2021-2023 Batam buildout), but the operating entity Data Center First Pte Ltd (Singapore-registered, reg. 202117964R) shows as "Dissolved - Members Voluntary Winding Up" on sgpbusiness.com/ACRA-sourced company records. The datacenterfirst.com website and Nongsa One facility page still appear live, so this may be a corporate restructuring rather than a facility closure, but no 2025/2026 news or current operating confirmation was found and WebFetch is blocked this session so the live site could not be directly checked. No domain-matched email was found either way. Needs manual verification of current legal/operating status before any outreach — do not add to prospects.csv or contact_form_queue.csv until confirmed live.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U152"/>
+  <dimension ref="A1:U164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11663,39 +11663,31 @@
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Jeffrey Springborn</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>info@epsilontel.com</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr"/>
+      <c r="C145" t="inlineStr"/>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>Epsilon Telecommunications, a KT company</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://epsilontel.com</t>
         </is>
       </c>
       <c r="F145" t="inlineStr"/>
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://baxtel.com/data-center/epsilon-singapore-new-tech-park and https://www.datacenters.com/epsilon-telecommunications-singapore</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
@@ -11705,16 +11697,28 @@
       </c>
       <c r="K145" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L145" t="n">
-        <v>0</v>
-      </c>
-      <c r="M145" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>1a0f025bf08c9490</t>
+        </is>
+      </c>
       <c r="N145" t="inlineStr"/>
-      <c r="O145" t="inlineStr"/>
-      <c r="P145" t="inlineStr"/>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:29:50+00:00</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:30:05+00:00</t>
+        </is>
+      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>none</t>
@@ -11732,39 +11736,39 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
+          <t>suyi@a-star.edu.sg</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Nidhi Chappell</t>
+          <t>Dr Su Yi</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>Executive Director, A*STAR Institute of Advanced Intelligence and Computing (IAIC)</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>A*STAR Institute of Advanced Intelligence and Computing (IAIC)</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.a-star.edu.sg/iaic</t>
         </is>
       </c>
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.sgdi.gov.sg/ministries/mti/statutory-boards/a-star/departments/re/departments/iaic</t>
         </is>
       </c>
       <c r="J146" t="inlineStr">
@@ -11774,16 +11778,28 @@
       </c>
       <c r="K146" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L146" t="n">
-        <v>0</v>
-      </c>
-      <c r="M146" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>1a0f025c1ccbb399</t>
+        </is>
+      </c>
       <c r="N146" t="inlineStr"/>
-      <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:29:50+00:00</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:30:05+00:00</t>
+        </is>
+      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>none</t>
@@ -11801,39 +11817,39 @@
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Michael Intrator</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>allocare@allobank.com</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
       <c r="D147" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>Allo Bank Indonesia</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr"/>
-      <c r="G147" t="inlineStr"/>
+          <t>https://www.allobank.com</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>0822 0822 4110</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>080 4110 4110</t>
+        </is>
+      </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://tiaonline.org/942-datacenter/pt-allo-bank-indonesia-tbk-data-center-allo-bank/ ; contact confirmed via Allo Bank official verified account, e.g. https://x.com/AlloBankID/status/2011269529486442641 — Allo Bank separated its infrastructure from parent Bank Mega and launched its own dedicated, TIA Rated-3 certified data center in May 2024</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
@@ -11843,16 +11859,28 @@
       </c>
       <c r="K147" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L147" t="n">
-        <v>0</v>
-      </c>
-      <c r="M147" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028608588884</t>
+        </is>
+      </c>
       <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>none</t>
@@ -11870,27 +11898,35 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>ap.ask@global.ntt</t>
         </is>
       </c>
       <c r="B148" t="inlineStr"/>
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>NTT Indonesia (NTT Global Data Centers)</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://services.global.ntt</t>
         </is>
       </c>
       <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>+65 6991 2020</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific/jakarta-2a-data-center ; contact confirmed via https://services.global.ntt/en-us/speak-to-our-experts and https://services.global.ntt/en-us/services-and-products/global-data-centers/global-locations/asia-pacific — Jakarta 2 Annex (JKT2A), NTT's third Indonesia facility, delivers 12MW of IT load purpose-built for high-density deployments supporting racks up to 40kW, opening early 2026</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -11900,16 +11936,28 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L148" t="n">
-        <v>0</v>
-      </c>
-      <c r="M148" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M148" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028ba720fbc3</t>
+        </is>
+      </c>
       <c r="N148" t="inlineStr"/>
-      <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
+      <c r="O148" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q148" t="inlineStr">
         <is>
           <t>none</t>
@@ -11927,39 +11975,39 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Charlie Faulkner</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>callcenter@dukcapil.kemendagri.go.id</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr"/>
+      <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Ditjen Dukcapil, Kemendagri (Data Center Ampera)</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr"/>
-      <c r="G149" t="inlineStr"/>
+          <t>https://dukcapil.kemendagri.go.id</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>08118005373</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>1500537</t>
+        </is>
+      </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://nirmedia.co/dukcapil-hadapi-tantangan-2026-dengan-penguatan-digitalisasi-dan-integritas/ ; contact confirmed via Ditjen Dukcapil official verified account, e.g. https://x.com/dukcapil168/status/1691300522341617665 — Building a Tier 3 data center ('Data Center Ampera') at the IPDN campus on Jalan Ampera, Jakarta, as backbone infrastructure for national population-data digital services, alongside expanded biometric servers and storage capacity</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -11969,16 +12017,28 @@
       </c>
       <c r="K149" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L149" t="n">
-        <v>0</v>
-      </c>
-      <c r="M149" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02878d0e9351</t>
+        </is>
+      </c>
       <c r="N149" t="inlineStr"/>
-      <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
+      <c r="O149" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P149" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>none</t>
@@ -11996,39 +12056,47 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>contactus@bankbsi.co.id</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>I Wayan Pulantara</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>AI Strategy &amp; Innovation Department Head</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Bank Syariah Indonesia (BSI)</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr"/>
-      <c r="G150" t="inlineStr"/>
+          <t>https://www.bankbsi.co.id</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>081584114040</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>14040 / +62 21 80639999</t>
+        </is>
+      </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://teknologi.bisnis.com/read/20260617/84/1981304/bsi-bris-targetkan-infrastruktur-ai-gateway-rampung-tahun-ini ; contact confirmed via BSI verified official account, e.g. https://x.com/bankbsi_id/status/1669650245427544065 — Building an internal 'AI Gateway' computing infrastructure targeted for completion in 2026 to support internal AI applications and prevent shadow AI use, per AI Strategy &amp; Innovation Department Head I Wayan Pulantara at the Indonesia Ethical AI Summit (June 2026)</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12038,16 +12106,28 @@
       </c>
       <c r="K150" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L150" t="n">
-        <v>0</v>
-      </c>
-      <c r="M150" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M150" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02839627f518</t>
+        </is>
+      </c>
       <c r="N150" t="inlineStr"/>
-      <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
+      <c r="O150" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P150" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>none</t>
@@ -12065,39 +12145,35 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Gary Wu</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>CEO</t>
-        </is>
-      </c>
+          <t>info@idc.co.id</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>IDC Indonesia (PT Internetindo Data Centra Indonesia)</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://www.idc.co.id</t>
         </is>
       </c>
       <c r="F151" t="inlineStr"/>
-      <c r="G151" t="inlineStr"/>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>+62 21 526-9988</t>
+        </is>
+      </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.idc.co.id/ — Indonesia's first carrier-neutral data center operator, now operating 6 facilities across Jakarta, Batam, Bandung, Surabaya and Makassar carrying over 95% of Indonesian internet traffic — Indonesia's first carrier-neutral data center operator, now operating 6 facilities across Jakarta, Batam, Bandung, Surabaya and Makassar carrying over 95% of Indonesian internet traffic</t>
         </is>
       </c>
       <c r="J151" t="inlineStr">
@@ -12107,16 +12183,28 @@
       </c>
       <c r="K151" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L151" t="n">
-        <v>0</v>
-      </c>
-      <c r="M151" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M151" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028bc989ed33</t>
+        </is>
+      </c>
       <c r="N151" t="inlineStr"/>
-      <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
+      <c r="O151" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P151" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q151" t="inlineStr">
         <is>
           <t>none</t>
@@ -12134,39 +12222,35 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Ken Patchett</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>VP of Data Center Infrastructure</t>
-        </is>
-      </c>
+          <t>marketing@ag-it.com</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr"/>
+      <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Astragraphia Information Technology (AGIT)</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://www.ag-it.com</t>
         </is>
       </c>
       <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>(021) 2924 1177</t>
+        </is>
+      </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.itworks.id/53011/lewat-anak-usaha-astra-graphia-berencana-perkuat-bisnis-data-center.html ; contact confirmed via https://www.ag-it.com/contact-us — Astra Graphia's IT subsidiary AGIT is expanding its data center business and partnering with HPE and Equinix to build AI-based private cloud infrastructure for the Indonesian market</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12176,16 +12260,28 @@
       </c>
       <c r="K152" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L152" t="n">
-        <v>0</v>
-      </c>
-      <c r="M152" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028a5a72f66f</t>
+        </is>
+      </c>
       <c r="N152" t="inlineStr"/>
-      <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
+      <c r="O152" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P152" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
       <c r="Q152" t="inlineStr">
         <is>
           <t>none</t>
@@ -12199,6 +12295,854 @@
       </c>
       <c r="T152" t="inlineStr"/>
       <c r="U152" t="inlineStr"/>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>marketing@nongsadigital.com</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr"/>
+      <c r="C153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>Nongsa Digital Park (Citramas Group)</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>https://nongsadigital.com</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>+62 778 7100 673</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>web_research: https://nongsadigital.com/dc-hub-ndp/8-data-centre-infrastructure-nongsa-digital-park ; contact confirmed via https://nongsadigital.com/contact-us/ — NDP1 facility at Nongsa Digital Park (Batam) is designed for high-density enterprise, cloud, and AI workloads, with planned IT capacity of 120MW, hosting multiple data center operators (BW Digital, DayOne, Golden Digital Gateway, Racks Central) on its own park infrastructure</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L153" t="n">
+        <v>1</v>
+      </c>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>gmail:1a0f02876c4ba0c6</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P153" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R153" t="inlineStr"/>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T153" t="inlineStr"/>
+      <c r="U153" t="inlineStr"/>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>marketingicp@iconpln.co.id</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr"/>
+      <c r="C154" t="inlineStr"/>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>PLN Icon Plus (PT Indonesia Comnets Plus)</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>https://www.plniconplus.co.id</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr"/>
+      <c r="H154" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>web_research: https://listrikindonesia.com/detail/14093/energi-bersih-pln-icon-plus-siap-dukung-proyek-data-center-indonesia ; contact confirmed via the company's own site, https://lights.iconpln.co.id/article/37 (iconpln.co.id and plniconplus.co.id are the same company under its PLN Icon Plus rebrand, per https://iconews.iconpln.co.id/rebranding-pln-icon-plus-setting-tone-from-the-top/) — PLN Icon Plus (ICON+), PLN's telecom/data center subsidiary, states its commitment to supporting green data center development in Indonesia and operates its own DC2 data center facility amid rising AI-driven power and cooling demand</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K154" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L154" t="n">
+        <v>1</v>
+      </c>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028a241d929f</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P154" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R154" t="inlineStr"/>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T154" t="inlineStr"/>
+      <c r="U154" t="inlineStr"/>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>noc@napinfo.co.id</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>Matrix NAP Info (PT NAP Info Lintas Nusa)</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>https://www.napinfo.co.id</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>1-500-787 / +62 21 3970 1787</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>web_research: https://napinfo.co.id/highlights/article/id/matrix-nap-info-jalin-kerja-sama-strategis-dengan-digital-realty-bersama-untuk-perkuat-ekosistem-infrastruktur-digital-nasional ; contact confirmed via https://www.napinfo.co.id/contact-us — Matrix NAP Info operates its own Matrix Data Center and struck a strategic partnership with Digital Realty Bersama to strengthen Jakarta data center interconnection for AI/cloud growth</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L155" t="n">
+        <v>1</v>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028620d291fb</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr"/>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R155" t="inlineStr"/>
+      <c r="S155" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T155" t="inlineStr"/>
+      <c r="U155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>support@lintasarta.co.id</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr"/>
+      <c r="C156" t="inlineStr"/>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>Lintasarta (PT Aplikanusa Lintasarta)</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>https://www.lintasarta.net</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>08561114052</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>14052 / +62 21 80669499</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>web_research: https://freehire.me/jobs/cloud-data-center-engineer-gpu-openstack-lintasarta-qdsgh4bu and https://freehire.me/jobs/data-center-engineer-l2-lintasarta-qkksv7zy ; contact confirmed via https://www.lintasarta.net/en/contact-us/ — Actively hiring multiple onsite 24x7 Data Center Engineers (L1/L2/L3) for a large-scale GPU cloud built on rack-scale NVIDIA GB200 NVL72, with explicit responsibility for liquid-cooling systems (CDU and secondary loop) operation, monitoring and anomaly handling, alongside its NVIDIA-powered GPU Merdeka sovereign AI GPUaaS cloud already launched</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L156" t="n">
+        <v>1</v>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>gmail:1a0f028365b6c54f</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr"/>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:32:36+00:00</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:33:22+00:00</t>
+        </is>
+      </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R156" t="inlineStr"/>
+      <c r="S156" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T156" t="inlineStr"/>
+      <c r="U156" t="inlineStr"/>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Colovore</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>https://colovore.com</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr"/>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L157" t="n">
+        <v>0</v>
+      </c>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
+      <c r="P157" t="inlineStr"/>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R157" t="inlineStr"/>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T157" t="inlineStr"/>
+      <c r="U157" t="inlineStr"/>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr"/>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L158" t="n">
+        <v>0</v>
+      </c>
+      <c r="M158" t="inlineStr"/>
+      <c r="N158" t="inlineStr"/>
+      <c r="O158" t="inlineStr"/>
+      <c r="P158" t="inlineStr"/>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R158" t="inlineStr"/>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T158" t="inlineStr"/>
+      <c r="U158" t="inlineStr"/>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L159" t="n">
+        <v>0</v>
+      </c>
+      <c r="M159" t="inlineStr"/>
+      <c r="N159" t="inlineStr"/>
+      <c r="O159" t="inlineStr"/>
+      <c r="P159" t="inlineStr"/>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R159" t="inlineStr"/>
+      <c r="S159" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T159" t="inlineStr"/>
+      <c r="U159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr"/>
+      <c r="C160" t="inlineStr"/>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr"/>
+      <c r="G160" t="inlineStr"/>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L160" t="n">
+        <v>0</v>
+      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
+      <c r="O160" t="inlineStr"/>
+      <c r="P160" t="inlineStr"/>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R160" t="inlineStr"/>
+      <c r="S160" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T160" t="inlineStr"/>
+      <c r="U160" t="inlineStr"/>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr"/>
+      <c r="G161" t="inlineStr"/>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I161" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J161" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K161" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L161" t="n">
+        <v>0</v>
+      </c>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
+      <c r="O161" t="inlineStr"/>
+      <c r="P161" t="inlineStr"/>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R161" t="inlineStr"/>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T161" t="inlineStr"/>
+      <c r="U161" t="inlineStr"/>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr"/>
+      <c r="G162" t="inlineStr"/>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L162" t="n">
+        <v>0</v>
+      </c>
+      <c r="M162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
+      <c r="O162" t="inlineStr"/>
+      <c r="P162" t="inlineStr"/>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R162" t="inlineStr"/>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T162" t="inlineStr"/>
+      <c r="U162" t="inlineStr"/>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I163" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J163" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L163" t="n">
+        <v>0</v>
+      </c>
+      <c r="M163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
+      <c r="O163" t="inlineStr"/>
+      <c r="P163" t="inlineStr"/>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T163" t="inlineStr"/>
+      <c r="U163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr"/>
+      <c r="G164" t="inlineStr"/>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I164" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K164" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L164" t="n">
+        <v>0</v>
+      </c>
+      <c r="M164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
+      <c r="O164" t="inlineStr"/>
+      <c r="P164" t="inlineStr"/>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T164" t="inlineStr"/>
+      <c r="U164" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -12211,7 +13155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L195"/>
+  <dimension ref="A1:L199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12552,10 +13496,14 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr">
         <is>
           <t>Jakarta 2 Annex (JKT2A), NTT's third Indonesia facility, delivers 12MW of IT load purpose-built for high-density deployments supporting racks up to 40kW, opening early 2026; no verifiable published email found</t>
@@ -13394,10 +14342,14 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
+        </is>
+      </c>
       <c r="J26" t="inlineStr">
         <is>
           <t>Launched GPU Merdeka, a sovereign AI cloud (GPUaaS) built on NVIDIA H100 SXM GPUs, alongside parent Indosat's $200M AI data center/telco building planned in Surakarta with Nvidia; published contact emails are on the lintasarta.co.id domain (mismatched from the lintasarta.net site the claim was verified on), so routed to contact form only per domain-match rule</t>
@@ -14028,12 +14980,12 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-08T13:13:14.278333+00:00: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.datacomm.co.id and also for a generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue). Not a code bug - left as pending, needs retry from a session/environment without</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
@@ -14212,12 +15164,12 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-09T07:27Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for indosatooredoo.com and www.peruri.co.id, confirming a session-wide policy block, not a site-specific issue, consistent with the last 2 batches). Not a code bug - left as pending, needs retry from a session/environment without this res</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -14672,12 +15624,12 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-10T07:24:33Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.bca.co.id, investor.intiland.com, and the generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue, consistent with the last several batches). Not a code bug - left as pending, need</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -14764,12 +15716,12 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-10T07:24:33Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.bca.co.id, investor.intiland.com, and the generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue, consistent with the last several batches). Not a code bug - left as pending, need</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
@@ -14864,12 +15816,12 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-10T07:24:33Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.bca.co.id, investor.intiland.com, and the generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue, consistent with the last several batches). Not a code bug - left as pending, need</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -15094,12 +16046,12 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-10T07:24:33Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.bca.co.id, investor.intiland.com, and the generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue, consistent with the last several batches). Not a code bug - left as pending, need</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -15140,12 +16092,12 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-10T07:24:33Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for www.bca.co.id, investor.intiland.com, and the generic control host www.google.com, confirming a session-wide policy block, not a site-specific issue, consistent with the last several batches). Not a code bug - left as pending, need</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -20809,7 +21761,7 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
@@ -21219,7 +22171,7 @@
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>2026-09-25 Day 13 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SingHealth row) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for www.singhealth.com.sg:443 moments later. This confir</t>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
@@ -21281,6 +22233,186 @@
       <c r="L195" t="inlineStr">
         <is>
           <t>2026-09-28T02:18:56+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr"/>
+      <c r="B196" t="inlineStr"/>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Epsilon Telecommunications, a KT company</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>https://epsilontel.com</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr"/>
+      <c r="F196" t="inlineStr"/>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>https://epsilontel.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>Epsilon operates its own 12,900 sqft, 500-rack internet data center at New Tech Park, Singapore, integrating AI service infrastructure for parent KT (GiGA Genie).</t>
+        </is>
+      </c>
+      <c r="K196" t="inlineStr">
+        <is>
+          <t>https://baxtel.com/data-center/epsilon-singapore-new-tech-park and https://www.datacenters.com/epsilon-telecommunications-singapore</t>
+        </is>
+      </c>
+      <c r="L196" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:12:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr"/>
+      <c r="B197" t="inlineStr"/>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>SC Zeus Data Centers</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>https://www.zeusdatacenters.com</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr"/>
+      <c r="F197" t="inlineStr"/>
+      <c r="G197" t="inlineStr">
+        <is>
+          <t>https://www.zeusdatacenters.com/contact</t>
+        </is>
+      </c>
+      <c r="H197" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I197" t="inlineStr">
+        <is>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
+        </is>
+      </c>
+      <c r="J197" t="inlineStr">
+        <is>
+          <t>Singapore-headquartered AI-ready data center developer/operator (SC Capital Partners platform, HQ 2 Nassim Road, Singapore) building scalable, high-density facilities engineered for liquid-cooling readiness and next-generation cooling technologies; COO AC Lee is a former Chayora technical director, a genuinely facilities-technical hire.</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>https://sustainabilitymag.com/sustainability/how-sc-zeus-is-building-ai-ready-data-centres-in-apac and https://www.mingtiandi.com/real-estate/data-centres/sc-zeus-teams-with-softbank-unit-for-se-asia-data-centre-push/</t>
+        </is>
+      </c>
+      <c r="L197" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:12:02+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr"/>
+      <c r="B198" t="inlineStr"/>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Centre for Climate Research Singapore (CCRS) / Meteorological Service Singapore</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>https://ccrs.weather.gov.sg</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr"/>
+      <c r="F198" t="inlineStr"/>
+      <c r="G198" t="inlineStr">
+        <is>
+          <t>https://ccrs.weather.gov.sg/contact-us</t>
+        </is>
+      </c>
+      <c r="H198" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I198" t="inlineStr"/>
+      <c r="J198" t="inlineStr">
+        <is>
+          <t>CCRS runs an on-site HPC supercomputing cluster (Utama/SINGV) for weather and climate research.</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr">
+        <is>
+          <t>https://ccrs.weather.gov.sg/high-performance-computing/</t>
+        </is>
+      </c>
+      <c r="L198" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:15:22+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr"/>
+      <c r="B199" t="inlineStr"/>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>AI Singapore (AISG)</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>https://aisingapore.org</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr"/>
+      <c r="F199" t="inlineStr"/>
+      <c r="G199" t="inlineStr">
+        <is>
+          <t>https://aisingapore.org/home/contact-us/</t>
+        </is>
+      </c>
+      <c r="H199" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I199" t="inlineStr">
+        <is>
+          <t>2026-09-30 Day 16 run: NOT filled. Confirmed via curl through the agent proxy (recentRelayFailures showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443, a generic control host) and a live fill_contact_form() test against this batch (SC Zeus Data Centers row, https://www.zeusdatacenters.com/contact) which returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint recording the same connect_rejected / 403-to-CONNECT failure for w</t>
+        </is>
+      </c>
+      <c r="J199" t="inlineStr">
+        <is>
+          <t>AISG runs its own on-premise GPU/FPGA compute cluster and has publicly cited difficulty securing guaranteed, energy-efficient large-scale GPU capacity for LLM training given Singapore climate, leading it to partner with Firmus for additional capacity.</t>
+        </is>
+      </c>
+      <c r="K199" t="inlineStr">
+        <is>
+          <t>https://firmus.co/newsroom/ai-singapore-firmus-case-study — AISG operates its own on-premise GPU/FPGA cluster (32 NVIDIA V100 GPUs, 6 FPGAs) and partnered with Firmus Technologies for guaranteed large-scale, energy-efficient GPU clusters to train SEA-LION LLMs after citing operational-cost and infrastructure-complexity challenges tied to Singapore climate</t>
+        </is>
+      </c>
+      <c r="L199" t="inlineStr">
+        <is>
+          <t>2026-09-30T02:17:08+00:00</t>
         </is>
       </c>
     </row>
@@ -21295,7 +22427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -21754,6 +22886,82 @@
         </is>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Press/Media Relations</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Amazon Web Services (AWS) Singapore</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>amazon-pr@amazon.com</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>web_research: https://www.aboutamazon.sg/news/aws/aws-deepens-commitment-to-singapore-with-additional-sg-12-billion-investment-by-2028-and-new-flagship-ai-programme — AWS committed an additional S$12 billion (to over S$23 billion total by 2028) in Singapore cloud/AI infrastructure; Dr Saji PK, Director of Infrastructure Operations APMEA, is based in Singapore and is the actual relevant decision-maker named in the source, but no email for him was found.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Not a fabrication issue (email is real, verified, domain-matched) - a channel-fit issue: amazon-pr@amazon.com is AWS's global press/media office, not a sales or general business contact. The source itself names the real relevant decision-maker (Dr Saji PK) but no email exists for him - sending a vendor pitch to a press inbox is a poor fit and was held out by the sending agent rather than sent as a substitute. Retry once a real contact for Dr Saji PK (or another AWS Singapore infrastructure contact) is found.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>General Enquiries (CCRS, under Prof Dale Barker, Director)</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Centre for Climate Research Singapore (CCRS) / Meteorological Service Singapore</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>nea_ccrs_engage@nea.gov.sg</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>web_research: https://ccrs.weather.gov.sg/high-performance-computing/ — CCRS operates the Utama HPE Cray EX supercomputer plus the newer SINGV system for national weather/climate modelling; Prof Dale Barker is CCRS's Director, the actual relevant decision-maker named in the source, but no email for him was found.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Not a fabrication issue (email is real, verified, published on CCRS's own contact page) - a channel-fit issue: nea_ccrs_engage@nea.gov.sg is a .gov.sg general public-enquiries alias for weather/climate services, not a business contact channel. Sending a commercial vendor pitch into a government general-enquiries line is a different risk category than a company's own sales/info inbox, and was held out by the sending agent rather than sent as a substitute. Retry once a real contact for Prof Dale Barker (or another CCRS technical/facilities contact) is found.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U164"/>
+  <dimension ref="A1:U181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12607,39 +12607,39 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>info@colovore.com</t>
+          <t>christina.koh@sttelemediagdc.com</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Jeffrey Springborn</t>
+          <t>Christina Koh</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Head, Group Marketing and Communications</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Colovore</t>
+          <t>ST Telemedia Global Data Centres</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>https://colovore.com</t>
+          <t>https://www.sttelemediagdc.com</t>
         </is>
       </c>
       <c r="F157" t="inlineStr"/>
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+          <t>web_research: https://www.sttelemediagdc.com/newsroom/st-telemedia-global-data-centres-announces-new-executive-appointments — STT GDC operates multiple Singapore data centre campuses and is developing the FutureGrid HVDC-AI testbed; Christina Koh is named alongside Chow Yi as the company's own media contact across its newsroom press releases.</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
@@ -12649,16 +12649,28 @@
       </c>
       <c r="K157" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L157" t="n">
-        <v>0</v>
-      </c>
-      <c r="M157" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547310677735</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
-      <c r="O157" t="inlineStr"/>
-      <c r="P157" t="inlineStr"/>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q157" t="inlineStr">
         <is>
           <t>none</t>
@@ -12676,39 +12688,35 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>press@nscale.com</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Nidhi Chappell</t>
-        </is>
-      </c>
+          <t>contactus@synapxe.sg</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr"/>
       <c r="C158" t="inlineStr">
         <is>
-          <t>President, AI Infrastructure</t>
+          <t>General Enquiries</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Nscale</t>
+          <t>Synapxe</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>https://nscale.com</t>
+          <t>https://www.synapxe.sg</t>
         </is>
       </c>
       <c r="F158" t="inlineStr"/>
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+          <t>web_research: https://www.synapxe.sg/healthtech/cloud/h-cloud — Synapxe, Singapore's national HealthTech agency, built H-Cloud to rationalise and consolidate local hospital data centres into a modernised, nation-wide private cloud serving all public hospitals, specialty centres, polyclinics and nursing homes.</t>
         </is>
       </c>
       <c r="J158" t="inlineStr">
@@ -12718,16 +12726,28 @@
       </c>
       <c r="K158" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L158" t="n">
-        <v>0</v>
-      </c>
-      <c r="M158" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472d8f8548c</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
-      <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>none</t>
@@ -12745,39 +12765,35 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>press@coreweave.com</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Michael Intrator</t>
-        </is>
-      </c>
+          <t>corpcomms@ocbc.com</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr"/>
       <c r="C159" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Group Brand and Communications</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>CoreWeave</t>
+          <t>OCBC Bank</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>https://coreweave.com</t>
+          <t>https://www.ocbc.com</t>
         </is>
       </c>
       <c r="F159" t="inlineStr"/>
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapores-ocbc-bank-to-introduce-rack-based-data-center-cooling/ — OCBC operates its own S$240M purpose-built data center in Singapore (first purpose-built DC owned by a Singapore bank) and is implementing a rack-based cooling system to cut emissions by 400+ tons/year; separately hiring a Data Centre Facilities Engineer and a Lead, Data Centre Facilities Management (AVP/VP) for the Loyang facility.</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
@@ -12787,16 +12803,28 @@
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L159" t="n">
-        <v>0</v>
-      </c>
-      <c r="M159" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5471f98cfb7a</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
-      <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q159" t="inlineStr">
         <is>
           <t>none</t>
@@ -12814,27 +12842,35 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>deepinfra@scratchmm.com</t>
+          <t>investor.relations@keppeldcreit.com</t>
         </is>
       </c>
       <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Investor Relations</t>
+        </is>
+      </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>DeepInfra</t>
+          <t>Keppel DC REIT</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>https://deepinfra.com</t>
+          <t>https://www.keppeldcreit.com</t>
         </is>
       </c>
       <c r="F160" t="inlineStr"/>
       <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+          <t>web_research: https://www.keppeldcreit.com/en/investor-relations/ir-contact/ — Keppel DC REIT is participating in the Keppel DC Singapore 9 build at the AI-ready Genting Lane campus (construction start mid-2026, 19MW), alongside Keppel Data Centre Funds II and III.</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
@@ -12844,16 +12880,28 @@
       </c>
       <c r="K160" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L160" t="n">
-        <v>0</v>
-      </c>
-      <c r="M160" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54728c833da5</t>
+        </is>
+      </c>
       <c r="N160" t="inlineStr"/>
-      <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q160" t="inlineStr">
         <is>
           <t>none</t>
@@ -12871,39 +12919,39 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>hello@edgemode.io</t>
+          <t>ir_industrial@mapletree.com.sg</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Charlie Faulkner</t>
+          <t>Cheng Mui Lian</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Investor Relations and Sustainability</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>EdgeMode Inc.</t>
+          <t>Mapletree Industrial Trust</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>https://edgemode.io</t>
+          <t>https://www.mapletreeindustrialtrust.com</t>
         </is>
       </c>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+          <t>web_research: https://www.mapletreeindustrialtrust.com/about-us/ — Mapletree Industrial Trust's data-centre portfolio is roughly 57% of its S$8.3B total AUM, including the purpose-built 7 Tai Seng Drive facility (fully leased to Equinix Singapore) and the Sunview Drive data centre in Singapore, plus 13 data centres held via JV with Mapletree Investments in North America.</t>
         </is>
       </c>
       <c r="J161" t="inlineStr">
@@ -12913,16 +12961,28 @@
       </c>
       <c r="K161" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
-      </c>
-      <c r="M161" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54724a989642</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
-      <c r="O161" t="inlineStr"/>
-      <c r="P161" t="inlineStr"/>
+      <c r="O161" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q161" t="inlineStr">
         <is>
           <t>none</t>
@@ -12940,39 +13000,39 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>press@edgeconnex.com</t>
+          <t>lauren.crystal@smc.co</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Don MacNeil</t>
+          <t>Lauren Crystal</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Chief Revenue Officer</t>
+          <t>Head of Communications</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>EdgeConneX</t>
+          <t>Sustainable Metal Cloud (SMC)</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>https://edgeconnex.com</t>
+          <t>https://smc.co</t>
         </is>
       </c>
       <c r="F162" t="inlineStr"/>
       <c r="G162" t="inlineStr"/>
       <c r="H162" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/singapores-sustainable-metal-cloud-outlines-global-expansion-plans/ — Singapore-founded and HQ'd SMC runs fully immersion-cooled NVIDIA GPU clusters (SIN01/SIN02 availability zones at STT GDC) for AI training/inference, achieving a PUE of 1.03 via its HyperCube immersion-cooling technology.</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
@@ -12982,16 +13042,28 @@
       </c>
       <c r="K162" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
-      </c>
-      <c r="M162" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472318d99a1</t>
+        </is>
+      </c>
       <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>none</t>
@@ -13009,39 +13081,39 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>press@fluidstack.io</t>
+          <t>luana.low@gf.com</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Gary Wu</t>
+          <t>Luana Low</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>CEO</t>
+          <t>Deputy Director, Corporate Communications (Public Relations, Singapore)</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Fluidstack</t>
+          <t>GlobalFoundries Singapore</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>https://fluidstack.io</t>
+          <t>https://gf.com</t>
         </is>
       </c>
       <c r="F163" t="inlineStr"/>
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+          <t>web_research: https://www.edb.gov.sg/en/about-edb/media-releases-publications/globalfoundries-opens-us4-billion-expansion-facility-in-singapore.html — GlobalFoundries officially opened a US$4B expansion fab in Singapore (23,000 sqm), its most advanced Singapore semiconductor facility to date, raising overall Singapore capacity to ~1.5M 300mm wafers/year.</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
@@ -13051,16 +13123,28 @@
       </c>
       <c r="K163" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L163" t="n">
-        <v>0</v>
-      </c>
-      <c r="M163" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M163" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547267649121</t>
+        </is>
+      </c>
       <c r="N163" t="inlineStr"/>
-      <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
+      <c r="O163" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P163" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>none</t>
@@ -13078,39 +13162,39 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>pr@lambda.ai</t>
+          <t>nola.pocock@colt.net</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Ken Patchett</t>
+          <t>Nola Pocock</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>VP of Data Center Infrastructure</t>
+          <t>VP, Global Communications (Colt Group)</t>
         </is>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Lambda, Inc.</t>
+          <t>Colt Data Centre Services Singapore</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>https://lambda.ai</t>
+          <t>https://www.coltdatacentres.net</t>
         </is>
       </c>
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+          <t>web_research: https://www.colt.net/resources/insights/connectivity-for-mc-digital-realty-data-centre — Colt operates a Singapore data center at 29A International Business Park Road; Colt Group's own Global Communications lead (covering both Colt Technology Services and Colt Data Centre Services announcements) is Nola Pocock, consistently listed as press contact on colt.net data-centre-related releases.</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
@@ -13120,16 +13204,28 @@
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>unsent</t>
+          <t>sent</t>
         </is>
       </c>
       <c r="L164" t="n">
-        <v>0</v>
-      </c>
-      <c r="M164" t="inlineStr"/>
+        <v>1</v>
+      </c>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472e0be35ce</t>
+        </is>
+      </c>
       <c r="N164" t="inlineStr"/>
-      <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
+      <c r="O164" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P164" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>none</t>
@@ -13143,6 +13239,1283 @@
       </c>
       <c r="T164" t="inlineStr"/>
       <c r="U164" t="inlineStr"/>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>tanya.netto@oracle.com</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Tanya Netto</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Communications &amp; PR Lead, ASEAN</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Oracle Cloud Infrastructure Singapore</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>https://www.oracle.com/sg/</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr"/>
+      <c r="G165" t="inlineStr"/>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>web_research: https://blogs.oracle.com/cloud-infrastructure/oracle-opens-second-cloud-region-in-singapore — Oracle opened a second Oracle Cloud Region in Singapore to meet rapidly growing AI/cloud demand, enabling customers to migrate mission-critical AI workloads.</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K165" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L165" t="n">
+        <v>1</v>
+      </c>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5472bfb7b7c4</t>
+        </is>
+      </c>
+      <c r="N165" t="inlineStr"/>
+      <c r="O165" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:14+00:00</t>
+        </is>
+      </c>
+      <c r="P165" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:45+00:00</t>
+        </is>
+      </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T165" t="inlineStr"/>
+      <c r="U165" t="inlineStr"/>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>ai.center@binus.edu</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Prof. Bens Pardamean</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Director, Artificial Intelligence R&amp;D Center (AIRDC)</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>BINUS University (AI R&amp;D Center)</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>https://research.binus.ac.id/airdc/</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>+62.21 530 0244</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>web_research: https://research.binus.ac.id/airdc/ ; https://binus.ac.id/2019/04/binus-dirikan-pusat-riset-artificial-intelligence/ — BINUS University AI R&amp;D Center (AIRDC), founded via NVIDIA-BINUS collaboration, operates a GPU cluster for AI research and industry collaboration, directed by Prof. Bens Pardamean</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K166" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L166" t="n">
+        <v>1</v>
+      </c>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475eb87633c</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
+      <c r="O166" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P166" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T166" t="inlineStr"/>
+      <c r="U166" t="inlineStr"/>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>corsec@pancaanugrahwisesa.com</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr"/>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Corporate Secretary</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>PT NexAI Digital Infrastruktur Tbk (MGLV, formerly PT Panca Anugrah Wisesa Tbk)</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>http://pancaanugrahwisesa.com</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr"/>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>+62 21 718 0349</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>web_research: https://harianenergi.com/detail/1440376/dapat-restu-rupslb-nexai-mantap-garap-bisnis-ai-data-center ; https://bisnisinsight.com/detail/921750/nexai-mglv-resmi-masuk-bisnis-ai-data-center-usai-restu-rupslb — IDX-listed PT NexAI Digital Infrastruktur Tbk (MGLV) received shareholder approval (RUPSLB, July 2026) to formally pivot its core business from furniture/household equipment to AI-based data center infrastructure</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K167" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L167" t="n">
+        <v>1</v>
+      </c>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475ddf337f9</t>
+        </is>
+      </c>
+      <c r="N167" t="inlineStr"/>
+      <c r="O167" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R167" t="inlineStr"/>
+      <c r="S167" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T167" t="inlineStr"/>
+      <c r="U167" t="inlineStr"/>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>info@edgnex.com</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr"/>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>DAMAC Digital (EDGNEX Cikarang AI Campus)</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>https://www.edgnex.com</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr"/>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>+971 4 373 2 373</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgnex.com/contact/ ; https://www.idnfinancials.com/news/56071/dubais-damac-digital-to-build-usd-2-3-billion-data-centre-in-cikarang — DAMAC Digital (EDGNEX) is building a $2.3B AI data center in Greenland International Industrial Center, Pasirranji, Bekasi (JKT02/Cikarang AI Campus), designed for high-density AI racks with a projected capacity exceeding 144MW, first phase slated for Q3 2026 completion</t>
+        </is>
+      </c>
+      <c r="J168" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L168" t="n">
+        <v>1</v>
+      </c>
+      <c r="M168" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54759960550c</t>
+        </is>
+      </c>
+      <c r="N168" t="inlineStr"/>
+      <c r="O168" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R168" t="inlineStr"/>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T168" t="inlineStr"/>
+      <c r="U168" t="inlineStr"/>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>infodgx@gunadarma.ac.id</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Prof. Dr. Detty Purnamasari</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Head, AI and Robotics Development Team (DGX Development Team)</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Universitas Gunadarma</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>https://www.hpc-hub.gunadarma.ac.id</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>+628-1212-9955-61</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr"/>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>web_research: https://www.praktikum-hpc.gunadarma.ac.id/kontak/tim-pengembangan-dgx ; https://www.hpc-hub.gunadarma.ac.id/kontak — Prof. Dr. Detty Purnamasari heads the DGX Development Team overseeing Gunadarma University NVIDIA DGX-1 and DGX A100 supercomputers at its dedicated HPC/DGX hub for AI and data-intensive research</t>
+        </is>
+      </c>
+      <c r="J169" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L169" t="n">
+        <v>1</v>
+      </c>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54761cbada73</t>
+        </is>
+      </c>
+      <c r="N169" t="inlineStr"/>
+      <c r="O169" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:58+00:00</t>
+        </is>
+      </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R169" t="inlineStr"/>
+      <c r="S169" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T169" t="inlineStr"/>
+      <c r="U169" t="inlineStr"/>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>inquiry@indokeppeldc.com</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr"/>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>IndoData Data Center (Salim Group, formerly IndoKeppel Data Centres)</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>https://indokeppeldc.com</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>+622139520140</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/keppel-salim-group-launch-data-center-in-bogor-indonesia/ ; https://w.media/indokeppel-sees-significant-data-center-opportunities-in-indonesia/ — IndoKeppel Data Centre 1 (IKDC1) in Bogor, a Salim Group/Keppel JV (Salim Group took full ownership in Dec 2025 and relaunched as IndoData Data Center), is a 7-hectare campus planned for 50MW+ of IT power across 3 phases, featuring N+1 water-cooled chillers and dual water supply, with a stated strategic focus on AI and hyperscale computing; IndoData has up to 500MW of power capacity secured under contract with PLN</t>
+        </is>
+      </c>
+      <c r="J170" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L170" t="n">
+        <v>1</v>
+      </c>
+      <c r="M170" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475268bea7a</t>
+        </is>
+      </c>
+      <c r="N170" t="inlineStr"/>
+      <c r="O170" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T170" t="inlineStr"/>
+      <c r="U170" t="inlineStr"/>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>inquiry@lgsinarmas.com</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr"/>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>General/Corporate Contact</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LG Sinar Mas Technology Solutions (LG CNS / SM+ JV)</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>https://www.lgsinarmas.com</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr"/>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>+62-21-31990258</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr">
+        <is>
+          <t>web_research: https://www.sinarmas.com/blog/?p=4168 ; https://www.lgsinarmas.com/ — LG Sinar Mas, a joint venture between South Korean DC services provider LG CNS and Sinar Mas-backed PT SMPlus Digital Investment (SM+), is developing a US$300M AI-based data center on a 44,195 sqm facility in Menteng Atas, Setiabudi, Jakarta, scheduled to begin operations in H2 2026</t>
+        </is>
+      </c>
+      <c r="J171" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L171" t="n">
+        <v>1</v>
+      </c>
+      <c r="M171" t="inlineStr">
+        <is>
+          <t>gmail:1a0f54756301e30b</t>
+        </is>
+      </c>
+      <c r="N171" t="inlineStr"/>
+      <c r="O171" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T171" t="inlineStr"/>
+      <c r="U171" t="inlineStr"/>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>sales@dhs-dc.com</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Stanley Go</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Operations Manager</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Digital Hyperspace Indonesia (DHI)</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>https://dh-indonesia.com</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr"/>
+      <c r="G172" t="inlineStr"/>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>web_research: https://dh-indonesia.com/contact/ ; https://dh-indonesia.com/about/ — PT Digital Hyperspace Indonesia operates DHI, a Tier III hyperscale data center in Pasirranji, Central Cikarang, Bekasi Regency, West Java, with an initial 20MW IT load (1,200,000 SF purpose-built facility), financed by the GTC Fund and co-investors; Operations Manager Stanley Go is ASHRAE BCxP-certified</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L172" t="n">
+        <v>1</v>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>gmail:1a0f547554b25881</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="O172" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R172" t="inlineStr"/>
+      <c r="S172" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T172" t="inlineStr"/>
+      <c r="U172" t="inlineStr"/>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>selena.sheikh@princetondg.com</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Selena Sheikh</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Corporate Communications Associate Director, Public Relations</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Princeton Digital Group (PDG) Indonesia</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>https://princetondg.com</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr">
+        <is>
+          <t>web_research: https://princetondg.com/newsroom/princeton-digital-group-launches-its-22mw-hyperscale-data-center-in-greater-jakarta-2/ — PDG operates JC1 (6MW) and JC2 (22MW hyperscale, launched) data centers in Cibitung, Greater Jakarta, and agreed to acquire a 70%% stake in XL Axiata Indonesian data centers (5 sites) with US$100M growth capital committed to expand capacity</t>
+        </is>
+      </c>
+      <c r="J173" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>sent</t>
+        </is>
+      </c>
+      <c r="L173" t="n">
+        <v>1</v>
+      </c>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>gmail:1a0f5475a8ba596c</t>
+        </is>
+      </c>
+      <c r="N173" t="inlineStr"/>
+      <c r="O173" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:30+00:00</t>
+        </is>
+      </c>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:24:57+00:00</t>
+        </is>
+      </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R173" t="inlineStr"/>
+      <c r="S173" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T173" t="inlineStr"/>
+      <c r="U173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>info@colovore.com</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Jeffrey Springborn</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Colovore</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>https://colovore.com</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr"/>
+      <c r="G174" t="inlineStr"/>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/colovore-secures-925m-debt-facility-from-blackstone-for-liquid-cooled-data-center-build-out/ — Secured a $925M Blackstone debt facility to build liquid-cooled colocation supporting up to 250kW per rack via direct-to-chip and rear-door cooling, expanding into Reno, Chicago, and Austin</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K174" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L174" t="n">
+        <v>0</v>
+      </c>
+      <c r="M174" t="inlineStr"/>
+      <c r="N174" t="inlineStr"/>
+      <c r="O174" t="inlineStr"/>
+      <c r="P174" t="inlineStr"/>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R174" t="inlineStr"/>
+      <c r="S174" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T174" t="inlineStr"/>
+      <c r="U174" t="inlineStr"/>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>press@nscale.com</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Nidhi Chappell</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>President, AI Infrastructure</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>Nscale</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>https://nscale.com</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr"/>
+      <c r="G175" t="inlineStr"/>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>GB</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr">
+        <is>
+          <t>web_research: https://www.prnewswire.com/news-releases/whitefiber-and-nscale-announce-10-year-40-mw-colocation-agreement-representing-approximately-865-million-in-total-contract-value-at-nc-1-ai-data-center-campus-302646399.html — Anchor tenant taking 40MW of critical IT load at WhiteFiber's 150kW/cabinet NC-1 campus (~$865M contract), alongside its own Stargate Norway project targeting 100,000 GPUs by 2026</t>
+        </is>
+      </c>
+      <c r="J175" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K175" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L175" t="n">
+        <v>0</v>
+      </c>
+      <c r="M175" t="inlineStr"/>
+      <c r="N175" t="inlineStr"/>
+      <c r="O175" t="inlineStr"/>
+      <c r="P175" t="inlineStr"/>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R175" t="inlineStr"/>
+      <c r="S175" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T175" t="inlineStr"/>
+      <c r="U175" t="inlineStr"/>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>press@coreweave.com</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Michael Intrator</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>CoreWeave</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>https://coreweave.com</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I176" t="inlineStr">
+        <is>
+          <t>web_research: https://www.businesswire.com/news/home/20250715975958/en/CoreWeave-Announces-Multi-Billion-Dollar-Commitment-to-AI-Infrastructure-in-Pennsylvania — Committing up to $6B to a new AI data center in Lancaster, PA, an initial 100MW facility with potential to expand to 300MW</t>
+        </is>
+      </c>
+      <c r="J176" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K176" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L176" t="n">
+        <v>0</v>
+      </c>
+      <c r="M176" t="inlineStr"/>
+      <c r="N176" t="inlineStr"/>
+      <c r="O176" t="inlineStr"/>
+      <c r="P176" t="inlineStr"/>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R176" t="inlineStr"/>
+      <c r="S176" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T176" t="inlineStr"/>
+      <c r="U176" t="inlineStr"/>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>deepinfra@scratchmm.com</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr"/>
+      <c r="C177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DeepInfra</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>https://deepinfra.com</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr"/>
+      <c r="G177" t="inlineStr"/>
+      <c r="H177" t="inlineStr"/>
+      <c r="I177" t="inlineStr">
+        <is>
+          <t>web_research: https://www.theglobeandmail.com/investing/markets/markets-news/GlobeNewswire/3184601/deepinfra-expands-ai-inference-capacity-with-first-international-data-center-in-toronto/ — Opened its first international data center, a 1.7MW facility in Toronto housing more than 1,000 NVIDIA Blackwell B300 GPUs for AI inference</t>
+        </is>
+      </c>
+      <c r="J177" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L177" t="n">
+        <v>0</v>
+      </c>
+      <c r="M177" t="inlineStr"/>
+      <c r="N177" t="inlineStr"/>
+      <c r="O177" t="inlineStr"/>
+      <c r="P177" t="inlineStr"/>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R177" t="inlineStr"/>
+      <c r="S177" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T177" t="inlineStr"/>
+      <c r="U177" t="inlineStr"/>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>hello@edgemode.io</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Charlie Faulkner</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>EdgeMode Inc.</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>https://edgemode.io</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr"/>
+      <c r="G178" t="inlineStr"/>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>web_research: https://www.stocktitan.net/news/EDGM/edge-mode-mora-town-council-and-other-developers-of-the-dc-malpica-0l7s578vv02x.html — Presented an estimated EUR3B 'DC Malpica' AI data center campus plan in Mora, Spain -- two 150,000 sqm data centers totaling 300MW -- via its BLACK AI venture with BlackBerry AIF</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L178" t="n">
+        <v>0</v>
+      </c>
+      <c r="M178" t="inlineStr"/>
+      <c r="N178" t="inlineStr"/>
+      <c r="O178" t="inlineStr"/>
+      <c r="P178" t="inlineStr"/>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R178" t="inlineStr"/>
+      <c r="S178" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T178" t="inlineStr"/>
+      <c r="U178" t="inlineStr"/>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>press@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Don MacNeil</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Chief Revenue Officer</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>EdgeConneX</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>https://edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
+      <c r="H179" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I179" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edgeconnex.com/news/press-releases/edgeconnex-and-lambda-to-build-ai-factory-in-chicago-with-industry-leading-high-density-data-center-infrastructure/ — Building 30+MW of high-density data center infrastructure in Chicago and Atlanta for Lambda, combining direct liquid-to-chip and air cooling for AI workloads</t>
+        </is>
+      </c>
+      <c r="J179" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K179" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L179" t="n">
+        <v>0</v>
+      </c>
+      <c r="M179" t="inlineStr"/>
+      <c r="N179" t="inlineStr"/>
+      <c r="O179" t="inlineStr"/>
+      <c r="P179" t="inlineStr"/>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R179" t="inlineStr"/>
+      <c r="S179" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T179" t="inlineStr"/>
+      <c r="U179" t="inlineStr"/>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>press@fluidstack.io</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Gary Wu</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>CEO</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Fluidstack</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>https://fluidstack.io</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I180" t="inlineStr">
+        <is>
+          <t>web_research: https://investors.terawulf.com/news-events/press-releases/detail/114/terawulf-announces-fluidstack-expansion-with-160-mw-cb-5 — Expanded contracted critical IT load to roughly 360MW at TeraWulf's Lake Mariner HPC campus (adding a new 160MW CB-5 building) to support AI/HPC compute</t>
+        </is>
+      </c>
+      <c r="J180" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L180" t="n">
+        <v>0</v>
+      </c>
+      <c r="M180" t="inlineStr"/>
+      <c r="N180" t="inlineStr"/>
+      <c r="O180" t="inlineStr"/>
+      <c r="P180" t="inlineStr"/>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R180" t="inlineStr"/>
+      <c r="S180" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T180" t="inlineStr"/>
+      <c r="U180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>pr@lambda.ai</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Ken Patchett</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>VP of Data Center Infrastructure</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Lambda, Inc.</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>https://lambda.ai</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr"/>
+      <c r="G181" t="inlineStr"/>
+      <c r="H181" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="I181" t="inlineStr">
+        <is>
+          <t>web_research: https://lambda.ai/blog/lambda-edgeconnex-dc-pr — Building gigawatt-scale 'AI Factories' with a stated target of 3GW of liquid-cooled data center capacity and 1M+ NVIDIA GPUs, including a multibillion-dollar Microsoft infrastructure deal</t>
+        </is>
+      </c>
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K181" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L181" t="n">
+        <v>0</v>
+      </c>
+      <c r="M181" t="inlineStr"/>
+      <c r="N181" t="inlineStr"/>
+      <c r="O181" t="inlineStr"/>
+      <c r="P181" t="inlineStr"/>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T181" t="inlineStr"/>
+      <c r="U181" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -13155,7 +14528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L199"/>
+  <dimension ref="A1:L200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13542,10 +14915,14 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J8" t="inlineStr">
         <is>
           <t>LG CNS's first AI data center build in Indonesia, via JV with Sinar Mas: a ~$300M (Rp4.6T) facility under construction in Jakarta's Kuningan CBD, due 2027; no dedicated contact page/email found</t>
@@ -13630,10 +15007,14 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J10" t="inlineStr">
         <is>
           <t>Acquired 240MW of powered land for a new JC4 hyperscale campus in Bekasi (Greater Jakarta), bringing PDG's Indonesia portfolio to 400MW, following groundbreaking on the 120MW AI-ready JC3 campus</t>
@@ -14430,10 +15811,14 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J28" t="inlineStr">
         <is>
           <t>Building a $2.3B, 144MW AI-focused data center in Cikarang, Bekasi (Greenland International Industrial Center) designed for high-density AI racks with a target PUE of 1.32, phase one due for service by December 2026; no independently-verified published business email found, only a contact form</t>
@@ -15532,12 +16917,12 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-09T07:27Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT' for indosatooredoo.com and www.peruri.co.id, confirming a session-wide policy block, not a site-specific issue, consistent with the last 2 batches). Not a code bug - left as pending, needs retry from a session/environment without this res</t>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -16362,12 +17747,12 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-11T07:26:51Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403 for www.morarepublic.co.id:443; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT', confirming a session-wide policy block, not a site-specific issue, consistent with prior batches). Not a code bug - left as pending, needs retry from a session/environment without this restriction.</t>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -16558,10 +17943,14 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J72" t="inlineStr">
         <is>
           <t>Pivoted entirely from furniture trading to AI data center services after acquisition by PT Nextier Datamate Center; approved a rights issue of up to 285.7M shares and acquired PT Nextier Askara Center and PT Nextier GenAi Center to build AI data center infrastructure</t>
@@ -17130,12 +18519,12 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Attempted 2026-09-12T07:16:55Z: browser navigation blocked by this session's network egress policy (confirmed via curl through the agent proxy: CONNECT tunnel failed, response 403 for www.ub.ac.id:443 and www.google.com:443; proxy status endpoint recorded connect_rejected / 'gateway answered 403 to CONNECT', confirming a session-wide policy block, not a site-specific issue, consistent with every prior batch). Not a code bug - left as pending, needs retry from a session/environment without this r</t>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -17602,12 +18991,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>blocked</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>2026-09-14 dual-channel-backup run: NOT attempted. This session's network egress policy blocked outbound CONNECT (agentproxy status showed repeated connect_rejected / 403-to-CONNECT, e.g. to www.google.com, moments before this batch) -- same root cause documented for Playwright/WebFetch in this environment. No navigation was performed and no fields were filled or guessed. Left as pending for retry in a session where egress isn't blocked.</t>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -18108,10 +19497,14 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J105" t="inlineStr">
         <is>
           <t>Keeps sensitive data and AI workloads on-premise (30+ GenAI applications in production) rather than in external cloud, and plans to lift annual technology spending above S$771M under new CEO's AI push</t>
@@ -18766,10 +20159,14 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J120" t="inlineStr">
         <is>
           <t>Computer Weekly reports Colt built its Jurong East, Singapore facility (SGDC1, Tier 3+) and is introducing new data-centre cooling technology (dry heat exchanges) aiming for a PUE of about 1.3-1.35 -- a direct, publicly stated cooling-efficiency initiative at an active Singapore facility.</t>
@@ -19034,10 +20431,14 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J126" t="inlineStr">
         <is>
           <t>Synapxe, Singapore's national HealthTech agency, built H-Cloud to rationalise and consolidate local hospital data centres into a modernised, nation-wide private cloud serving all public hospitals, specialty centres, polyclinics and nursing homes. No domain-matched named-individual email found, only a contact form.</t>
@@ -19084,10 +20485,14 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J127" t="inlineStr">
         <is>
           <t>Singapore-founded and HQ'd SMC runs fully immersion-cooled NVIDIA GPU clusters (SIN01/SIN02 availability zones at STT GDC) for AI training/inference, with co-CEO Tim Rosenfield stating immersion cooling 'enables high density hosting for GPUs...the sort of hosting we need to see for platforms like [Nvidia's] Grace Blackwell.' No domain-matched published email found (only third-party guessed patterns, not used); routed via contact form.</t>
@@ -19218,10 +20623,14 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>GlobalFoundries officially opened its US$4B expansion fab in Singapore (23,000 sqm), its most advanced Singapore semiconductor facility to date, raising overall Singapore capacity to ~1.5M 300mm wafers/year. Named PR contact Luana Low (Public Relations, Singapore) found on GF's own newsroom page, but exact email text was obscured/unrenderable in search results, so not used as a verified address; routed via contact form.</t>
@@ -21000,10 +22409,14 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I169" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J169" t="inlineStr">
         <is>
           <t>Tier III (Uptime Institute) 20MW greenfield hyperscale data center in Cikarang/Jakarta with 2N UPS redundancy and N+1 cooling infrastructure, expandable to 80MW on a 68,000 sqm campus (GTC Fund/China Telecom-backed); Operations Manager Stanley Go holds ASHRAE BCxP (building/mechanical commissioning) credential, a real facilities-engineering signal.</t>
@@ -21894,10 +23307,14 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="I188" t="inlineStr"/>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
       <c r="J188" t="inlineStr">
         <is>
           <t>Keppel DC Singapore 9 construction (mid-2026 start), AI-ready Genting Lane campus expansion.</t>
@@ -22413,6 +23830,60 @@
       <c r="L199" t="inlineStr">
         <is>
           <t>2026-09-30T02:17:08+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Cheng Mui Lian</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>Investor Relations and Sustainability</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Mapletree Industrial Trust</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>https://www.mapletreeindustrialtrust.com</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr"/>
+      <c r="F200" t="inlineStr"/>
+      <c r="G200" t="inlineStr">
+        <is>
+          <t>https://www.mapletreeindustrialtrust.com/contact-us/</t>
+        </is>
+      </c>
+      <c r="H200" t="inlineStr">
+        <is>
+          <t>blocked</t>
+        </is>
+      </c>
+      <c r="I200" t="inlineStr">
+        <is>
+          <t>2026-10-01 Day 17 run: NOT filled. Confirmed session-wide network egress block before and during this batch: curl via agentproxy status endpoint showed repeated connect_rejected / "gateway answered 403 to CONNECT" for www.google.com:443 (generic control host), and a live fill_contact_form() test against this batch (Mapletree Industrial Trust row, https://www.mapletreeindustrialtrust.com/contact-us/) returned navigation_failed: ERR_TUNNEL_CONNECTION_FAILED, with the proxy status endpoint then rec</t>
+        </is>
+      </c>
+      <c r="J200" t="inlineStr">
+        <is>
+          <t>Mapletree Industrial Trust's data-centre portfolio is roughly 57% of its S$8.3B total AUM, including the purpose-built 7 Tai Seng Drive facility (fully leased to Equinix Singapore) and the Sunview Drive data centre in Singapore.</t>
+        </is>
+      </c>
+      <c r="K200" t="inlineStr">
+        <is>
+          <t>https://www.mapletreeindustrialtrust.com/about-us/</t>
+        </is>
+      </c>
+      <c r="L200" t="inlineStr">
+        <is>
+          <t>2026-10-01T02:18:24+00:00</t>
         </is>
       </c>
     </row>

--- a/data/crm_database_full.xlsx
+++ b/data/crm_database_full.xlsx
@@ -415,7 +415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U181"/>
+  <dimension ref="A1:U192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13779,7 +13779,7 @@
       </c>
       <c r="K171" t="inlineStr">
         <is>
-          <t>sent</t>
+          <t>bounced</t>
         </is>
       </c>
       <c r="L171" t="n">
@@ -13790,17 +13790,17 @@
           <t>gmail:1a0f54756301e30b</t>
         </is>
       </c>
-      <c r="N171" t="inlineStr"/>
+      <c r="N171" t="inlineStr">
+        <is>
+          <t>550 5.4.1 Recipient address rejected: Access denied. (lgsinarmas-com.mail.protection.outlook.com)</t>
+        </is>
+      </c>
       <c r="O171" t="inlineStr">
         <is>
           <t>2026-10-01T02:24:30+00:00</t>
         </is>
       </c>
-      <c r="P171" t="inlineStr">
-        <is>
-          <t>2026-10-01T02:24:57+00:00</t>
-        </is>
-      </c>
+      <c r="P171" t="inlineStr"/>
       <c r="Q171" t="inlineStr">
         <is>
           <t>none</t>
@@ -14516,6 +14516,713 @@
       </c>
       <c r="T181" t="inlineStr"/>
       <c r="U181" t="inlineStr"/>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>annho@ap.equinix.com</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Annie Ho</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Asia-Pacific Media Contact</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Equinix Singapore</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>https://www.equinix.com/data-centers/asia-pacific-colocation/singapore-colocation</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr"/>
+      <c r="G182" t="inlineStr"/>
+      <c r="H182" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I182" t="inlineStr">
+        <is>
+          <t>web_research: https://www.mingtiandi.com/real-estate/data-centres/equinix-developing-260m-data-centre-as-sixth-singapore-facility/ — Equinix is developing SG6, a US$260M+ sixth Singapore IBX data center explicitly positioned to accelerate AI innovation capacity, following the US$86M SG5 expansion.</t>
+        </is>
+      </c>
+      <c r="J182" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K182" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L182" t="n">
+        <v>0</v>
+      </c>
+      <c r="M182" t="inlineStr"/>
+      <c r="N182" t="inlineStr"/>
+      <c r="O182" t="inlineStr"/>
+      <c r="P182" t="inlineStr"/>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T182" t="inlineStr"/>
+      <c r="U182" t="inlineStr"/>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>media@soitec.com</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr"/>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Media Relations</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Soitec Singapore</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>https://www.soitec.com</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr"/>
+      <c r="G183" t="inlineStr"/>
+      <c r="H183" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I183" t="inlineStr">
+        <is>
+          <t>web_research: https://www.edb.gov.sg/en/about-edb/media-releases-publications/soitec-breaks-ground-on-singapore-fab-extension-to-grow-its-global-semiconductor-wafer-production-capacity.html — Soitec is investing EUR400M (~$430M) to double capacity at its Pasir Ris, Singapore wafer fab (+45,000 sqm), qualifying the facility for high-volume Photonics SOI manufacturing to supply substrates for AI-focused data centers.</t>
+        </is>
+      </c>
+      <c r="J183" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K183" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L183" t="n">
+        <v>0</v>
+      </c>
+      <c r="M183" t="inlineStr"/>
+      <c r="N183" t="inlineStr"/>
+      <c r="O183" t="inlineStr"/>
+      <c r="P183" t="inlineStr"/>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T183" t="inlineStr"/>
+      <c r="U183" t="inlineStr"/>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>contact@statschippac.com</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>General Enquiries</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>STATS ChipPAC (JCET Group) Singapore</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>https://www.statschippac.com</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="I184" t="inlineStr">
+        <is>
+          <t>web_research: https://www.digitimes.com/news/a20251030PD205/jcet-singapore-packaging-demand-5g-hpc.html — STATS ChipPAC's Singapore Yishun campus (JCET Group's Singapore advanced-packaging hub) is central to JCET's next-generation semiconductor packaging blueprint for rising AI/5G/HPC chip demand, using JCET's proprietary XDFOI 2.5D/3D heterogeneous integration platform which requires high-density interconnect and thermal management for AI accelerators.</t>
+        </is>
+      </c>
+      <c r="J184" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L184" t="n">
+        <v>0</v>
+      </c>
+      <c r="M184" t="inlineStr"/>
+      <c r="N184" t="inlineStr"/>
+      <c r="O184" t="inlineStr"/>
+      <c r="P184" t="inlineStr"/>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T184" t="inlineStr"/>
+      <c r="U184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>simran.sethi@microsoft.com</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Simran Singh Sethi</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Head of Communications, Southeast Asia, Hong Kong &amp; Taiwan, Microsoft</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Microsoft Indonesia</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>https://news.microsoft.com/source/asia/</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr"/>
+      <c r="G185" t="inlineStr"/>
+      <c r="H185" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>web_research: https://news.microsoft.com/id-id/2025/05/27/microsoft-opens-indonesia-central/ — Microsoft opened Indonesia Central, its first Azure cloud region in Indonesia, with a planned US$1.7 billion investment (2024-2028); the region has three Availability Zones each with separate power, cooling, and networking, and now offers GPU-accelerated VM options for AI workloads.</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L185" t="n">
+        <v>0</v>
+      </c>
+      <c r="M185" t="inlineStr"/>
+      <c r="N185" t="inlineStr"/>
+      <c r="O185" t="inlineStr"/>
+      <c r="P185" t="inlineStr"/>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R185" t="inlineStr"/>
+      <c r="S185" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T185" t="inlineStr"/>
+      <c r="U185" t="inlineStr"/>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>sales@huaweicloud.com</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr"/>
+      <c r="C186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Huawei Cloud Indonesia</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>https://www.huaweicloud.com/intl/en-us/</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr"/>
+      <c r="G186" t="inlineStr"/>
+      <c r="H186" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I186" t="inlineStr">
+        <is>
+          <t>web_research: https://www.telecompaper.com/news/huawei-cloud-to-expand-indonesia-ops-launch-4th-availability-zone-by-2026--1556161 — Huawei Cloud's existing 3-Availability-Zone Jakarta region has reached 90.99% utilization and the company plans to roll out a 4th Availability Zone in Jakarta by 2026, alongside new AI platform offerings (ModelArts, Data Fabric) for the Indonesian market.</t>
+        </is>
+      </c>
+      <c r="J186" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K186" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L186" t="n">
+        <v>0</v>
+      </c>
+      <c r="M186" t="inlineStr"/>
+      <c r="N186" t="inlineStr"/>
+      <c r="O186" t="inlineStr"/>
+      <c r="P186" t="inlineStr"/>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R186" t="inlineStr"/>
+      <c r="S186" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T186" t="inlineStr"/>
+      <c r="U186" t="inlineStr"/>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>intlcloudsupport@tencent.com</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Tencent Cloud Indonesia</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>https://www.tencentcloud.com/</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I187" t="inlineStr">
+        <is>
+          <t>web_research: https://www.datacenterdynamics.com/en/news/tencent-to-invest-500m-for-data-center-development-in-indonesia/ — Tencent is investing US$500 million by 2030 in Indonesia cloud and AI infrastructure, operating multiple Jakarta data centers and a newly launched GPU Cloud region to support AI workloads.</t>
+        </is>
+      </c>
+      <c r="J187" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L187" t="n">
+        <v>0</v>
+      </c>
+      <c r="M187" t="inlineStr"/>
+      <c r="N187" t="inlineStr"/>
+      <c r="O187" t="inlineStr"/>
+      <c r="P187" t="inlineStr"/>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R187" t="inlineStr"/>
+      <c r="S187" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T187" t="inlineStr"/>
+      <c r="U187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>info@edgeconnex.com</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr"/>
+      <c r="C188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>EdgeConneX Indonesia</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>https://www.edgeconnex.com/</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr"/>
+      <c r="G188" t="inlineStr"/>
+      <c r="H188" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I188" t="inlineStr">
+        <is>
+          <t>web_research: https://thetechcapital.com/edgeconnex-expands-jakarta-data-centre-campus-to-over-200-mw-capacity/ — EdgeConneX tripled its Jakarta hyperscale data center campus capacity to over 200MW (via a 45,000 sqm Bekasi/Cikarang land acquisition) specifically to host multi-tenant GPU clusters for AI workloads.</t>
+        </is>
+      </c>
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L188" t="n">
+        <v>0</v>
+      </c>
+      <c r="M188" t="inlineStr"/>
+      <c r="N188" t="inlineStr"/>
+      <c r="O188" t="inlineStr"/>
+      <c r="P188" t="inlineStr"/>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R188" t="inlineStr"/>
+      <c r="S188" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T188" t="inlineStr"/>
+      <c r="U188" t="inlineStr"/>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>commpge@pertamina.com</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr"/>
+      <c r="C189" t="inlineStr"/>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>Pertamina Geothermal Energy (PGEO)</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>https://www.pge.pertamina.com/</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
+      <c r="H189" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I189" t="inlineStr">
+        <is>
+          <t>web_research: https://www.cnbcindonesia.com/market/20260804161817-17-756516/pertamina-geothermal-energy--pgeo--siapkan-pilot-project-data-center — PGEO is building its own pilot green data center in Kamojang, West Java, paired with a dedicated 5MW geothermal power plant built specifically to supply it, as part of its 'Beyond Electricity' diversification strategy pursued jointly with IDPRO and Universitas Indonesia.</t>
+        </is>
+      </c>
+      <c r="J189" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K189" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L189" t="n">
+        <v>0</v>
+      </c>
+      <c r="M189" t="inlineStr"/>
+      <c r="N189" t="inlineStr"/>
+      <c r="O189" t="inlineStr"/>
+      <c r="P189" t="inlineStr"/>
+      <c r="Q189" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R189" t="inlineStr"/>
+      <c r="S189" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T189" t="inlineStr"/>
+      <c r="U189" t="inlineStr"/>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>info@sinergynetworks.co.id</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr"/>
+      <c r="C190" t="inlineStr"/>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>Sinergi Inti Andalan Prima (INET) / PT Sinergi Inti Data Indonesia (SIDI)</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>https://siapnetworks.co.id/</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>+62 812-4000-7427</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr"/>
+      <c r="H190" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I190" t="inlineStr">
+        <is>
+          <t>web_research: https://market.bisnis.com/read/20260812/192/1995734/inet-buka-data-center-di-gedung-cyber-bidik-pertumbuhan-bisnis — INET's data center subsidiary SIDI launched Data Center JKT01 at Cyber Building 1, Jakarta, and is preparing a larger expansion project in Purwakarta, driven by rising cloud and AI workload demand.</t>
+        </is>
+      </c>
+      <c r="J190" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K190" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L190" t="n">
+        <v>0</v>
+      </c>
+      <c r="M190" t="inlineStr"/>
+      <c r="N190" t="inlineStr"/>
+      <c r="O190" t="inlineStr"/>
+      <c r="P190" t="inlineStr"/>
+      <c r="Q190" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R190" t="inlineStr"/>
+      <c r="S190" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T190" t="inlineStr"/>
+      <c r="U190" t="inlineStr"/>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>sales.id@trendmicro.com</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>Trend Micro Indonesia (TrendAI)</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>https://www.trendmicro.com/en_id/</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I191" t="inlineStr">
+        <is>
+          <t>web_research: https://www.trendmicro.com/en_id/business/ai.html — TrendAI has expanded its data center capabilities with new local infrastructure in Indonesia, giving Indonesian enterprises in-country data residency and dedicated local AI security processing capacity.</t>
+        </is>
+      </c>
+      <c r="J191" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K191" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L191" t="n">
+        <v>0</v>
+      </c>
+      <c r="M191" t="inlineStr"/>
+      <c r="N191" t="inlineStr"/>
+      <c r="O191" t="inlineStr"/>
+      <c r="P191" t="inlineStr"/>
+      <c r="Q191" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R191" t="inlineStr"/>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T191" t="inlineStr"/>
+      <c r="U191" t="inlineStr"/>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>bnbr.corcomm@bakrie.co.id</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Christofer Alexander Uktolseja</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Corporate Secretary</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>Bakrie &amp; Brothers (BNBR)</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>https://bakrie-brothers.com/</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr"/>
+      <c r="G192" t="inlineStr"/>
+      <c r="H192" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="I192" t="inlineStr">
+        <is>
+          <t>web_research: https://www.cnbcindonesia.com/market/20260227185032-17-714679/grup-bakrie--bnbr--jajaki-bisnis-data-center-ini-kata-anindya-bakrie — BNBR's subsidiary PT Multi Kontrol Nusantara acquired 1.67 hectares of land in Kalideres, West Jakarta (Rp500 billion) to build an inner-city data center.</t>
+        </is>
+      </c>
+      <c r="J192" t="inlineStr">
+        <is>
+          <t>legitimate_interest_b2b_public_contact</t>
+        </is>
+      </c>
+      <c r="K192" t="inlineStr">
+        <is>
+          <t>unsent</t>
+        </is>
+      </c>
+      <c r="L192" t="n">
+        <v>0</v>
+      </c>
+      <c r="M192" t="inlineStr"/>
+      <c r="N192" t="inlineStr"/>
+      <c r="O192" t="inlineStr"/>
+      <c r="P192" t="inlineStr"/>
+      <c r="Q192" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T192" t="inlineStr"/>
+      <c r="U192" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -14528,7 +15235,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L200"/>
+  <dimension ref="A1:L201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -23884,6 +24591,48 @@
       <c r="L200" t="inlineStr">
         <is>
           <t>2026-10-01T02:18:24+00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr"/>
+      <c r="B201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>STATS ChipPAC (JCET Group) Singapore</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>https://www.statschippac.com</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr"/>
+      <c r="F201" t="inlineStr"/>
+      <c r="G201" t="inlineStr">
+        <is>
+          <t>https://www.statschippac.com/contact-us</t>
+        </is>
+      </c>
+      <c r="H201" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="I201" t="inlineStr"/>
+      <c r="J201" t="inlineStr">
+        <is>
+          <t>STATS ChipPAC's Singapore Yishun campus (JCET Group's Singapore advanced-packaging hub) supports JCET's XDFOI 2.5D/3D heterogeneous integration platform for AI/HPC chip packaging, which requires high-density interconnect and thermal management for AI accelerators. Dual-channel backup alongside the domain-matched contact@statschippac.com email already in prospects.csv.</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>https://www.digitimes.com/news/a20251030PD205/jcet-singapore-packaging-demand-5g-hpc.html</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>2026-10-02T02:31:25+00:00</t>
         </is>
       </c>
     </row>
